--- a/MSC_stdev_lt.xlsx
+++ b/MSC_stdev_lt.xlsx
@@ -21,13 +21,13 @@
     <t>st_dev_lt_msc</t>
   </si>
   <si>
-    <t>st_dev_resid_lt_msc</t>
+    <t>st_dev_resid_lt_power_msc</t>
   </si>
   <si>
     <t>st_dev_lt_msc_ma</t>
   </si>
   <si>
-    <t>st_dev_resid_lt_msc_ma</t>
+    <t>st_dev_resid_lt_power_msc_ma</t>
   </si>
 </sst>
 </file>
@@ -75,7 +75,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E569"/>
+  <dimension ref="A1:E577"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -219,15 +219,11 @@
       <c r="B15" s="2">
         <v>4.1788797378540039</v>
       </c>
-      <c r="C15" s="2">
-        <v>4.1878609657287598</v>
-      </c>
+      <c r="C15" s="2"/>
       <c r="D15" s="2">
         <v>4.1788797378540039</v>
       </c>
-      <c r="E15" s="2">
-        <v>4.1878609657287598</v>
-      </c>
+      <c r="E15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="1">
@@ -335,15 +331,11 @@
       <c r="B27" s="2">
         <v>6.1115078926086426</v>
       </c>
-      <c r="C27" s="2">
-        <v>6.1378183364868164</v>
-      </c>
+      <c r="C27" s="2"/>
       <c r="D27" s="2">
         <v>6.1115078926086426</v>
       </c>
-      <c r="E27" s="2">
-        <v>6.1378183364868164</v>
-      </c>
+      <c r="E27" s="2"/>
     </row>
     <row r="28">
       <c r="A28" s="1">
@@ -397,15 +389,11 @@
       <c r="B33" s="2">
         <v>5.7580242156982422</v>
       </c>
-      <c r="C33" s="2">
-        <v>5.908879280090332</v>
-      </c>
+      <c r="C33" s="2"/>
       <c r="D33" s="2">
         <v>5.8651628494262695</v>
       </c>
-      <c r="E33" s="2">
-        <v>5.9052715301513672</v>
-      </c>
+      <c r="E33" s="2"/>
     </row>
     <row r="34">
       <c r="A34" s="1">
@@ -414,15 +402,11 @@
       <c r="B34" s="2">
         <v>5.9723010063171387</v>
       </c>
-      <c r="C34" s="2">
-        <v>5.9016642570495605</v>
-      </c>
+      <c r="C34" s="2"/>
       <c r="D34" s="2">
         <v>5.9284567832946777</v>
       </c>
-      <c r="E34" s="2">
-        <v>5.9282093048095703</v>
-      </c>
+      <c r="E34" s="2"/>
     </row>
     <row r="35">
       <c r="A35" s="1">
@@ -458,15 +442,11 @@
       <c r="B38" s="2">
         <v>6.0550446510314941</v>
       </c>
-      <c r="C38" s="2">
-        <v>5.9740843772888184</v>
-      </c>
+      <c r="C38" s="2"/>
       <c r="D38" s="2">
         <v>5.9516944885253906</v>
       </c>
-      <c r="E38" s="2">
-        <v>5.8538951873779297</v>
-      </c>
+      <c r="E38" s="2"/>
     </row>
     <row r="39">
       <c r="A39" s="1">
@@ -475,15 +455,11 @@
       <c r="B39" s="2">
         <v>5.4729719161987305</v>
       </c>
-      <c r="C39" s="2">
-        <v>5.3173108100891113</v>
-      </c>
+      <c r="C39" s="2"/>
       <c r="D39" s="2">
         <v>5.9448256492614746</v>
       </c>
-      <c r="E39" s="2">
-        <v>5.8379721641540527</v>
-      </c>
+      <c r="E39" s="2"/>
     </row>
     <row r="40">
       <c r="A40" s="1">
@@ -492,15 +468,11 @@
       <c r="B40" s="2">
         <v>6.306459903717041</v>
       </c>
-      <c r="C40" s="2">
-        <v>6.2225213050842285</v>
-      </c>
+      <c r="C40" s="2"/>
       <c r="D40" s="2">
         <v>5.9566988945007324</v>
       </c>
-      <c r="E40" s="2">
-        <v>5.8947439193725586</v>
-      </c>
+      <c r="E40" s="2"/>
     </row>
     <row r="41">
       <c r="A41" s="1">
@@ -536,15 +508,11 @@
       <c r="B44" s="2">
         <v>5.9923186302185059</v>
       </c>
-      <c r="C44" s="2">
-        <v>6.065058708190918</v>
-      </c>
+      <c r="C44" s="2"/>
       <c r="D44" s="2">
         <v>6.1459627151489258</v>
       </c>
-      <c r="E44" s="2">
-        <v>6.1218180656433105</v>
-      </c>
+      <c r="E44" s="2"/>
     </row>
     <row r="45">
       <c r="A45" s="1">
@@ -553,15 +521,11 @@
       <c r="B45" s="2">
         <v>6.0672760009765625</v>
       </c>
-      <c r="C45" s="2">
-        <v>5.9382591247558594</v>
-      </c>
+      <c r="C45" s="2"/>
       <c r="D45" s="2">
         <v>6.0924639701843262</v>
       </c>
-      <c r="E45" s="2">
-        <v>6.0882501602172852</v>
-      </c>
+      <c r="E45" s="2"/>
     </row>
     <row r="46">
       <c r="A46" s="1">
@@ -570,15 +534,11 @@
       <c r="B46" s="2">
         <v>6.2177972793579102</v>
       </c>
-      <c r="C46" s="2">
-        <v>6.2614331245422363</v>
-      </c>
+      <c r="C46" s="2"/>
       <c r="D46" s="2">
         <v>5.9169168472290039</v>
       </c>
-      <c r="E46" s="2">
-        <v>5.8947548866271973</v>
-      </c>
+      <c r="E46" s="2"/>
     </row>
     <row r="47">
       <c r="A47" s="1">
@@ -614,15 +574,11 @@
       <c r="B50" s="2">
         <v>5.3902754783630371</v>
       </c>
-      <c r="C50" s="2">
-        <v>5.3142685890197754</v>
-      </c>
+      <c r="C50" s="2"/>
       <c r="D50" s="2">
         <v>5.8341712951660156</v>
       </c>
-      <c r="E50" s="2">
-        <v>5.7847247123718262</v>
-      </c>
+      <c r="E50" s="2"/>
     </row>
     <row r="51">
       <c r="A51" s="1">
@@ -631,15 +587,11 @@
       <c r="B51" s="2">
         <v>5.9486303329467773</v>
       </c>
-      <c r="C51" s="2">
-        <v>5.8905973434448242</v>
-      </c>
+      <c r="C51" s="2"/>
       <c r="D51" s="2">
         <v>5.7062959671020508</v>
       </c>
-      <c r="E51" s="2">
-        <v>5.625821590423584</v>
-      </c>
+      <c r="E51" s="2"/>
     </row>
     <row r="52">
       <c r="A52" s="1">
@@ -648,15 +600,11 @@
       <c r="B52" s="2">
         <v>5.7799816131591797</v>
       </c>
-      <c r="C52" s="2">
-        <v>5.6725993156433105</v>
-      </c>
+      <c r="C52" s="2"/>
       <c r="D52" s="2">
         <v>5.6263575553894043</v>
       </c>
-      <c r="E52" s="2">
-        <v>5.5696134567260742</v>
-      </c>
+      <c r="E52" s="2"/>
     </row>
     <row r="53">
       <c r="A53" s="1">
@@ -692,15 +640,11 @@
       <c r="B56" s="2">
         <v>5.3865432739257812</v>
       </c>
-      <c r="C56" s="2">
-        <v>5.4009895324707031</v>
-      </c>
+      <c r="C56" s="2"/>
       <c r="D56" s="2">
         <v>5.6400809288024902</v>
       </c>
-      <c r="E56" s="2">
-        <v>5.5655379295349121</v>
-      </c>
+      <c r="E56" s="2"/>
     </row>
     <row r="57">
       <c r="A57" s="1">
@@ -709,15 +653,11 @@
       <c r="B57" s="2">
         <v>5.5564494132995605</v>
       </c>
-      <c r="C57" s="2">
-        <v>5.5814008712768555</v>
-      </c>
+      <c r="C57" s="2"/>
       <c r="D57" s="2">
         <v>5.5934476852416992</v>
       </c>
-      <c r="E57" s="2">
-        <v>5.529850959777832</v>
-      </c>
+      <c r="E57" s="2"/>
     </row>
     <row r="58">
       <c r="A58" s="1">
@@ -726,15 +666,11 @@
       <c r="B58" s="2">
         <v>5.8373498916625977</v>
       </c>
-      <c r="C58" s="2">
-        <v>5.6071624755859375</v>
-      </c>
+      <c r="C58" s="2"/>
       <c r="D58" s="2">
         <v>5.580876350402832</v>
       </c>
-      <c r="E58" s="2">
-        <v>5.5307254791259766</v>
-      </c>
+      <c r="E58" s="2"/>
     </row>
     <row r="59">
       <c r="A59" s="1">
@@ -770,15 +706,11 @@
       <c r="B62" s="2">
         <v>5.5431632995605469</v>
       </c>
-      <c r="C62" s="2">
-        <v>5.5333495140075684</v>
-      </c>
+      <c r="C62" s="2"/>
       <c r="D62" s="2">
         <v>5.5256805419921875</v>
       </c>
-      <c r="E62" s="2">
-        <v>5.3989272117614746</v>
-      </c>
+      <c r="E62" s="2"/>
     </row>
     <row r="63">
       <c r="A63" s="1">
@@ -787,15 +719,11 @@
       <c r="B63" s="2">
         <v>5.6156759262084961</v>
       </c>
-      <c r="C63" s="2">
-        <v>5.4378347396850586</v>
-      </c>
+      <c r="C63" s="2"/>
       <c r="D63" s="2">
         <v>5.421790599822998</v>
       </c>
-      <c r="E63" s="2">
-        <v>5.3295154571533203</v>
-      </c>
+      <c r="E63" s="2"/>
     </row>
     <row r="64">
       <c r="A64" s="1">
@@ -804,15 +732,11 @@
       <c r="B64" s="2">
         <v>5.1065330505371094</v>
       </c>
-      <c r="C64" s="2">
-        <v>5.0173625946044922</v>
-      </c>
+      <c r="C64" s="2"/>
       <c r="D64" s="2">
         <v>5.3345050811767578</v>
       </c>
-      <c r="E64" s="2">
-        <v>5.2467041015625</v>
-      </c>
+      <c r="E64" s="2"/>
     </row>
     <row r="65">
       <c r="A65" s="1">
@@ -848,15 +772,11 @@
       <c r="B68" s="2">
         <v>5.0726470947265625</v>
       </c>
-      <c r="C68" s="2">
-        <v>4.9982705116271973</v>
-      </c>
+      <c r="C68" s="2"/>
       <c r="D68" s="2">
         <v>5.0970463752746582</v>
       </c>
-      <c r="E68" s="2">
-        <v>5.0724163055419922</v>
-      </c>
+      <c r="E68" s="2"/>
     </row>
     <row r="69">
       <c r="A69" s="1">
@@ -865,15 +785,11 @@
       <c r="B69" s="2">
         <v>4.991325855255127</v>
       </c>
-      <c r="C69" s="2">
-        <v>5.0341448783874512</v>
-      </c>
+      <c r="C69" s="2"/>
       <c r="D69" s="2">
         <v>5.0938844680786133</v>
       </c>
-      <c r="E69" s="2">
-        <v>5.0907678604125977</v>
-      </c>
+      <c r="E69" s="2"/>
     </row>
     <row r="70">
       <c r="A70" s="1">
@@ -882,15 +798,11 @@
       <c r="B70" s="2">
         <v>5.2176799774169922</v>
       </c>
-      <c r="C70" s="2">
-        <v>5.2398881912231445</v>
-      </c>
+      <c r="C70" s="2"/>
       <c r="D70" s="2">
         <v>4.9554963111877441</v>
       </c>
-      <c r="E70" s="2">
-        <v>4.9433250427246094</v>
-      </c>
+      <c r="E70" s="2"/>
     </row>
     <row r="71">
       <c r="A71" s="1">
@@ -926,15 +838,11 @@
       <c r="B74" s="2">
         <v>4.5403318405151367</v>
       </c>
-      <c r="C74" s="2">
-        <v>4.5009965896606445</v>
-      </c>
+      <c r="C74" s="2"/>
       <c r="D74" s="2">
         <v>4.8358821868896484</v>
       </c>
-      <c r="E74" s="2">
-        <v>4.7992544174194336</v>
-      </c>
+      <c r="E74" s="2"/>
     </row>
     <row r="75">
       <c r="A75" s="1">
@@ -943,15 +851,11 @@
       <c r="B75" s="2">
         <v>4.6630620956420898</v>
       </c>
-      <c r="C75" s="2">
-        <v>4.5694117546081543</v>
-      </c>
+      <c r="C75" s="2"/>
       <c r="D75" s="2">
         <v>4.7086162567138672</v>
       </c>
-      <c r="E75" s="2">
-        <v>4.6523761749267578</v>
-      </c>
+      <c r="E75" s="2"/>
     </row>
     <row r="76">
       <c r="A76" s="1">
@@ -960,15 +864,11 @@
       <c r="B76" s="2">
         <v>4.922454833984375</v>
       </c>
-      <c r="C76" s="2">
-        <v>4.8867206573486328</v>
-      </c>
+      <c r="C76" s="2"/>
       <c r="D76" s="2">
         <v>4.8247361183166504</v>
       </c>
-      <c r="E76" s="2">
-        <v>4.8026409149169922</v>
-      </c>
+      <c r="E76" s="2"/>
     </row>
     <row r="77">
       <c r="A77" s="1">
@@ -1004,15 +904,11 @@
       <c r="B80" s="2">
         <v>5.173095703125</v>
       </c>
-      <c r="C80" s="2">
-        <v>5.2534341812133789</v>
-      </c>
+      <c r="C80" s="2"/>
       <c r="D80" s="2">
         <v>4.7965712547302246</v>
       </c>
-      <c r="E80" s="2">
-        <v>4.7713065147399902</v>
-      </c>
+      <c r="E80" s="2"/>
     </row>
     <row r="81">
       <c r="A81" s="1">
@@ -1021,15 +917,11 @@
       <c r="B81" s="2">
         <v>4.6439208984375</v>
       </c>
-      <c r="C81" s="2">
-        <v>4.5649881362915039</v>
-      </c>
+      <c r="C81" s="2"/>
       <c r="D81" s="2">
         <v>4.7546100616455078</v>
       </c>
-      <c r="E81" s="2">
-        <v>4.7328352928161621</v>
-      </c>
+      <c r="E81" s="2"/>
     </row>
     <row r="82">
       <c r="A82" s="1">
@@ -1038,15 +930,11 @@
       <c r="B82" s="2">
         <v>4.4468135833740234</v>
       </c>
-      <c r="C82" s="2">
-        <v>4.3800835609436035</v>
-      </c>
+      <c r="C82" s="2"/>
       <c r="D82" s="2">
         <v>4.757075309753418</v>
       </c>
-      <c r="E82" s="2">
-        <v>4.713047981262207</v>
-      </c>
+      <c r="E82" s="2"/>
     </row>
     <row r="83">
       <c r="A83" s="1">
@@ -1082,15 +970,11 @@
       <c r="B86" s="2">
         <v>4.7644710540771484</v>
       </c>
-      <c r="C86" s="2">
-        <v>4.6536855697631836</v>
-      </c>
+      <c r="C86" s="2"/>
       <c r="D86" s="2">
         <v>4.815241813659668</v>
       </c>
-      <c r="E86" s="2">
-        <v>4.7348203659057617</v>
-      </c>
+      <c r="E86" s="2"/>
     </row>
     <row r="87">
       <c r="A87" s="1">
@@ -1099,15 +983,11 @@
       <c r="B87" s="2">
         <v>4.888249397277832</v>
       </c>
-      <c r="C87" s="2">
-        <v>4.811887264251709</v>
-      </c>
+      <c r="C87" s="2"/>
       <c r="D87" s="2">
         <v>4.9380512237548828</v>
       </c>
-      <c r="E87" s="2">
-        <v>4.8530664443969727</v>
-      </c>
+      <c r="E87" s="2"/>
     </row>
     <row r="88">
       <c r="A88" s="1">
@@ -1116,15 +996,11 @@
       <c r="B88" s="2">
         <v>5.1614327430725098</v>
       </c>
-      <c r="C88" s="2">
-        <v>5.0936260223388672</v>
-      </c>
+      <c r="C88" s="2"/>
       <c r="D88" s="2">
         <v>4.8513517379760742</v>
       </c>
-      <c r="E88" s="2">
-        <v>4.7517871856689453</v>
-      </c>
+      <c r="E88" s="2"/>
     </row>
     <row r="89">
       <c r="A89" s="1">
@@ -1160,15 +1036,11 @@
       <c r="B92" s="2">
         <v>4.5912532806396484</v>
       </c>
-      <c r="C92" s="2">
-        <v>4.4479494094848633</v>
-      </c>
+      <c r="C92" s="2"/>
       <c r="D92" s="2">
         <v>4.6403255462646484</v>
       </c>
-      <c r="E92" s="2">
-        <v>4.5827727317810059</v>
-      </c>
+      <c r="E92" s="2"/>
     </row>
     <row r="93">
       <c r="A93" s="1">
@@ -1177,15 +1049,11 @@
       <c r="B93" s="2">
         <v>4.1453595161437988</v>
       </c>
-      <c r="C93" s="2">
-        <v>4.1632308959960938</v>
-      </c>
+      <c r="C93" s="2"/>
       <c r="D93" s="2">
         <v>4.4666228294372559</v>
       </c>
-      <c r="E93" s="2">
-        <v>4.4124884605407715</v>
-      </c>
+      <c r="E93" s="2"/>
     </row>
     <row r="94">
       <c r="A94" s="1">
@@ -1194,15 +1062,11 @@
       <c r="B94" s="2">
         <v>4.6632556915283203</v>
       </c>
-      <c r="C94" s="2">
-        <v>4.6262845993041992</v>
-      </c>
+      <c r="C94" s="2"/>
       <c r="D94" s="2">
         <v>4.4666228294372559</v>
       </c>
-      <c r="E94" s="2">
-        <v>4.4124884605407715</v>
-      </c>
+      <c r="E94" s="2"/>
     </row>
     <row r="95">
       <c r="A95" s="1">
@@ -1256,15 +1120,11 @@
       <c r="B100" s="2">
         <v>4.4021458625793457</v>
       </c>
-      <c r="C100" s="2">
-        <v>4.1623001098632812</v>
-      </c>
+      <c r="C100" s="2"/>
       <c r="D100" s="2">
         <v>4.1503567695617676</v>
       </c>
-      <c r="E100" s="2">
-        <v>3.9591379165649414</v>
-      </c>
+      <c r="E100" s="2"/>
     </row>
     <row r="101">
       <c r="A101" s="1">
@@ -1291,15 +1151,11 @@
       <c r="B103" s="2">
         <v>3.8985676765441895</v>
       </c>
-      <c r="C103" s="2">
-        <v>3.7559754848480225</v>
-      </c>
+      <c r="C103" s="2"/>
       <c r="D103" s="2">
         <v>4.0395383834838867</v>
       </c>
-      <c r="E103" s="2">
-        <v>3.9068701267242432</v>
-      </c>
+      <c r="E103" s="2"/>
     </row>
     <row r="104">
       <c r="A104" s="1">
@@ -1326,15 +1182,11 @@
       <c r="B106" s="2">
         <v>3.8179013729095459</v>
       </c>
-      <c r="C106" s="2">
-        <v>3.8023347854614258</v>
-      </c>
+      <c r="C106" s="2"/>
       <c r="D106" s="2">
         <v>4.0753483772277832</v>
       </c>
-      <c r="E106" s="2">
-        <v>4.0159292221069336</v>
-      </c>
+      <c r="E106" s="2"/>
     </row>
     <row r="107">
       <c r="A107" s="1">
@@ -1361,15 +1213,11 @@
       <c r="B109" s="2">
         <v>4.5095758438110352</v>
       </c>
-      <c r="C109" s="2">
-        <v>4.4894776344299316</v>
-      </c>
+      <c r="C109" s="2"/>
       <c r="D109" s="2">
         <v>4.1512641906738281</v>
       </c>
-      <c r="E109" s="2">
-        <v>4.0789790153503418</v>
-      </c>
+      <c r="E109" s="2"/>
     </row>
     <row r="110">
       <c r="A110" s="1">
@@ -1396,15 +1244,11 @@
       <c r="B112" s="2">
         <v>4.1263151168823242</v>
       </c>
-      <c r="C112" s="2">
-        <v>3.945124626159668</v>
-      </c>
+      <c r="C112" s="2"/>
       <c r="D112" s="2">
         <v>4.3904008865356445</v>
       </c>
-      <c r="E112" s="2">
-        <v>4.3284130096435547</v>
-      </c>
+      <c r="E112" s="2"/>
     </row>
     <row r="113">
       <c r="A113" s="1">
@@ -1431,15 +1275,11 @@
       <c r="B115" s="2">
         <v>4.5353116989135742</v>
       </c>
-      <c r="C115" s="2">
-        <v>4.5506367683410645</v>
-      </c>
+      <c r="C115" s="2"/>
       <c r="D115" s="2">
         <v>3.9998931884765625</v>
       </c>
-      <c r="E115" s="2">
-        <v>3.9512410163879395</v>
-      </c>
+      <c r="E115" s="2"/>
     </row>
     <row r="116">
       <c r="A116" s="1">
@@ -1466,15 +1306,11 @@
       <c r="B118" s="2">
         <v>3.3380529880523682</v>
       </c>
-      <c r="C118" s="2">
-        <v>3.3579614162445068</v>
-      </c>
+      <c r="C118" s="2"/>
       <c r="D118" s="2">
         <v>4.2668075561523438</v>
       </c>
-      <c r="E118" s="2">
-        <v>4.3041377067565918</v>
-      </c>
+      <c r="E118" s="2"/>
     </row>
     <row r="119">
       <c r="A119" s="1">
@@ -1501,15 +1337,11 @@
       <c r="B121" s="2">
         <v>4.9270586967468262</v>
       </c>
-      <c r="C121" s="2">
-        <v>5.0038151741027832</v>
-      </c>
+      <c r="C121" s="2"/>
       <c r="D121" s="2">
         <v>4.1325559616088867</v>
       </c>
-      <c r="E121" s="2">
-        <v>4.1808881759643555</v>
-      </c>
+      <c r="E121" s="2"/>
     </row>
     <row r="122">
       <c r="A122" s="1">
@@ -1761,15 +1593,11 @@
       <c r="B149" s="2">
         <v>4.0407509803771973</v>
       </c>
-      <c r="C149" s="2">
-        <v>4.0184760093688965</v>
-      </c>
+      <c r="C149" s="2"/>
       <c r="D149" s="2">
         <v>3.9090104103088379</v>
       </c>
-      <c r="E149" s="2">
-        <v>3.9077436923980713</v>
-      </c>
+      <c r="E149" s="2"/>
     </row>
     <row r="150">
       <c r="A150" s="1">
@@ -1778,15 +1606,11 @@
       <c r="B150" s="2">
         <v>3.6292774677276611</v>
       </c>
-      <c r="C150" s="2">
-        <v>3.6038060188293457</v>
-      </c>
+      <c r="C150" s="2"/>
       <c r="D150" s="2">
         <v>3.974285364151001</v>
       </c>
-      <c r="E150" s="2">
-        <v>3.965116024017334</v>
-      </c>
+      <c r="E150" s="2"/>
     </row>
     <row r="151">
       <c r="A151" s="1">
@@ -1795,15 +1619,11 @@
       <c r="B151" s="2">
         <v>4.0736160278320312</v>
       </c>
-      <c r="C151" s="2">
-        <v>4.039647102355957</v>
-      </c>
+      <c r="C151" s="2"/>
       <c r="D151" s="2">
         <v>3.9965953826904297</v>
       </c>
-      <c r="E151" s="2">
-        <v>3.9802112579345703</v>
-      </c>
+      <c r="E151" s="2"/>
     </row>
     <row r="152">
       <c r="A152" s="1">
@@ -1812,15 +1632,11 @@
       <c r="B152" s="2">
         <v>4.0311360359191895</v>
       </c>
-      <c r="C152" s="2">
-        <v>4.0811896324157715</v>
-      </c>
+      <c r="C152" s="2"/>
       <c r="D152" s="2">
         <v>4.0567965507507324</v>
       </c>
-      <c r="E152" s="2">
-        <v>4.0248847007751465</v>
-      </c>
+      <c r="E152" s="2"/>
     </row>
     <row r="153">
       <c r="A153" s="1">
@@ -1829,15 +1645,11 @@
       <c r="B153" s="2">
         <v>3.7702715396881104</v>
       </c>
-      <c r="C153" s="2">
-        <v>3.7956001758575439</v>
-      </c>
+      <c r="C153" s="2"/>
       <c r="D153" s="2">
         <v>4.0978078842163086</v>
       </c>
-      <c r="E153" s="2">
-        <v>4.0625333786010742</v>
-      </c>
+      <c r="E153" s="2"/>
     </row>
     <row r="154">
       <c r="A154" s="1">
@@ -1846,15 +1658,11 @@
       <c r="B154" s="2">
         <v>4.3006601333618164</v>
       </c>
-      <c r="C154" s="2">
-        <v>4.2519769668579102</v>
-      </c>
+      <c r="C154" s="2"/>
       <c r="D154" s="2">
         <v>4.1319494247436523</v>
       </c>
-      <c r="E154" s="2">
-        <v>4.0599889755249023</v>
-      </c>
+      <c r="E154" s="2"/>
     </row>
     <row r="155">
       <c r="A155" s="1">
@@ -1863,15 +1671,11 @@
       <c r="B155" s="2">
         <v>4.130455493927002</v>
       </c>
-      <c r="C155" s="2">
-        <v>4.0707831382751465</v>
-      </c>
+      <c r="C155" s="2"/>
       <c r="D155" s="2">
         <v>4.1520943641662598</v>
       </c>
-      <c r="E155" s="2">
-        <v>4.0786828994750977</v>
-      </c>
+      <c r="E155" s="2"/>
     </row>
     <row r="156">
       <c r="A156" s="1">
@@ -1880,15 +1684,11 @@
       <c r="B156" s="2">
         <v>4.478203296661377</v>
       </c>
-      <c r="C156" s="2">
-        <v>4.3375992774963379</v>
-      </c>
+      <c r="C156" s="2"/>
       <c r="D156" s="2">
         <v>4.1483449935913086</v>
       </c>
-      <c r="E156" s="2">
-        <v>4.0669960975646973</v>
-      </c>
+      <c r="E156" s="2"/>
     </row>
     <row r="157">
       <c r="A157" s="1">
@@ -1897,15 +1697,11 @@
       <c r="B157" s="2">
         <v>4.425900936126709</v>
       </c>
-      <c r="C157" s="2">
-        <v>4.3637237548828125</v>
-      </c>
+      <c r="C157" s="2"/>
       <c r="D157" s="2">
         <v>4.1562228202819824</v>
       </c>
-      <c r="E157" s="2">
-        <v>4.0643477439880371</v>
-      </c>
+      <c r="E157" s="2"/>
     </row>
     <row r="158">
       <c r="A158" s="1">
@@ -1914,15 +1710,11 @@
       <c r="B158" s="2">
         <v>4.3480219841003418</v>
       </c>
-      <c r="C158" s="2">
-        <v>3.9955751895904541</v>
-      </c>
+      <c r="C158" s="2"/>
       <c r="D158" s="2">
         <v>4.1692380905151367</v>
       </c>
-      <c r="E158" s="2">
-        <v>4.0669608116149902</v>
-      </c>
+      <c r="E158" s="2"/>
     </row>
     <row r="159">
       <c r="A159" s="1">
@@ -1931,15 +1723,11 @@
       <c r="B159" s="2">
         <v>3.8105847835540771</v>
       </c>
-      <c r="C159" s="2">
-        <v>3.7720513343811035</v>
-      </c>
+      <c r="C159" s="2"/>
       <c r="D159" s="2">
-        <v>4.0699191093444824</v>
-      </c>
-      <c r="E159" s="2">
-        <v>3.978524923324585</v>
-      </c>
+        <v>4.0693359375</v>
+      </c>
+      <c r="E159" s="2"/>
     </row>
     <row r="160">
       <c r="A160" s="1">
@@ -1948,15 +1736,11 @@
       <c r="B160" s="2">
         <v>4.0398716926574707</v>
       </c>
-      <c r="C160" s="2">
-        <v>3.9344663619995117</v>
-      </c>
+      <c r="C160" s="2"/>
       <c r="D160" s="2">
-        <v>3.9994978904724121</v>
-      </c>
-      <c r="E160" s="2">
-        <v>3.9089846611022949</v>
-      </c>
+        <v>3.9989147186279297</v>
+      </c>
+      <c r="E160" s="2"/>
     </row>
     <row r="161">
       <c r="A161" s="1">
@@ -1965,15 +1749,11 @@
       <c r="B161" s="2">
         <v>4.1020364761352539</v>
       </c>
-      <c r="C161" s="2">
-        <v>4.0573525428771973</v>
-      </c>
+      <c r="C161" s="2"/>
       <c r="D161" s="2">
-        <v>3.8941307067871094</v>
-      </c>
-      <c r="E161" s="2">
-        <v>3.8217494487762451</v>
-      </c>
+        <v>3.893547534942627</v>
+      </c>
+      <c r="E161" s="2"/>
     </row>
     <row r="162">
       <c r="A162" s="1">
@@ -1982,32 +1762,24 @@
       <c r="B162" s="2">
         <v>3.8874070644378662</v>
       </c>
-      <c r="C162" s="2">
-        <v>3.8191177845001221</v>
-      </c>
+      <c r="C162" s="2"/>
       <c r="D162" s="2">
-        <v>3.8076536655426025</v>
-      </c>
-      <c r="E162" s="2">
-        <v>3.7370572090148926</v>
-      </c>
+        <v>3.8070704936981201</v>
+      </c>
+      <c r="E162" s="2"/>
     </row>
     <row r="163">
       <c r="A163" s="1">
         <v>33390</v>
       </c>
       <c r="B163" s="2">
-        <v>3.4067883491516113</v>
-      </c>
-      <c r="C163" s="2">
-        <v>3.4560549259185791</v>
-      </c>
+        <v>3.4015405178070068</v>
+      </c>
+      <c r="C163" s="2"/>
       <c r="D163" s="2">
-        <v>3.8048508167266846</v>
-      </c>
-      <c r="E163" s="2">
-        <v>3.7546029090881348</v>
-      </c>
+        <v>3.8042676448822021</v>
+      </c>
+      <c r="E163" s="2"/>
     </row>
     <row r="164">
       <c r="A164" s="1">
@@ -2016,15 +1788,11 @@
       <c r="B164" s="2">
         <v>3.4966666698455811</v>
       </c>
-      <c r="C164" s="2">
-        <v>3.4449207782745361</v>
-      </c>
+      <c r="C164" s="2"/>
       <c r="D164" s="2">
-        <v>3.8857729434967041</v>
-      </c>
-      <c r="E164" s="2">
-        <v>3.8197100162506104</v>
-      </c>
+        <v>3.8851900100708008</v>
+      </c>
+      <c r="E164" s="2"/>
     </row>
     <row r="165">
       <c r="A165" s="1">
@@ -2033,15 +1801,11 @@
       <c r="B165" s="2">
         <v>3.5298976898193359</v>
       </c>
-      <c r="C165" s="2">
-        <v>3.5524821281433105</v>
-      </c>
+      <c r="C165" s="2"/>
       <c r="D165" s="2">
-        <v>3.8797805309295654</v>
-      </c>
-      <c r="E165" s="2">
-        <v>3.8225507736206055</v>
-      </c>
+        <v>3.879197359085083</v>
+      </c>
+      <c r="E165" s="2"/>
     </row>
     <row r="166">
       <c r="A166" s="1">
@@ -2050,15 +1814,11 @@
       <c r="B166" s="2">
         <v>3.6476085186004639</v>
       </c>
-      <c r="C166" s="2">
-        <v>3.6014931201934814</v>
-      </c>
+      <c r="C166" s="2"/>
       <c r="D166" s="2">
-        <v>3.8594353199005127</v>
-      </c>
-      <c r="E166" s="2">
-        <v>3.8074402809143066</v>
-      </c>
+        <v>3.8588523864746094</v>
+      </c>
+      <c r="E166" s="2"/>
     </row>
     <row r="167">
       <c r="A167" s="1">
@@ -2067,15 +1827,11 @@
       <c r="B167" s="2">
         <v>4.3227953910827637</v>
       </c>
-      <c r="C167" s="2">
-        <v>4.1534867286682129</v>
-      </c>
+      <c r="C167" s="2"/>
       <c r="D167" s="2">
-        <v>3.8741469383239746</v>
-      </c>
-      <c r="E167" s="2">
-        <v>3.8403887748718262</v>
-      </c>
+        <v>3.8735637664794922</v>
+      </c>
+      <c r="E167" s="2"/>
     </row>
     <row r="168">
       <c r="A168" s="1">
@@ -2084,15 +1840,11 @@
       <c r="B168" s="2">
         <v>4.5388855934143066</v>
       </c>
-      <c r="C168" s="2">
-        <v>4.3580155372619629</v>
-      </c>
+      <c r="C168" s="2"/>
       <c r="D168" s="2">
         <v>3.9207284450531006</v>
       </c>
-      <c r="E168" s="2">
-        <v>3.8815019130706787</v>
-      </c>
+      <c r="E168" s="2"/>
     </row>
     <row r="169">
       <c r="A169" s="1">
@@ -2101,15 +1853,11 @@
       <c r="B169" s="2">
         <v>3.9859380722045898</v>
       </c>
-      <c r="C169" s="2">
-        <v>3.960033655166626</v>
-      </c>
+      <c r="C169" s="2"/>
       <c r="D169" s="2">
         <v>4.0254907608032227</v>
       </c>
-      <c r="E169" s="2">
-        <v>3.9515330791473389</v>
-      </c>
+      <c r="E169" s="2"/>
     </row>
     <row r="170">
       <c r="A170" s="1">
@@ -2118,15 +1866,11 @@
       <c r="B170" s="2">
         <v>3.918931245803833</v>
       </c>
-      <c r="C170" s="2">
-        <v>3.9213571548461914</v>
-      </c>
+      <c r="C170" s="2"/>
       <c r="D170" s="2">
         <v>4.0412383079528809</v>
       </c>
-      <c r="E170" s="2">
-        <v>3.952751636505127</v>
-      </c>
+      <c r="E170" s="2"/>
     </row>
     <row r="171">
       <c r="A171" s="1">
@@ -2135,15 +1879,11 @@
       <c r="B171" s="2">
         <v>4.0198111534118652</v>
       </c>
-      <c r="C171" s="2">
-        <v>4.1156549453735352</v>
-      </c>
+      <c r="C171" s="2"/>
       <c r="D171" s="2">
         <v>4.0694746971130371</v>
       </c>
-      <c r="E171" s="2">
-        <v>3.9795844554901123</v>
-      </c>
+      <c r="E171" s="2"/>
     </row>
     <row r="172">
       <c r="A172" s="1">
@@ -2152,15 +1892,11 @@
       <c r="B172" s="2">
         <v>3.8260209560394287</v>
       </c>
-      <c r="C172" s="2">
-        <v>3.8260729312896729</v>
-      </c>
+      <c r="C172" s="2"/>
       <c r="D172" s="2">
         <v>4.0094428062438965</v>
       </c>
-      <c r="E172" s="2">
-        <v>3.9402670860290527</v>
-      </c>
+      <c r="E172" s="2"/>
     </row>
     <row r="173">
       <c r="A173" s="1">
@@ -2169,15 +1905,11 @@
       <c r="B173" s="2">
         <v>4.4395270347595215</v>
       </c>
-      <c r="C173" s="2">
-        <v>4.0752005577087402</v>
-      </c>
+      <c r="C173" s="2"/>
       <c r="D173" s="2">
         <v>3.9834260940551758</v>
       </c>
-      <c r="E173" s="2">
-        <v>3.9421195983886719</v>
-      </c>
+      <c r="E173" s="2"/>
     </row>
     <row r="174">
       <c r="A174" s="1">
@@ -2186,15 +1918,11 @@
       <c r="B174" s="2">
         <v>3.6716256141662598</v>
       </c>
-      <c r="C174" s="2">
-        <v>3.5634500980377197</v>
-      </c>
+      <c r="C174" s="2"/>
       <c r="D174" s="2">
         <v>3.9549510478973389</v>
       </c>
-      <c r="E174" s="2">
-        <v>3.9080941677093506</v>
-      </c>
+      <c r="E174" s="2"/>
     </row>
     <row r="175">
       <c r="A175" s="1">
@@ -2203,15 +1931,11 @@
       <c r="B175" s="2">
         <v>3.9017355442047119</v>
       </c>
-      <c r="C175" s="2">
-        <v>3.8429892063140869</v>
-      </c>
+      <c r="C175" s="2"/>
       <c r="D175" s="2">
         <v>3.9263350963592529</v>
       </c>
-      <c r="E175" s="2">
-        <v>3.8793210983276367</v>
-      </c>
+      <c r="E175" s="2"/>
     </row>
     <row r="176">
       <c r="A176" s="1">
@@ -2220,15 +1944,11 @@
       <c r="B176" s="2">
         <v>3.7825098037719727</v>
       </c>
-      <c r="C176" s="2">
-        <v>3.7996289730072021</v>
-      </c>
+      <c r="C176" s="2"/>
       <c r="D176" s="2">
         <v>3.9105796813964844</v>
       </c>
-      <c r="E176" s="2">
-        <v>3.8399636745452881</v>
-      </c>
+      <c r="E176" s="2"/>
     </row>
     <row r="177">
       <c r="A177" s="1">
@@ -2237,15 +1957,11 @@
       <c r="B177" s="2">
         <v>4.3047347068786621</v>
       </c>
-      <c r="C177" s="2">
-        <v>4.3746891021728516</v>
-      </c>
+      <c r="C177" s="2"/>
       <c r="D177" s="2">
         <v>3.8544960021972656</v>
       </c>
-      <c r="E177" s="2">
-        <v>3.7776343822479248</v>
-      </c>
+      <c r="E177" s="2"/>
     </row>
     <row r="178">
       <c r="A178" s="1">
@@ -2254,15 +1970,11 @@
       <c r="B178" s="2">
         <v>3.7296640872955322</v>
       </c>
-      <c r="C178" s="2">
-        <v>3.6538047790527344</v>
-      </c>
+      <c r="C178" s="2"/>
       <c r="D178" s="2">
         <v>3.8200070858001709</v>
       </c>
-      <c r="E178" s="2">
-        <v>3.7539300918579102</v>
-      </c>
+      <c r="E178" s="2"/>
     </row>
     <row r="179">
       <c r="A179" s="1">
@@ -2271,15 +1983,11 @@
       <c r="B179" s="2">
         <v>3.6613872051239014</v>
       </c>
-      <c r="C179" s="2">
-        <v>3.6623990535736084</v>
-      </c>
+      <c r="C179" s="2"/>
       <c r="D179" s="2">
         <v>3.7984433174133301</v>
       </c>
-      <c r="E179" s="2">
-        <v>3.7367379665374756</v>
-      </c>
+      <c r="E179" s="2"/>
     </row>
     <row r="180">
       <c r="A180" s="1">
@@ -2288,15 +1996,11 @@
       <c r="B180" s="2">
         <v>3.8780112266540527</v>
       </c>
-      <c r="C180" s="2">
-        <v>3.7614386081695557</v>
-      </c>
+      <c r="C180" s="2"/>
       <c r="D180" s="2">
         <v>3.7613801956176758</v>
       </c>
-      <c r="E180" s="2">
-        <v>3.7101540565490723</v>
-      </c>
+      <c r="E180" s="2"/>
     </row>
     <row r="181">
       <c r="A181" s="1">
@@ -2305,15 +2009,11 @@
       <c r="B181" s="2">
         <v>3.3212690353393555</v>
       </c>
-      <c r="C181" s="2">
-        <v>3.2651097774505615</v>
-      </c>
+      <c r="C181" s="2"/>
       <c r="D181" s="2">
         <v>3.7816169261932373</v>
       </c>
-      <c r="E181" s="2">
-        <v>3.7188172340393066</v>
-      </c>
+      <c r="E181" s="2"/>
     </row>
     <row r="182">
       <c r="A182" s="1">
@@ -2322,15 +2022,11 @@
       <c r="B182" s="2">
         <v>4.129127025604248</v>
       </c>
-      <c r="C182" s="2">
-        <v>3.8618621826171875</v>
-      </c>
+      <c r="C182" s="2"/>
       <c r="D182" s="2">
         <v>3.745964527130127</v>
       </c>
-      <c r="E182" s="2">
-        <v>3.6819205284118652</v>
-      </c>
+      <c r="E182" s="2"/>
     </row>
     <row r="183">
       <c r="A183" s="1">
@@ -2339,15 +2035,11 @@
       <c r="B183" s="2">
         <v>3.4775512218475342</v>
       </c>
-      <c r="C183" s="2">
-        <v>3.4087209701538086</v>
-      </c>
+      <c r="C183" s="2"/>
       <c r="D183" s="2">
         <v>3.7568225860595703</v>
       </c>
-      <c r="E183" s="2">
-        <v>3.6985948085784912</v>
-      </c>
+      <c r="E183" s="2"/>
     </row>
     <row r="184">
       <c r="A184" s="1">
@@ -2356,15 +2048,11 @@
       <c r="B184" s="2">
         <v>3.5681676864624023</v>
       </c>
-      <c r="C184" s="2">
-        <v>3.6037335395812988</v>
-      </c>
+      <c r="C184" s="2"/>
       <c r="D184" s="2">
         <v>3.7859220504760742</v>
       </c>
-      <c r="E184" s="2">
-        <v>3.6965148448944092</v>
-      </c>
+      <c r="E184" s="2"/>
     </row>
     <row r="185">
       <c r="A185" s="1">
@@ -2373,15 +2061,11 @@
       <c r="B185" s="2">
         <v>3.9646396636962891</v>
       </c>
-      <c r="C185" s="2">
-        <v>3.8775961399078369</v>
-      </c>
+      <c r="C185" s="2"/>
       <c r="D185" s="2">
         <v>3.804668664932251</v>
       </c>
-      <c r="E185" s="2">
-        <v>3.7189066410064697</v>
-      </c>
+      <c r="E185" s="2"/>
     </row>
     <row r="186">
       <c r="A186" s="1">
@@ -2390,15 +2074,11 @@
       <c r="B186" s="2">
         <v>3.9838638305664062</v>
       </c>
-      <c r="C186" s="2">
-        <v>4.0426201820373535</v>
-      </c>
+      <c r="C186" s="2"/>
       <c r="D186" s="2">
         <v>3.9430408477783203</v>
       </c>
-      <c r="E186" s="2">
-        <v>3.8571665287017822</v>
-      </c>
+      <c r="E186" s="2"/>
     </row>
     <row r="187">
       <c r="A187" s="1">
@@ -2407,15 +2087,11 @@
       <c r="B187" s="2">
         <v>3.8273870944976807</v>
       </c>
-      <c r="C187" s="2">
-        <v>3.8038735389709473</v>
-      </c>
+      <c r="C187" s="2"/>
       <c r="D187" s="2">
         <v>3.9191761016845703</v>
       </c>
-      <c r="E187" s="2">
-        <v>3.8485808372497559</v>
-      </c>
+      <c r="E187" s="2"/>
     </row>
     <row r="188">
       <c r="A188" s="1">
@@ -2424,15 +2100,11 @@
       <c r="B188" s="2">
         <v>3.9232823848724365</v>
       </c>
-      <c r="C188" s="2">
-        <v>3.643679141998291</v>
-      </c>
+      <c r="C188" s="2"/>
       <c r="D188" s="2">
         <v>3.9901235103607178</v>
       </c>
-      <c r="E188" s="2">
-        <v>3.9278454780578613</v>
-      </c>
+      <c r="E188" s="2"/>
     </row>
     <row r="189">
       <c r="A189" s="1">
@@ -2441,15 +2113,11 @@
       <c r="B189" s="2">
         <v>4.0467309951782227</v>
       </c>
-      <c r="C189" s="2">
-        <v>3.9629638195037842</v>
-      </c>
+      <c r="C189" s="2"/>
       <c r="D189" s="2">
         <v>4.0468387603759766</v>
       </c>
-      <c r="E189" s="2">
-        <v>3.9853482246398926</v>
-      </c>
+      <c r="E189" s="2"/>
     </row>
     <row r="190">
       <c r="A190" s="1">
@@ -2458,15 +2126,11 @@
       <c r="B190" s="2">
         <v>4.5666170120239258</v>
       </c>
-      <c r="C190" s="2">
-        <v>4.5094490051269531</v>
-      </c>
+      <c r="C190" s="2"/>
       <c r="D190" s="2">
         <v>3.960597038269043</v>
       </c>
-      <c r="E190" s="2">
-        <v>3.8915989398956299</v>
-      </c>
+      <c r="E190" s="2"/>
     </row>
     <row r="191">
       <c r="A191" s="1">
@@ -2475,15 +2139,11 @@
       <c r="B191" s="2">
         <v>3.9143457412719727</v>
       </c>
-      <c r="C191" s="2">
-        <v>3.7845911979675293</v>
-      </c>
+      <c r="C191" s="2"/>
       <c r="D191" s="2">
         <v>3.8566398620605469</v>
       </c>
-      <c r="E191" s="2">
-        <v>3.7840530872344971</v>
-      </c>
+      <c r="E191" s="2"/>
     </row>
     <row r="192">
       <c r="A192" s="1">
@@ -2492,15 +2152,11 @@
       <c r="B192" s="2">
         <v>4.1160769462585449</v>
       </c>
-      <c r="C192" s="2">
-        <v>4.1221022605895996</v>
-      </c>
+      <c r="C192" s="2"/>
       <c r="D192" s="2">
         <v>3.8897714614868164</v>
       </c>
-      <c r="E192" s="2">
-        <v>3.8118948936462402</v>
-      </c>
+      <c r="E192" s="2"/>
     </row>
     <row r="193">
       <c r="A193" s="1">
@@ -2509,15 +2165,11 @@
       <c r="B193" s="2">
         <v>4.0786056518554688</v>
       </c>
-      <c r="C193" s="2">
-        <v>4.1212577819824219</v>
-      </c>
+      <c r="C193" s="2"/>
       <c r="D193" s="2">
         <v>3.8120527267456055</v>
       </c>
-      <c r="E193" s="2">
-        <v>3.7749643325805664</v>
-      </c>
+      <c r="E193" s="2"/>
     </row>
     <row r="194">
       <c r="A194" s="1">
@@ -2526,15 +2178,11 @@
       <c r="B194" s="2">
         <v>3.1884627342224121</v>
       </c>
-      <c r="C194" s="2">
-        <v>3.0338528156280518</v>
-      </c>
+      <c r="C194" s="2"/>
       <c r="D194" s="2">
         <v>3.7646775245666504</v>
       </c>
-      <c r="E194" s="2">
-        <v>3.7207996845245361</v>
-      </c>
+      <c r="E194" s="2"/>
     </row>
     <row r="195">
       <c r="A195" s="1">
@@ -2543,15 +2191,11 @@
       <c r="B195" s="2">
         <v>3.0482499599456787</v>
       </c>
-      <c r="C195" s="2">
-        <v>3.0747084617614746</v>
-      </c>
+      <c r="C195" s="2"/>
       <c r="D195" s="2">
         <v>3.6284298896789551</v>
       </c>
-      <c r="E195" s="2">
-        <v>3.5928275585174561</v>
-      </c>
+      <c r="E195" s="2"/>
     </row>
     <row r="196">
       <c r="A196" s="1">
@@ -2560,15 +2204,11 @@
       <c r="B196" s="2">
         <v>4.1255717277526855</v>
       </c>
-      <c r="C196" s="2">
-        <v>4.0544490814208984</v>
-      </c>
+      <c r="C196" s="2"/>
       <c r="D196" s="2">
         <v>3.6339685916900635</v>
       </c>
-      <c r="E196" s="2">
-        <v>3.6044244766235352</v>
-      </c>
+      <c r="E196" s="2"/>
     </row>
     <row r="197">
       <c r="A197" s="1">
@@ -2577,15 +2217,11 @@
       <c r="B197" s="2">
         <v>3.2238137722015381</v>
       </c>
-      <c r="C197" s="2">
-        <v>3.311305046081543</v>
-      </c>
+      <c r="C197" s="2"/>
       <c r="D197" s="2">
         <v>3.5637655258178711</v>
       </c>
-      <c r="E197" s="2">
-        <v>3.5312325954437256</v>
-      </c>
+      <c r="E197" s="2"/>
     </row>
     <row r="198">
       <c r="A198" s="1">
@@ -2594,15 +2230,11 @@
       <c r="B198" s="2">
         <v>3.6203534603118896</v>
       </c>
-      <c r="C198" s="2">
-        <v>3.4754805564880371</v>
-      </c>
+      <c r="C198" s="2"/>
       <c r="D198" s="2">
         <v>3.4463129043579102</v>
       </c>
-      <c r="E198" s="2">
-        <v>3.3973376750946045</v>
-      </c>
+      <c r="E198" s="2"/>
     </row>
     <row r="199">
       <c r="A199" s="1">
@@ -2611,15 +2243,11 @@
       <c r="B199" s="2">
         <v>3.3403892517089844</v>
       </c>
-      <c r="C199" s="2">
-        <v>3.3577008247375488</v>
-      </c>
+      <c r="C199" s="2"/>
       <c r="D199" s="2">
         <v>3.4527311325073242</v>
       </c>
-      <c r="E199" s="2">
-        <v>3.4211220741271973</v>
-      </c>
+      <c r="E199" s="2"/>
     </row>
     <row r="200">
       <c r="A200" s="1">
@@ -2628,15 +2256,11 @@
       <c r="B200" s="2">
         <v>3.9641928672790527</v>
       </c>
-      <c r="C200" s="2">
-        <v>3.8889634609222412</v>
-      </c>
+      <c r="C200" s="2"/>
       <c r="D200" s="2">
         <v>3.5121605396270752</v>
       </c>
-      <c r="E200" s="2">
-        <v>3.4819412231445312</v>
-      </c>
+      <c r="E200" s="2"/>
     </row>
     <row r="201">
       <c r="A201" s="1">
@@ -2645,15 +2269,11 @@
       <c r="B201" s="2">
         <v>3.4842512607574463</v>
       </c>
-      <c r="C201" s="2">
-        <v>3.4633758068084717</v>
-      </c>
+      <c r="C201" s="2"/>
       <c r="D201" s="2">
         <v>3.3905034065246582</v>
       </c>
-      <c r="E201" s="2">
-        <v>3.3647823333740234</v>
-      </c>
+      <c r="E201" s="2"/>
     </row>
     <row r="202">
       <c r="A202" s="1">
@@ -2662,15 +2282,11 @@
       <c r="B202" s="2">
         <v>3.0215303897857666</v>
       </c>
-      <c r="C202" s="2">
-        <v>2.9162030220031738</v>
-      </c>
+      <c r="C202" s="2"/>
       <c r="D202" s="2">
         <v>3.4051318168640137</v>
       </c>
-      <c r="E202" s="2">
-        <v>3.3596217632293701</v>
-      </c>
+      <c r="E202" s="2"/>
     </row>
     <row r="203">
       <c r="A203" s="1">
@@ -2679,15 +2295,11 @@
       <c r="B203" s="2">
         <v>3.2462267875671387</v>
       </c>
-      <c r="C203" s="2">
-        <v>3.2479133605957031</v>
-      </c>
+      <c r="C203" s="2"/>
       <c r="D203" s="2">
         <v>3.3391690254211426</v>
       </c>
-      <c r="E203" s="2">
-        <v>3.3101809024810791</v>
-      </c>
+      <c r="E203" s="2"/>
     </row>
     <row r="204">
       <c r="A204" s="1">
@@ -2696,15 +2308,11 @@
       <c r="B204" s="2">
         <v>3.5831162929534912</v>
       </c>
-      <c r="C204" s="2">
-        <v>3.6220803260803223</v>
-      </c>
+      <c r="C204" s="2"/>
       <c r="D204" s="2">
         <v>3.3376224040985107</v>
       </c>
-      <c r="E204" s="2">
-        <v>3.292471170425415</v>
-      </c>
+      <c r="E204" s="2"/>
     </row>
     <row r="205">
       <c r="A205" s="1">
@@ -2713,15 +2321,11 @@
       <c r="B205" s="2">
         <v>3.0306565761566162</v>
       </c>
-      <c r="C205" s="2">
-        <v>3.000018835067749</v>
-      </c>
+      <c r="C205" s="2"/>
       <c r="D205" s="2">
         <v>3.2475378513336182</v>
       </c>
-      <c r="E205" s="2">
-        <v>3.1999096870422363</v>
-      </c>
+      <c r="E205" s="2"/>
     </row>
     <row r="206">
       <c r="A206" s="1">
@@ -2730,15 +2334,11 @@
       <c r="B206" s="2">
         <v>3.3554694652557373</v>
       </c>
-      <c r="C206" s="2">
-        <v>3.2648603916168213</v>
-      </c>
+      <c r="C206" s="2"/>
       <c r="D206" s="2">
         <v>3.167449951171875</v>
       </c>
-      <c r="E206" s="2">
-        <v>3.0970497131347656</v>
-      </c>
+      <c r="E206" s="2"/>
     </row>
     <row r="207">
       <c r="A207" s="1">
@@ -2747,15 +2347,11 @@
       <c r="B207" s="2">
         <v>3.0266876220703125</v>
       </c>
-      <c r="C207" s="2">
-        <v>3.0305116176605225</v>
-      </c>
+      <c r="C207" s="2"/>
       <c r="D207" s="2">
         <v>3.191051721572876</v>
       </c>
-      <c r="E207" s="2">
-        <v>3.130326509475708</v>
-      </c>
+      <c r="E207" s="2"/>
     </row>
     <row r="208">
       <c r="A208" s="1">
@@ -2764,15 +2360,11 @@
       <c r="B208" s="2">
         <v>3.326469898223877</v>
       </c>
-      <c r="C208" s="2">
-        <v>3.1983132362365723</v>
-      </c>
+      <c r="C208" s="2"/>
       <c r="D208" s="2">
         <v>3.1807165145874023</v>
       </c>
-      <c r="E208" s="2">
-        <v>3.1259293556213379</v>
-      </c>
+      <c r="E208" s="2"/>
     </row>
     <row r="209">
       <c r="A209" s="1">
@@ -2781,15 +2373,11 @@
       <c r="B209" s="2">
         <v>3.1534333229064941</v>
       </c>
-      <c r="C209" s="2">
-        <v>3.055910587310791</v>
-      </c>
+      <c r="C209" s="2"/>
       <c r="D209" s="2">
         <v>3.1588447093963623</v>
       </c>
-      <c r="E209" s="2">
-        <v>3.0959484577178955</v>
-      </c>
+      <c r="E209" s="2"/>
     </row>
     <row r="210">
       <c r="A210" s="1">
@@ -2798,15 +2386,11 @@
       <c r="B210" s="2">
         <v>2.7634584903717041</v>
       </c>
-      <c r="C210" s="2">
-        <v>2.5376360416412354</v>
-      </c>
+      <c r="C210" s="2"/>
       <c r="D210" s="2">
         <v>3.1920223236083984</v>
       </c>
-      <c r="E210" s="2">
-        <v>3.1320004463195801</v>
-      </c>
+      <c r="E210" s="2"/>
     </row>
     <row r="211">
       <c r="A211" s="1">
@@ -2815,15 +2399,11 @@
       <c r="B211" s="2">
         <v>3.2339470386505127</v>
       </c>
-      <c r="C211" s="2">
-        <v>3.2156949043273926</v>
-      </c>
+      <c r="C211" s="2"/>
       <c r="D211" s="2">
         <v>3.1167340278625488</v>
       </c>
-      <c r="E211" s="2">
-        <v>3.0676453113555908</v>
-      </c>
+      <c r="E211" s="2"/>
     </row>
     <row r="212">
       <c r="A212" s="1">
@@ -2832,15 +2412,11 @@
       <c r="B212" s="2">
         <v>3.1532101631164551</v>
       </c>
-      <c r="C212" s="2">
-        <v>3.208338737487793</v>
-      </c>
+      <c r="C212" s="2"/>
       <c r="D212" s="2">
         <v>3.1478762626647949</v>
       </c>
-      <c r="E212" s="2">
-        <v>3.0692763328552246</v>
-      </c>
+      <c r="E212" s="2"/>
     </row>
     <row r="213">
       <c r="A213" s="1">
@@ -2849,15 +2425,11 @@
       <c r="B213" s="2">
         <v>3.3862698078155518</v>
       </c>
-      <c r="C213" s="2">
-        <v>3.3522517681121826</v>
-      </c>
+      <c r="C213" s="2"/>
       <c r="D213" s="2">
         <v>3.1121904850006104</v>
       </c>
-      <c r="E213" s="2">
-        <v>3.0231037139892578</v>
-      </c>
+      <c r="E213" s="2"/>
     </row>
     <row r="214">
       <c r="A214" s="1">
@@ -2866,15 +2438,11 @@
       <c r="B214" s="2">
         <v>3.3292543888092041</v>
       </c>
-      <c r="C214" s="2">
-        <v>3.3244874477386475</v>
-      </c>
+      <c r="C214" s="2"/>
       <c r="D214" s="2">
         <v>3.1172163486480713</v>
       </c>
-      <c r="E214" s="2">
-        <v>3.0228631496429443</v>
-      </c>
+      <c r="E214" s="2"/>
     </row>
     <row r="215">
       <c r="A215" s="1">
@@ -2883,15 +2451,11 @@
       <c r="B215" s="2">
         <v>2.6778759956359863</v>
       </c>
-      <c r="C215" s="2">
-        <v>2.6856634616851807</v>
-      </c>
+      <c r="C215" s="2"/>
       <c r="D215" s="2">
         <v>3.1227946281433105</v>
       </c>
-      <c r="E215" s="2">
-        <v>3.0161299705505371</v>
-      </c>
+      <c r="E215" s="2"/>
     </row>
     <row r="216">
       <c r="A216" s="1">
@@ -2900,15 +2464,11 @@
       <c r="B216" s="2">
         <v>3.3069674968719482</v>
       </c>
-      <c r="C216" s="2">
-        <v>3.0451905727386475</v>
-      </c>
+      <c r="C216" s="2"/>
       <c r="D216" s="2">
         <v>3.1679747104644775</v>
       </c>
-      <c r="E216" s="2">
-        <v>3.048954963684082</v>
-      </c>
+      <c r="E216" s="2"/>
     </row>
     <row r="217">
       <c r="A217" s="1">
@@ -2917,15 +2477,11 @@
       <c r="B217" s="2">
         <v>3.0052967071533203</v>
       </c>
-      <c r="C217" s="2">
-        <v>2.7827606201171875</v>
-      </c>
+      <c r="C217" s="2"/>
       <c r="D217" s="2">
         <v>3.1287002563476562</v>
       </c>
-      <c r="E217" s="2">
-        <v>2.9630985260009766</v>
-      </c>
+      <c r="E217" s="2"/>
     </row>
     <row r="218">
       <c r="A218" s="1">
@@ -2934,15 +2490,11 @@
       <c r="B218" s="2">
         <v>3.1986663341522217</v>
       </c>
-      <c r="C218" s="2">
-        <v>3.0537452697753906</v>
-      </c>
+      <c r="C218" s="2"/>
       <c r="D218" s="2">
         <v>3.1426537036895752</v>
       </c>
-      <c r="E218" s="2">
-        <v>2.9750850200653076</v>
-      </c>
+      <c r="E218" s="2"/>
     </row>
     <row r="219">
       <c r="A219" s="1">
@@ -2951,15 +2503,11 @@
       <c r="B219" s="2">
         <v>2.8136639595031738</v>
       </c>
-      <c r="C219" s="2">
-        <v>2.4770379066467285</v>
-      </c>
+      <c r="C219" s="2"/>
       <c r="D219" s="2">
         <v>3.13094162940979</v>
       </c>
-      <c r="E219" s="2">
-        <v>2.932873010635376</v>
-      </c>
+      <c r="E219" s="2"/>
     </row>
     <row r="220">
       <c r="A220" s="1">
@@ -2968,15 +2516,11 @@
       <c r="B220" s="2">
         <v>3.6405684947967529</v>
       </c>
-      <c r="C220" s="2">
-        <v>3.5111198425292969</v>
-      </c>
+      <c r="C220" s="2"/>
       <c r="D220" s="2">
         <v>3.2145609855651855</v>
       </c>
-      <c r="E220" s="2">
-        <v>3.0229892730712891</v>
-      </c>
+      <c r="E220" s="2"/>
     </row>
     <row r="221">
       <c r="A221" s="1">
@@ -2985,15 +2529,11 @@
       <c r="B221" s="2">
         <v>2.7997400760650635</v>
       </c>
-      <c r="C221" s="2">
-        <v>2.4356307983398438</v>
-      </c>
+      <c r="C221" s="2"/>
       <c r="D221" s="2">
         <v>3.1816213130950928</v>
       </c>
-      <c r="E221" s="2">
-        <v>3.0206804275512695</v>
-      </c>
+      <c r="E221" s="2"/>
     </row>
     <row r="222">
       <c r="A222" s="1">
@@ -3002,15 +2542,11 @@
       <c r="B222" s="2">
         <v>3.5118489265441895</v>
       </c>
-      <c r="C222" s="2">
-        <v>3.4601297378540039</v>
-      </c>
+      <c r="C222" s="2"/>
       <c r="D222" s="2">
         <v>3.1948869228363037</v>
       </c>
-      <c r="E222" s="2">
-        <v>3.0676991939544678</v>
-      </c>
+      <c r="E222" s="2"/>
     </row>
     <row r="223">
       <c r="A223" s="1">
@@ -3019,15 +2555,11 @@
       <c r="B223" s="2">
         <v>3.223846435546875</v>
       </c>
-      <c r="C223" s="2">
-        <v>2.9445793628692627</v>
-      </c>
+      <c r="C223" s="2"/>
       <c r="D223" s="2">
         <v>3.2163012027740479</v>
       </c>
-      <c r="E223" s="2">
-        <v>3.103801965713501</v>
-      </c>
+      <c r="E223" s="2"/>
     </row>
     <row r="224">
       <c r="A224" s="1">
@@ -3036,15 +2568,11 @@
       <c r="B224" s="2">
         <v>3.430450439453125</v>
       </c>
-      <c r="C224" s="2">
-        <v>3.4967093467712402</v>
-      </c>
+      <c r="C224" s="2"/>
       <c r="D224" s="2">
         <v>3.2372779846191406</v>
       </c>
-      <c r="E224" s="2">
-        <v>3.1648876667022705</v>
-      </c>
+      <c r="E224" s="2"/>
     </row>
     <row r="225">
       <c r="A225" s="1">
@@ -3053,15 +2581,11 @@
       <c r="B225" s="2">
         <v>3.0105109214782715</v>
       </c>
-      <c r="C225" s="2">
-        <v>3.0244102478027344</v>
-      </c>
+      <c r="C225" s="2"/>
       <c r="D225" s="2">
         <v>3.127838134765625</v>
       </c>
-      <c r="E225" s="2">
-        <v>3.0731575489044189</v>
-      </c>
+      <c r="E225" s="2"/>
     </row>
     <row r="226">
       <c r="A226" s="1">
@@ -3070,15 +2594,11 @@
       <c r="B226" s="2">
         <v>3.1246864795684814</v>
       </c>
-      <c r="C226" s="2">
-        <v>3.2059304714202881</v>
-      </c>
+      <c r="C226" s="2"/>
       <c r="D226" s="2">
         <v>3.1378114223480225</v>
       </c>
-      <c r="E226" s="2">
-        <v>3.1016144752502441</v>
-      </c>
+      <c r="E226" s="2"/>
     </row>
     <row r="227">
       <c r="A227" s="1">
@@ -3087,15 +2607,11 @@
       <c r="B227" s="2">
         <v>3.3913955688476562</v>
       </c>
-      <c r="C227" s="2">
-        <v>3.378669261932373</v>
-      </c>
+      <c r="C227" s="2"/>
       <c r="D227" s="2">
         <v>3.0965931415557861</v>
       </c>
-      <c r="E227" s="2">
-        <v>3.0580005645751953</v>
-      </c>
+      <c r="E227" s="2"/>
     </row>
     <row r="228">
       <c r="A228" s="1">
@@ -3104,15 +2620,11 @@
       <c r="B228" s="2">
         <v>3.0024549961090088</v>
       </c>
-      <c r="C228" s="2">
-        <v>3.026810884475708</v>
-      </c>
+      <c r="C228" s="2"/>
       <c r="D228" s="2">
         <v>3.0485906600952148</v>
       </c>
-      <c r="E228" s="2">
-        <v>3.0178759098052979</v>
-      </c>
+      <c r="E228" s="2"/>
     </row>
     <row r="229">
       <c r="A229" s="1">
@@ -3121,15 +2633,11 @@
       <c r="B229" s="2">
         <v>2.6556093692779541</v>
       </c>
-      <c r="C229" s="2">
-        <v>2.685546875</v>
-      </c>
+      <c r="C229" s="2"/>
       <c r="D229" s="2">
         <v>2.9838063716888428</v>
       </c>
-      <c r="E229" s="2">
-        <v>2.9253203868865967</v>
-      </c>
+      <c r="E229" s="2"/>
     </row>
     <row r="230">
       <c r="A230" s="1">
@@ -3138,15 +2646,11 @@
       <c r="B230" s="2">
         <v>2.8895001411437988</v>
       </c>
-      <c r="C230" s="2">
-        <v>2.6917448043823242</v>
-      </c>
+      <c r="C230" s="2"/>
       <c r="D230" s="2">
         <v>2.9771034717559814</v>
       </c>
-      <c r="E230" s="2">
-        <v>2.9021010398864746</v>
-      </c>
+      <c r="E230" s="2"/>
     </row>
     <row r="231">
       <c r="A231" s="1">
@@ -3155,15 +2659,11 @@
       <c r="B231" s="2">
         <v>3.1408829689025879</v>
       </c>
-      <c r="C231" s="2">
-        <v>3.0676031112670898</v>
-      </c>
+      <c r="C231" s="2"/>
       <c r="D231" s="2">
         <v>2.9764928817749023</v>
       </c>
-      <c r="E231" s="2">
-        <v>2.9053127765655518</v>
-      </c>
+      <c r="E231" s="2"/>
     </row>
     <row r="232">
       <c r="A232" s="1">
@@ -3172,15 +2672,11 @@
       <c r="B232" s="2">
         <v>2.7918250560760498</v>
       </c>
-      <c r="C232" s="2">
-        <v>2.583458423614502</v>
-      </c>
+      <c r="C232" s="2"/>
       <c r="D232" s="2">
         <v>2.9911315441131592</v>
       </c>
-      <c r="E232" s="2">
-        <v>2.9184854030609131</v>
-      </c>
+      <c r="E232" s="2"/>
     </row>
     <row r="233">
       <c r="A233" s="1">
@@ -3189,15 +2685,11 @@
       <c r="B233" s="2">
         <v>2.8473913669586182</v>
       </c>
-      <c r="C233" s="2">
-        <v>2.6637084484100342</v>
-      </c>
+      <c r="C233" s="2"/>
       <c r="D233" s="2">
         <v>3.0460283756256104</v>
       </c>
-      <c r="E233" s="2">
-        <v>2.9639818668365479</v>
-      </c>
+      <c r="E233" s="2"/>
     </row>
     <row r="234">
       <c r="A234" s="1">
@@ -3206,15 +2698,11 @@
       <c r="B234" s="2">
         <v>2.9501862525939941</v>
       </c>
-      <c r="C234" s="2">
-        <v>2.815436840057373</v>
-      </c>
+      <c r="C234" s="2"/>
       <c r="D234" s="2">
         <v>3.0399088859558105</v>
       </c>
-      <c r="E234" s="2">
-        <v>2.9554574489593506</v>
-      </c>
+      <c r="E234" s="2"/>
     </row>
     <row r="235">
       <c r="A235" s="1">
@@ -3223,15 +2711,11 @@
       <c r="B235" s="2">
         <v>3.1191895008087158</v>
       </c>
-      <c r="C235" s="2">
-        <v>3.2348361015319824</v>
-      </c>
+      <c r="C235" s="2"/>
       <c r="D235" s="2">
         <v>3.1280696392059326</v>
       </c>
-      <c r="E235" s="2">
-        <v>3.0749678611755371</v>
-      </c>
+      <c r="E235" s="2"/>
     </row>
     <row r="236">
       <c r="A236" s="1">
@@ -3240,15 +2724,11 @@
       <c r="B236" s="2">
         <v>3.5231449604034424</v>
       </c>
-      <c r="C236" s="2">
-        <v>3.4972226619720459</v>
-      </c>
+      <c r="C236" s="2"/>
       <c r="D236" s="2">
         <v>3.1685526371002197</v>
       </c>
-      <c r="E236" s="2">
-        <v>3.1333737373352051</v>
-      </c>
+      <c r="E236" s="2"/>
     </row>
     <row r="237">
       <c r="A237" s="1">
@@ -3257,15 +2737,11 @@
       <c r="B237" s="2">
         <v>3.4965260028839111</v>
       </c>
-      <c r="C237" s="2">
-        <v>3.4362800121307373</v>
-      </c>
+      <c r="C237" s="2"/>
       <c r="D237" s="2">
         <v>3.2153244018554688</v>
       </c>
-      <c r="E237" s="2">
-        <v>3.1773438453674316</v>
-      </c>
+      <c r="E237" s="2"/>
     </row>
     <row r="238">
       <c r="A238" s="1">
@@ -3274,15 +2750,11 @@
       <c r="B238" s="2">
         <v>2.6005332469940186</v>
       </c>
-      <c r="C238" s="2">
-        <v>2.6088259220123291</v>
-      </c>
+      <c r="C238" s="2"/>
       <c r="D238" s="2">
         <v>3.2169513702392578</v>
       </c>
-      <c r="E238" s="2">
-        <v>3.2058992385864258</v>
-      </c>
+      <c r="E238" s="2"/>
     </row>
     <row r="239">
       <c r="A239" s="1">
@@ -3291,15 +2763,11 @@
       <c r="B239" s="2">
         <v>3.6829466819763184</v>
       </c>
-      <c r="C239" s="2">
-        <v>3.7673385143280029</v>
-      </c>
+      <c r="C239" s="2"/>
       <c r="D239" s="2">
         <v>3.1889281272888184</v>
       </c>
-      <c r="E239" s="2">
-        <v>3.1941487789154053</v>
-      </c>
+      <c r="E239" s="2"/>
     </row>
     <row r="240">
       <c r="A240" s="1">
@@ -3308,15 +2776,11 @@
       <c r="B240" s="2">
         <v>3.505230188369751</v>
       </c>
-      <c r="C240" s="2">
-        <v>3.5932571887969971</v>
-      </c>
+      <c r="C240" s="2"/>
       <c r="D240" s="2">
         <v>3.2115790843963623</v>
       </c>
-      <c r="E240" s="2">
-        <v>3.1892988681793213</v>
-      </c>
+      <c r="E240" s="2"/>
     </row>
     <row r="241">
       <c r="A241" s="1">
@@ -3325,15 +2789,11 @@
       <c r="B241" s="2">
         <v>3.2127711772918701</v>
       </c>
-      <c r="C241" s="2">
-        <v>2.9791884422302246</v>
-      </c>
+      <c r="C241" s="2"/>
       <c r="D241" s="2">
         <v>3.0848937034606934</v>
       </c>
-      <c r="E241" s="2">
-        <v>3.0722718238830566</v>
-      </c>
+      <c r="E241" s="2"/>
     </row>
     <row r="242">
       <c r="A242" s="1">
@@ -3342,15 +2802,11 @@
       <c r="B242" s="2">
         <v>2.8620338439941406</v>
       </c>
-      <c r="C242" s="2">
-        <v>2.9207065105438232</v>
-      </c>
+      <c r="C242" s="2"/>
       <c r="D242" s="2">
         <v>3.0242416858673096</v>
       </c>
-      <c r="E242" s="2">
-        <v>3.008746862411499</v>
-      </c>
+      <c r="E242" s="2"/>
     </row>
     <row r="243">
       <c r="A243" s="1">
@@ -3359,15 +2815,11 @@
       <c r="B243" s="2">
         <v>2.6979777812957764</v>
       </c>
-      <c r="C243" s="2">
-        <v>2.7096827030181885</v>
-      </c>
+      <c r="C243" s="2"/>
       <c r="D243" s="2">
         <v>3.0114040374755859</v>
       </c>
-      <c r="E243" s="2">
-        <v>2.9876058101654053</v>
-      </c>
+      <c r="E243" s="2"/>
     </row>
     <row r="244">
       <c r="A244" s="1">
@@ -3376,15 +2828,11 @@
       <c r="B244" s="2">
         <v>3.3230476379394531</v>
       </c>
-      <c r="C244" s="2">
-        <v>3.191187858581543</v>
-      </c>
+      <c r="C244" s="2"/>
       <c r="D244" s="2">
         <v>2.8580513000488281</v>
       </c>
-      <c r="E244" s="2">
-        <v>2.8312220573425293</v>
-      </c>
+      <c r="E244" s="2"/>
     </row>
     <row r="245">
       <c r="A245" s="1">
@@ -3393,15 +2841,11 @@
       <c r="B245" s="2">
         <v>2.3829770088195801</v>
       </c>
-      <c r="C245" s="2">
-        <v>2.4439785480499268</v>
-      </c>
+      <c r="C245" s="2"/>
       <c r="D245" s="2">
         <v>2.7454192638397217</v>
       </c>
-      <c r="E245" s="2">
-        <v>2.6989505290985107</v>
-      </c>
+      <c r="E245" s="2"/>
     </row>
     <row r="246">
       <c r="A246" s="1">
@@ -3410,15 +2854,11 @@
       <c r="B246" s="2">
         <v>2.9506573677062988</v>
       </c>
-      <c r="C246" s="2">
-        <v>2.8645555973052979</v>
-      </c>
+      <c r="C246" s="2"/>
       <c r="D246" s="2">
         <v>2.7061033248901367</v>
       </c>
-      <c r="E246" s="2">
-        <v>2.6683933734893799</v>
-      </c>
+      <c r="E246" s="2"/>
     </row>
     <row r="247">
       <c r="A247" s="1">
@@ -3427,15 +2867,11 @@
       <c r="B247" s="2">
         <v>2.4849939346313477</v>
       </c>
-      <c r="C247" s="2">
-        <v>2.4185571670532227</v>
-      </c>
+      <c r="C247" s="2"/>
       <c r="D247" s="2">
         <v>2.6917681694030762</v>
       </c>
-      <c r="E247" s="2">
-        <v>2.631028413772583</v>
-      </c>
+      <c r="E247" s="2"/>
     </row>
     <row r="248">
       <c r="A248" s="1">
@@ -3444,15 +2880,11 @@
       <c r="B248" s="2">
         <v>2.302772045135498</v>
       </c>
-      <c r="C248" s="2">
-        <v>2.3598852157592773</v>
-      </c>
+      <c r="C248" s="2"/>
       <c r="D248" s="2">
         <v>2.7224681377410889</v>
       </c>
-      <c r="E248" s="2">
-        <v>2.6654479503631592</v>
-      </c>
+      <c r="E248" s="2"/>
     </row>
     <row r="249">
       <c r="A249" s="1">
@@ -3461,15 +2893,11 @@
       <c r="B249" s="2">
         <v>2.4915425777435303</v>
       </c>
-      <c r="C249" s="2">
-        <v>2.4028129577636719</v>
-      </c>
+      <c r="C249" s="2"/>
       <c r="D249" s="2">
         <v>2.6708219051361084</v>
       </c>
-      <c r="E249" s="2">
-        <v>2.6052587032318115</v>
-      </c>
+      <c r="E249" s="2"/>
     </row>
     <row r="250">
       <c r="A250" s="1">
@@ -3478,15 +2906,11 @@
       <c r="B250" s="2">
         <v>2.8589277267456055</v>
       </c>
-      <c r="C250" s="2">
-        <v>2.7041740417480469</v>
-      </c>
+      <c r="C250" s="2"/>
       <c r="D250" s="2">
         <v>2.7147762775421143</v>
       </c>
-      <c r="E250" s="2">
-        <v>2.6387374401092529</v>
-      </c>
+      <c r="E250" s="2"/>
     </row>
     <row r="251">
       <c r="A251" s="1">
@@ -3495,15 +2919,11 @@
       <c r="B251" s="2">
         <v>2.7330176830291748</v>
       </c>
-      <c r="C251" s="2">
-        <v>2.5844211578369141</v>
-      </c>
+      <c r="C251" s="2"/>
       <c r="D251" s="2">
         <v>2.6843230724334717</v>
       </c>
-      <c r="E251" s="2">
-        <v>2.6059088706970215</v>
-      </c>
+      <c r="E251" s="2"/>
     </row>
     <row r="252">
       <c r="A252" s="1">
@@ -3512,15 +2932,11 @@
       <c r="B252" s="2">
         <v>2.9742763042449951</v>
       </c>
-      <c r="C252" s="2">
-        <v>3.019458532333374</v>
-      </c>
+      <c r="C252" s="2"/>
       <c r="D252" s="2">
         <v>2.7008523941040039</v>
       </c>
-      <c r="E252" s="2">
-        <v>2.6127140522003174</v>
-      </c>
+      <c r="E252" s="2"/>
     </row>
     <row r="253">
       <c r="A253" s="1">
@@ -3529,15 +2945,11 @@
       <c r="B253" s="2">
         <v>2.8582320213317871</v>
       </c>
-      <c r="C253" s="2">
-        <v>2.6494851112365723</v>
-      </c>
+      <c r="C253" s="2"/>
       <c r="D253" s="2">
         <v>2.7425746917724609</v>
       </c>
-      <c r="E253" s="2">
-        <v>2.6451337337493896</v>
-      </c>
+      <c r="E253" s="2"/>
     </row>
     <row r="254">
       <c r="A254" s="1">
@@ -3546,15 +2958,11 @@
       <c r="B254" s="2">
         <v>2.7785665988922119</v>
       </c>
-      <c r="C254" s="2">
-        <v>2.7452874183654785</v>
-      </c>
+      <c r="C254" s="2"/>
       <c r="D254" s="2">
         <v>2.7578179836273193</v>
       </c>
-      <c r="E254" s="2">
-        <v>2.6621713638305664</v>
-      </c>
+      <c r="E254" s="2"/>
     </row>
     <row r="255">
       <c r="A255" s="1">
@@ -3563,15 +2971,11 @@
       <c r="B255" s="2">
         <v>2.6765787601470947</v>
       </c>
-      <c r="C255" s="2">
-        <v>2.5690972805023193</v>
-      </c>
+      <c r="C255" s="2"/>
       <c r="D255" s="2">
         <v>2.7331204414367676</v>
       </c>
-      <c r="E255" s="2">
-        <v>2.6619360446929932</v>
-      </c>
+      <c r="E255" s="2"/>
     </row>
     <row r="256">
       <c r="A256" s="1">
@@ -3580,15 +2984,11 @@
       <c r="B256" s="2">
         <v>2.6337580680847168</v>
       </c>
-      <c r="C256" s="2">
-        <v>2.4798038005828857</v>
-      </c>
+      <c r="C256" s="2"/>
       <c r="D256" s="2">
         <v>2.7129490375518799</v>
       </c>
-      <c r="E256" s="2">
-        <v>2.6616179943084717</v>
-      </c>
+      <c r="E256" s="2"/>
     </row>
     <row r="257">
       <c r="A257" s="1">
@@ -3597,15 +2997,11 @@
       <c r="B257" s="2">
         <v>2.678272008895874</v>
       </c>
-      <c r="C257" s="2">
-        <v>2.6516635417938232</v>
-      </c>
+      <c r="C257" s="2"/>
       <c r="D257" s="2">
         <v>2.7248332500457764</v>
       </c>
-      <c r="E257" s="2">
-        <v>2.6598665714263916</v>
-      </c>
+      <c r="E257" s="2"/>
     </row>
     <row r="258">
       <c r="A258" s="1">
@@ -3614,15 +3010,11 @@
       <c r="B258" s="2">
         <v>2.6287331581115723</v>
       </c>
-      <c r="C258" s="2">
-        <v>2.5561518669128418</v>
-      </c>
+      <c r="C258" s="2"/>
       <c r="D258" s="2">
         <v>2.7202703952789307</v>
       </c>
-      <c r="E258" s="2">
-        <v>2.6632769107818604</v>
-      </c>
+      <c r="E258" s="2"/>
     </row>
     <row r="259">
       <c r="A259" s="1">
@@ -3631,15 +3023,11 @@
       <c r="B259" s="2">
         <v>2.636648416519165</v>
       </c>
-      <c r="C259" s="2">
-        <v>2.7020549774169922</v>
-      </c>
+      <c r="C259" s="2"/>
       <c r="D259" s="2">
         <v>2.6817796230316162</v>
       </c>
-      <c r="E259" s="2">
-        <v>2.6055006980895996</v>
-      </c>
+      <c r="E259" s="2"/>
     </row>
     <row r="260">
       <c r="A260" s="1">
@@ -3648,15 +3036,11 @@
       <c r="B260" s="2">
         <v>2.5514752864837646</v>
       </c>
-      <c r="C260" s="2">
-        <v>2.5815596580505371</v>
-      </c>
+      <c r="C260" s="2"/>
       <c r="D260" s="2">
         <v>2.6873016357421875</v>
       </c>
-      <c r="E260" s="2">
-        <v>2.6210665702819824</v>
-      </c>
+      <c r="E260" s="2"/>
     </row>
     <row r="261">
       <c r="A261" s="1">
@@ -3665,15 +3049,11 @@
       <c r="B261" s="2">
         <v>3.0812349319458008</v>
       </c>
-      <c r="C261" s="2">
-        <v>3.0036952495574951</v>
-      </c>
+      <c r="C261" s="2"/>
       <c r="D261" s="2">
         <v>2.7034556865692139</v>
       </c>
-      <c r="E261" s="2">
-        <v>2.6527702808380127</v>
-      </c>
+      <c r="E261" s="2"/>
     </row>
     <row r="262">
       <c r="A262" s="1">
@@ -3682,15 +3062,11 @@
       <c r="B262" s="2">
         <v>2.8171656131744385</v>
       </c>
-      <c r="C262" s="2">
-        <v>2.6801791191101074</v>
-      </c>
+      <c r="C262" s="2"/>
       <c r="D262" s="2">
         <v>2.6964144706726074</v>
       </c>
-      <c r="E262" s="2">
-        <v>2.6240801811218262</v>
-      </c>
+      <c r="E262" s="2"/>
     </row>
     <row r="263">
       <c r="A263" s="1">
@@ -3699,15 +3075,11 @@
       <c r="B263" s="2">
         <v>2.4321508407592773</v>
       </c>
-      <c r="C263" s="2">
-        <v>2.2253012657165527</v>
-      </c>
+      <c r="C263" s="2"/>
       <c r="D263" s="2">
         <v>2.6909148693084717</v>
       </c>
-      <c r="E263" s="2">
-        <v>2.6154937744140625</v>
-      </c>
+      <c r="E263" s="2"/>
     </row>
     <row r="264">
       <c r="A264" s="1">
@@ -3716,15 +3088,11 @@
       <c r="B264" s="2">
         <v>2.7262763977050781</v>
       </c>
-      <c r="C264" s="2">
-        <v>2.7091891765594482</v>
-      </c>
+      <c r="C264" s="2"/>
       <c r="D264" s="2">
         <v>2.7549972534179688</v>
       </c>
-      <c r="E264" s="2">
-        <v>2.6533198356628418</v>
-      </c>
+      <c r="E264" s="2"/>
     </row>
     <row r="265">
       <c r="A265" s="1">
@@ -3733,15 +3101,11 @@
       <c r="B265" s="2">
         <v>2.779144287109375</v>
       </c>
-      <c r="C265" s="2">
-        <v>2.7651383876800537</v>
-      </c>
+      <c r="C265" s="2"/>
       <c r="D265" s="2">
         <v>2.8090832233428955</v>
       </c>
-      <c r="E265" s="2">
-        <v>2.6831283569335938</v>
-      </c>
+      <c r="E265" s="2"/>
     </row>
     <row r="266">
       <c r="A266" s="1">
@@ -3750,15 +3114,11 @@
       <c r="B266" s="2">
         <v>2.6149022579193115</v>
       </c>
-      <c r="C266" s="2">
-        <v>2.3934528827667236</v>
-      </c>
+      <c r="C266" s="2"/>
       <c r="D266" s="2">
         <v>2.768094539642334</v>
       </c>
-      <c r="E266" s="2">
-        <v>2.6401145458221436</v>
-      </c>
+      <c r="E266" s="2"/>
     </row>
     <row r="267">
       <c r="A267" s="1">
@@ -3767,15 +3127,11 @@
       <c r="B267" s="2">
         <v>2.5792360305786133</v>
       </c>
-      <c r="C267" s="2">
-        <v>2.4788727760314941</v>
-      </c>
+      <c r="C267" s="2"/>
       <c r="D267" s="2">
         <v>2.8302388191223145</v>
       </c>
-      <c r="E267" s="2">
-        <v>2.7109184265136719</v>
-      </c>
+      <c r="E267" s="2"/>
     </row>
     <row r="268">
       <c r="A268" s="1">
@@ -3784,15 +3140,11 @@
       <c r="B268" s="2">
         <v>3.2133891582489014</v>
       </c>
-      <c r="C268" s="2">
-        <v>3.0424909591674805</v>
-      </c>
+      <c r="C268" s="2"/>
       <c r="D268" s="2">
         <v>2.8525166511535645</v>
       </c>
-      <c r="E268" s="2">
-        <v>2.7585177421569824</v>
-      </c>
+      <c r="E268" s="2"/>
     </row>
     <row r="269">
       <c r="A269" s="1">
@@ -3801,15 +3153,11 @@
       <c r="B269" s="2">
         <v>3.0382492542266846</v>
       </c>
-      <c r="C269" s="2">
-        <v>2.8498356342315674</v>
-      </c>
+      <c r="C269" s="2"/>
       <c r="D269" s="2">
         <v>2.8651344776153564</v>
       </c>
-      <c r="E269" s="2">
-        <v>2.7390437126159668</v>
-      </c>
+      <c r="E269" s="2"/>
     </row>
     <row r="270">
       <c r="A270" s="1">
@@ -3818,15 +3166,11 @@
       <c r="B270" s="2">
         <v>2.7123379707336426</v>
       </c>
-      <c r="C270" s="2">
-        <v>2.6165714263916016</v>
-      </c>
+      <c r="C270" s="2"/>
       <c r="D270" s="2">
         <v>2.8804192543029785</v>
       </c>
-      <c r="E270" s="2">
-        <v>2.7529942989349365</v>
-      </c>
+      <c r="E270" s="2"/>
     </row>
     <row r="271">
       <c r="A271" s="1">
@@ -3835,15 +3179,11 @@
       <c r="B271" s="2">
         <v>3.3764641284942627</v>
       </c>
-      <c r="C271" s="2">
-        <v>3.3174130916595459</v>
-      </c>
+      <c r="C271" s="2"/>
       <c r="D271" s="2">
         <v>2.9208593368530273</v>
       </c>
-      <c r="E271" s="2">
-        <v>2.8050870895385742</v>
-      </c>
+      <c r="E271" s="2"/>
     </row>
     <row r="272">
       <c r="A272" s="1">
@@ -3852,15 +3192,11 @@
       <c r="B272" s="2">
         <v>2.6326503753662109</v>
       </c>
-      <c r="C272" s="2">
-        <v>2.6536962985992432</v>
-      </c>
+      <c r="C272" s="2"/>
       <c r="D272" s="2">
         <v>3.0039057731628418</v>
       </c>
-      <c r="E272" s="2">
-        <v>2.9026389122009277</v>
-      </c>
+      <c r="E272" s="2"/>
     </row>
     <row r="273">
       <c r="A273" s="1">
@@ -3869,15 +3205,11 @@
       <c r="B273" s="2">
         <v>2.8398375511169434</v>
       </c>
-      <c r="C273" s="2">
-        <v>2.5339229106903076</v>
-      </c>
+      <c r="C273" s="2"/>
       <c r="D273" s="2">
         <v>2.9937937259674072</v>
       </c>
-      <c r="E273" s="2">
-        <v>2.9044399261474609</v>
-      </c>
+      <c r="E273" s="2"/>
     </row>
     <row r="274">
       <c r="A274" s="1">
@@ -3886,15 +3218,11 @@
       <c r="B274" s="2">
         <v>2.9167056083679199</v>
       </c>
-      <c r="C274" s="2">
-        <v>2.8906924724578857</v>
-      </c>
+      <c r="C274" s="2"/>
       <c r="D274" s="2">
         <v>2.9863662719726562</v>
       </c>
-      <c r="E274" s="2">
-        <v>2.9182193279266357</v>
-      </c>
+      <c r="E274" s="2"/>
     </row>
     <row r="275">
       <c r="A275" s="1">
@@ -3903,15 +3231,11 @@
       <c r="B275" s="2">
         <v>2.9788649082183838</v>
       </c>
-      <c r="C275" s="2">
-        <v>2.8622887134552002</v>
-      </c>
+      <c r="C275" s="2"/>
       <c r="D275" s="2">
         <v>2.9935076236724854</v>
       </c>
-      <c r="E275" s="2">
-        <v>2.9288380146026611</v>
-      </c>
+      <c r="E275" s="2"/>
     </row>
     <row r="276">
       <c r="A276" s="1">
@@ -3920,15 +3244,11 @@
       <c r="B276" s="2">
         <v>3.3266537189483643</v>
       </c>
-      <c r="C276" s="2">
-        <v>3.3568391799926758</v>
-      </c>
+      <c r="C276" s="2"/>
       <c r="D276" s="2">
         <v>2.9609360694885254</v>
       </c>
-      <c r="E276" s="2">
-        <v>2.8958499431610107</v>
-      </c>
+      <c r="E276" s="2"/>
     </row>
     <row r="277">
       <c r="A277" s="1">
@@ -3937,15 +3257,11 @@
       <c r="B277" s="2">
         <v>3.1223795413970947</v>
       </c>
-      <c r="C277" s="2">
-        <v>3.0586991310119629</v>
-      </c>
+      <c r="C277" s="2"/>
       <c r="D277" s="2">
         <v>3.0026471614837646</v>
       </c>
-      <c r="E277" s="2">
-        <v>2.9229686260223389</v>
-      </c>
+      <c r="E277" s="2"/>
     </row>
     <row r="278">
       <c r="A278" s="1">
@@ -3954,15 +3270,11 @@
       <c r="B278" s="2">
         <v>2.9714028835296631</v>
       </c>
-      <c r="C278" s="2">
-        <v>2.9738514423370361</v>
-      </c>
+      <c r="C278" s="2"/>
       <c r="D278" s="2">
         <v>3.0358569622039795</v>
       </c>
-      <c r="E278" s="2">
-        <v>2.989093542098999</v>
-      </c>
+      <c r="E278" s="2"/>
     </row>
     <row r="279">
       <c r="A279" s="1">
@@ -3971,15 +3283,11 @@
       <c r="B279" s="2">
         <v>2.7766101360321045</v>
       </c>
-      <c r="C279" s="2">
-        <v>2.7121396064758301</v>
-      </c>
+      <c r="C279" s="2"/>
       <c r="D279" s="2">
         <v>3.0247781276702881</v>
       </c>
-      <c r="E279" s="2">
-        <v>2.9537947177886963</v>
-      </c>
+      <c r="E279" s="2"/>
     </row>
     <row r="280">
       <c r="A280" s="1">
@@ -3988,15 +3296,11 @@
       <c r="B280" s="2">
         <v>3.0833199024200439</v>
       </c>
-      <c r="C280" s="2">
-        <v>3.0205192565917969</v>
-      </c>
+      <c r="C280" s="2"/>
       <c r="D280" s="2">
         <v>3.0043797492980957</v>
       </c>
-      <c r="E280" s="2">
-        <v>2.938382625579834</v>
-      </c>
+      <c r="E280" s="2"/>
     </row>
     <row r="281">
       <c r="A281" s="1">
@@ -4005,15 +3309,11 @@
       <c r="B281" s="2">
         <v>3.0080509185791016</v>
       </c>
-      <c r="C281" s="2">
-        <v>2.8977658748626709</v>
-      </c>
+      <c r="C281" s="2"/>
       <c r="D281" s="2">
         <v>2.9357397556304932</v>
       </c>
-      <c r="E281" s="2">
-        <v>2.8578217029571533</v>
-      </c>
+      <c r="E281" s="2"/>
     </row>
     <row r="282">
       <c r="A282" s="1">
@@ -4022,15 +3322,11 @@
       <c r="B282" s="2">
         <v>3.1387259960174561</v>
       </c>
-      <c r="C282" s="2">
-        <v>3.1290462017059326</v>
-      </c>
+      <c r="C282" s="2"/>
       <c r="D282" s="2">
         <v>2.8883428573608398</v>
       </c>
-      <c r="E282" s="2">
-        <v>2.8060641288757324</v>
-      </c>
+      <c r="E282" s="2"/>
     </row>
     <row r="283">
       <c r="A283" s="1">
@@ -4039,15 +3335,11 @@
       <c r="B283" s="2">
         <v>2.8169944286346436</v>
       </c>
-      <c r="C283" s="2">
-        <v>2.5730020999908447</v>
-      </c>
+      <c r="C283" s="2"/>
       <c r="D283" s="2">
         <v>2.8581039905548096</v>
       </c>
-      <c r="E283" s="2">
-        <v>2.793879508972168</v>
-      </c>
+      <c r="E283" s="2"/>
     </row>
     <row r="284">
       <c r="A284" s="1">
@@ -4056,15 +3348,11 @@
       <c r="B284" s="2">
         <v>2.795280933380127</v>
       </c>
-      <c r="C284" s="2">
-        <v>2.7235801219940186</v>
-      </c>
+      <c r="C284" s="2"/>
       <c r="D284" s="2">
         <v>2.8784995079040527</v>
       </c>
-      <c r="E284" s="2">
-        <v>2.8091187477111816</v>
-      </c>
+      <c r="E284" s="2"/>
     </row>
     <row r="285">
       <c r="A285" s="1">
@@ -4073,15 +3361,11 @@
       <c r="B285" s="2">
         <v>2.7088937759399414</v>
       </c>
-      <c r="C285" s="2">
-        <v>2.6317906379699707</v>
-      </c>
+      <c r="C285" s="2"/>
       <c r="D285" s="2">
         <v>2.9298126697540283</v>
       </c>
-      <c r="E285" s="2">
-        <v>2.8733401298522949</v>
-      </c>
+      <c r="E285" s="2"/>
     </row>
     <row r="286">
       <c r="A286" s="1">
@@ -4090,15 +3374,11 @@
       <c r="B286" s="2">
         <v>2.6958062648773193</v>
       </c>
-      <c r="C286" s="2">
-        <v>2.5928819179534912</v>
-      </c>
+      <c r="C286" s="2"/>
       <c r="D286" s="2">
         <v>2.8711872100830078</v>
       </c>
-      <c r="E286" s="2">
-        <v>2.8228931427001953</v>
-      </c>
+      <c r="E286" s="2"/>
     </row>
     <row r="287">
       <c r="A287" s="1">
@@ -4107,15 +3387,11 @@
       <c r="B287" s="2">
         <v>2.6992526054382324</v>
       </c>
-      <c r="C287" s="2">
-        <v>2.8641893863677979</v>
-      </c>
+      <c r="C287" s="2"/>
       <c r="D287" s="2">
         <v>2.8382124900817871</v>
       </c>
-      <c r="E287" s="2">
-        <v>2.7869067192077637</v>
-      </c>
+      <c r="E287" s="2"/>
     </row>
     <row r="288">
       <c r="A288" s="1">
@@ -4124,15 +3400,11 @@
       <c r="B288" s="2">
         <v>2.9601714611053467</v>
       </c>
-      <c r="C288" s="2">
-        <v>2.849292516708374</v>
-      </c>
+      <c r="C288" s="2"/>
       <c r="D288" s="2">
         <v>2.8817493915557861</v>
       </c>
-      <c r="E288" s="2">
-        <v>2.8519666194915771</v>
-      </c>
+      <c r="E288" s="2"/>
     </row>
     <row r="289">
       <c r="A289" s="1">
@@ -4141,15 +3413,11 @@
       <c r="B289" s="2">
         <v>3.5451385974884033</v>
       </c>
-      <c r="C289" s="2">
-        <v>3.5985124111175537</v>
-      </c>
+      <c r="C289" s="2"/>
       <c r="D289" s="2">
         <v>2.9315910339355469</v>
       </c>
-      <c r="E289" s="2">
-        <v>2.8957180976867676</v>
-      </c>
+      <c r="E289" s="2"/>
     </row>
     <row r="290">
       <c r="A290" s="1">
@@ -4158,15 +3426,11 @@
       <c r="B290" s="2">
         <v>2.4804210662841797</v>
       </c>
-      <c r="C290" s="2">
-        <v>2.4437422752380371</v>
-      </c>
+      <c r="C290" s="2"/>
       <c r="D290" s="2">
         <v>2.9121754169464111</v>
       </c>
-      <c r="E290" s="2">
-        <v>2.8774456977844238</v>
-      </c>
+      <c r="E290" s="2"/>
     </row>
     <row r="291">
       <c r="A291" s="1">
@@ -4175,15 +3439,11 @@
       <c r="B291" s="2">
         <v>2.841954231262207</v>
       </c>
-      <c r="C291" s="2">
-        <v>2.8051683902740479</v>
-      </c>
+      <c r="C291" s="2"/>
       <c r="D291" s="2">
         <v>2.932633638381958</v>
       </c>
-      <c r="E291" s="2">
-        <v>2.8996829986572266</v>
-      </c>
+      <c r="E291" s="2"/>
     </row>
     <row r="292">
       <c r="A292" s="1">
@@ -4192,15 +3452,11 @@
       <c r="B292" s="2">
         <v>3.2088251113891602</v>
       </c>
-      <c r="C292" s="2">
-        <v>3.1585409641265869</v>
-      </c>
+      <c r="C292" s="2"/>
       <c r="D292" s="2">
         <v>2.9704816341400146</v>
       </c>
-      <c r="E292" s="2">
-        <v>2.9139575958251953</v>
-      </c>
+      <c r="E292" s="2"/>
     </row>
     <row r="293">
       <c r="A293" s="1">
@@ -4209,15 +3465,11 @@
       <c r="B293" s="2">
         <v>3.2438561916351318</v>
       </c>
-      <c r="C293" s="2">
-        <v>3.1173453330993652</v>
-      </c>
+      <c r="C293" s="2"/>
       <c r="D293" s="2">
         <v>2.9342086315155029</v>
       </c>
-      <c r="E293" s="2">
-        <v>2.8897972106933594</v>
-      </c>
+      <c r="E293" s="2"/>
     </row>
     <row r="294">
       <c r="A294" s="1">
@@ -4226,15 +3478,11 @@
       <c r="B294" s="2">
         <v>2.5341536998748779</v>
       </c>
-      <c r="C294" s="2">
-        <v>2.4673376083374023</v>
-      </c>
+      <c r="C294" s="2"/>
       <c r="D294" s="2">
         <v>2.8772158622741699</v>
       </c>
-      <c r="E294" s="2">
-        <v>2.8099110126495361</v>
-      </c>
+      <c r="E294" s="2"/>
     </row>
     <row r="295">
       <c r="A295" s="1">
@@ -4243,15 +3491,11 @@
       <c r="B295" s="2">
         <v>2.879929780960083</v>
       </c>
-      <c r="C295" s="2">
-        <v>2.7930171489715576</v>
-      </c>
+      <c r="C295" s="2"/>
       <c r="D295" s="2">
         <v>2.9354000091552734</v>
       </c>
-      <c r="E295" s="2">
-        <v>2.8629651069641113</v>
-      </c>
+      <c r="E295" s="2"/>
     </row>
     <row r="296">
       <c r="A296" s="1">
@@ -4260,15 +3504,11 @@
       <c r="B296" s="2">
         <v>3.0398852825164795</v>
       </c>
-      <c r="C296" s="2">
-        <v>2.9926621913909912</v>
-      </c>
+      <c r="C296" s="2"/>
       <c r="D296" s="2">
         <v>2.9405057430267334</v>
       </c>
-      <c r="E296" s="2">
-        <v>2.8402009010314941</v>
-      </c>
+      <c r="E296" s="2"/>
     </row>
     <row r="297">
       <c r="A297" s="1">
@@ -4277,15 +3517,11 @@
       <c r="B297" s="2">
         <v>2.6337132453918457</v>
       </c>
-      <c r="C297" s="2">
-        <v>2.6318480968475342</v>
-      </c>
+      <c r="C297" s="2"/>
       <c r="D297" s="2">
         <v>2.9440460205078125</v>
       </c>
-      <c r="E297" s="2">
-        <v>2.842738151550293</v>
-      </c>
+      <c r="E297" s="2"/>
     </row>
     <row r="298">
       <c r="A298" s="1">
@@ -4294,15 +3530,11 @@
       <c r="B298" s="2">
         <v>3.0322039127349854</v>
       </c>
-      <c r="C298" s="2">
-        <v>2.8795380592346191</v>
-      </c>
+      <c r="C298" s="2"/>
       <c r="D298" s="2">
         <v>2.888934850692749</v>
       </c>
-      <c r="E298" s="2">
-        <v>2.7928733825683594</v>
-      </c>
+      <c r="E298" s="2"/>
     </row>
     <row r="299">
       <c r="A299" s="1">
@@ -4311,15 +3543,11 @@
       <c r="B299" s="2">
         <v>3.0040779113769531</v>
       </c>
-      <c r="C299" s="2">
-        <v>2.9212286472320557</v>
-      </c>
+      <c r="C299" s="2"/>
       <c r="D299" s="2">
         <v>2.9606404304504395</v>
       </c>
-      <c r="E299" s="2">
-        <v>2.8876626491546631</v>
-      </c>
+      <c r="E299" s="2"/>
     </row>
     <row r="300">
       <c r="A300" s="1">
@@ -4328,15 +3556,11 @@
       <c r="B300" s="2">
         <v>2.8879055976867676</v>
       </c>
-      <c r="C300" s="2">
-        <v>2.6002907752990723</v>
-      </c>
+      <c r="C300" s="2"/>
       <c r="D300" s="2">
         <v>2.9479122161865234</v>
       </c>
-      <c r="E300" s="2">
-        <v>2.8971562385559082</v>
-      </c>
+      <c r="E300" s="2"/>
     </row>
     <row r="301">
       <c r="A301" s="1">
@@ -4345,15 +3569,11 @@
       <c r="B301" s="2">
         <v>3.2406888008117676</v>
       </c>
-      <c r="C301" s="2">
-        <v>3.1813745498657227</v>
-      </c>
+      <c r="C301" s="2"/>
       <c r="D301" s="2">
         <v>3.0099730491638184</v>
       </c>
-      <c r="E301" s="2">
-        <v>2.9303536415100098</v>
-      </c>
+      <c r="E301" s="2"/>
     </row>
     <row r="302">
       <c r="A302" s="1">
@@ -4362,15 +3582,11 @@
       <c r="B302" s="2">
         <v>2.7478563785552979</v>
       </c>
-      <c r="C302" s="2">
-        <v>2.6685633659362793</v>
-      </c>
+      <c r="C302" s="2"/>
       <c r="D302" s="2">
         <v>3.0016026496887207</v>
       </c>
-      <c r="E302" s="2">
-        <v>2.9179236888885498</v>
-      </c>
+      <c r="E302" s="2"/>
     </row>
     <row r="303">
       <c r="A303" s="1">
@@ -4379,15 +3595,11 @@
       <c r="B303" s="2">
         <v>3.1795029640197754</v>
       </c>
-      <c r="C303" s="2">
-        <v>3.320441722869873</v>
-      </c>
+      <c r="C303" s="2"/>
       <c r="D303" s="2">
         <v>2.9876425266265869</v>
       </c>
-      <c r="E303" s="2">
-        <v>2.9226644039154053</v>
-      </c>
+      <c r="E303" s="2"/>
     </row>
     <row r="304">
       <c r="A304" s="1">
@@ -4396,15 +3608,11 @@
       <c r="B304" s="2">
         <v>2.7653753757476807</v>
       </c>
-      <c r="C304" s="2">
-        <v>2.8784592151641846</v>
-      </c>
+      <c r="C304" s="2"/>
       <c r="D304" s="2">
         <v>2.9952743053436279</v>
       </c>
-      <c r="E304" s="2">
-        <v>2.9258270263671875</v>
-      </c>
+      <c r="E304" s="2"/>
     </row>
     <row r="305">
       <c r="A305" s="1">
@@ -4413,15 +3621,11 @@
       <c r="B305" s="2">
         <v>3.5984334945678711</v>
       </c>
-      <c r="C305" s="2">
-        <v>3.2914376258850098</v>
-      </c>
+      <c r="C305" s="2"/>
       <c r="D305" s="2">
         <v>3.0517692565917969</v>
       </c>
-      <c r="E305" s="2">
-        <v>3.0097761154174805</v>
-      </c>
+      <c r="E305" s="2"/>
     </row>
     <row r="306">
       <c r="A306" s="1">
@@ -4430,15 +3634,11 @@
       <c r="B306" s="2">
         <v>2.5583784580230713</v>
       </c>
-      <c r="C306" s="2">
-        <v>2.5199799537658691</v>
-      </c>
+      <c r="C306" s="2"/>
       <c r="D306" s="2">
         <v>3.0155408382415771</v>
       </c>
-      <c r="E306" s="2">
-        <v>2.978792667388916</v>
-      </c>
+      <c r="E306" s="2"/>
     </row>
     <row r="307">
       <c r="A307" s="1">
@@ -4447,15 +3647,11 @@
       <c r="B307" s="2">
         <v>2.9065632820129395</v>
       </c>
-      <c r="C307" s="2">
-        <v>2.9222044944763184</v>
-      </c>
+      <c r="C307" s="2"/>
       <c r="D307" s="2">
         <v>3.0446062088012695</v>
       </c>
-      <c r="E307" s="2">
-        <v>3.0190021991729736</v>
-      </c>
+      <c r="E307" s="2"/>
     </row>
     <row r="308">
       <c r="A308" s="1">
@@ -4464,15 +3660,11 @@
       <c r="B308" s="2">
         <v>3.0727653503417969</v>
       </c>
-      <c r="C308" s="2">
-        <v>2.949690580368042</v>
-      </c>
+      <c r="C308" s="2"/>
       <c r="D308" s="2">
         <v>2.9843366146087646</v>
       </c>
-      <c r="E308" s="2">
-        <v>2.9411156177520752</v>
-      </c>
+      <c r="E308" s="2"/>
     </row>
     <row r="309">
       <c r="A309" s="1">
@@ -4481,15 +3673,11 @@
       <c r="B309" s="2">
         <v>3.396359920501709</v>
       </c>
-      <c r="C309" s="2">
-        <v>3.3558335304260254</v>
-      </c>
+      <c r="C309" s="2"/>
       <c r="D309" s="2">
         <v>2.9754116535186768</v>
       </c>
-      <c r="E309" s="2">
-        <v>2.9115934371948242</v>
-      </c>
+      <c r="E309" s="2"/>
     </row>
     <row r="310">
       <c r="A310" s="1">
@@ -4498,15 +3686,11 @@
       <c r="B310" s="2">
         <v>2.9146325588226318</v>
       </c>
-      <c r="C310" s="2">
-        <v>2.9025232791900635</v>
-      </c>
+      <c r="C310" s="2"/>
       <c r="D310" s="2">
         <v>2.8857958316802979</v>
       </c>
-      <c r="E310" s="2">
-        <v>2.8614468574523926</v>
-      </c>
+      <c r="E310" s="2"/>
     </row>
     <row r="311">
       <c r="A311" s="1">
@@ -4515,15 +3699,11 @@
       <c r="B311" s="2">
         <v>3.009443998336792</v>
       </c>
-      <c r="C311" s="2">
-        <v>3.0304496288299561</v>
-      </c>
+      <c r="C311" s="2"/>
       <c r="D311" s="2">
         <v>2.9076120853424072</v>
       </c>
-      <c r="E311" s="2">
-        <v>2.8847436904907227</v>
-      </c>
+      <c r="E311" s="2"/>
     </row>
     <row r="312">
       <c r="A312" s="1">
@@ -4532,15 +3712,11 @@
       <c r="B312" s="2">
         <v>2.6370763778686523</v>
       </c>
-      <c r="C312" s="2">
-        <v>2.6194627285003662</v>
-      </c>
+      <c r="C312" s="2"/>
       <c r="D312" s="2">
         <v>2.9007503986358643</v>
       </c>
-      <c r="E312" s="2">
-        <v>2.8869779109954834</v>
-      </c>
+      <c r="E312" s="2"/>
     </row>
     <row r="313">
       <c r="A313" s="1">
@@ -4549,15 +3725,11 @@
       <c r="B313" s="2">
         <v>2.6850523948669434</v>
       </c>
-      <c r="C313" s="2">
-        <v>2.6127581596374512</v>
-      </c>
+      <c r="C313" s="2"/>
       <c r="D313" s="2">
         <v>2.8695483207702637</v>
       </c>
-      <c r="E313" s="2">
-        <v>2.8777604103088379</v>
-      </c>
+      <c r="E313" s="2"/>
     </row>
     <row r="314">
       <c r="A314" s="1">
@@ -4566,15 +3738,11 @@
       <c r="B314" s="2">
         <v>2.7918891906738281</v>
       </c>
-      <c r="C314" s="2">
-        <v>2.840118408203125</v>
-      </c>
+      <c r="C314" s="2"/>
       <c r="D314" s="2">
         <v>2.8094995021820068</v>
       </c>
-      <c r="E314" s="2">
-        <v>2.8205344676971436</v>
-      </c>
+      <c r="E314" s="2"/>
     </row>
     <row r="315">
       <c r="A315" s="1">
@@ -4583,15 +3751,11 @@
       <c r="B315" s="2">
         <v>2.7547266483306885</v>
       </c>
-      <c r="C315" s="2">
-        <v>2.7296526432037354</v>
-      </c>
+      <c r="C315" s="2"/>
       <c r="D315" s="2">
         <v>2.7660925388336182</v>
       </c>
-      <c r="E315" s="2">
-        <v>2.7688651084899902</v>
-      </c>
+      <c r="E315" s="2"/>
     </row>
     <row r="316">
       <c r="A316" s="1">
@@ -4600,15 +3764,11 @@
       <c r="B316" s="2">
         <v>2.8448073863983154</v>
       </c>
-      <c r="C316" s="2">
-        <v>2.9423112869262695</v>
-      </c>
+      <c r="C316" s="2"/>
       <c r="D316" s="2">
         <v>2.7220799922943115</v>
       </c>
-      <c r="E316" s="2">
-        <v>2.7207028865814209</v>
-      </c>
+      <c r="E316" s="2"/>
     </row>
     <row r="317">
       <c r="A317" s="1">
@@ -4617,15 +3777,11 @@
       <c r="B317" s="2">
         <v>2.7919459342956543</v>
       </c>
-      <c r="C317" s="2">
-        <v>2.8667337894439697</v>
-      </c>
+      <c r="C317" s="2"/>
       <c r="D317" s="2">
         <v>2.8139922618865967</v>
       </c>
-      <c r="E317" s="2">
-        <v>2.8138458728790283</v>
-      </c>
+      <c r="E317" s="2"/>
     </row>
     <row r="318">
       <c r="A318" s="1">
@@ -4634,15 +3790,11 @@
       <c r="B318" s="2">
         <v>2.855921745300293</v>
       </c>
-      <c r="C318" s="2">
-        <v>2.8408012390136719</v>
-      </c>
+      <c r="C318" s="2"/>
       <c r="D318" s="2">
         <v>2.8755722045898438</v>
       </c>
-      <c r="E318" s="2">
-        <v>2.8867316246032715</v>
-      </c>
+      <c r="E318" s="2"/>
     </row>
     <row r="319">
       <c r="A319" s="1">
@@ -4651,15 +3803,11 @@
       <c r="B319" s="2">
         <v>2.5239691734313965</v>
       </c>
-      <c r="C319" s="2">
-        <v>2.4374990463256836</v>
-      </c>
+      <c r="C319" s="2"/>
       <c r="D319" s="2">
         <v>2.8728706836700439</v>
       </c>
-      <c r="E319" s="2">
-        <v>2.873490571975708</v>
-      </c>
+      <c r="E319" s="2"/>
     </row>
     <row r="320">
       <c r="A320" s="1">
@@ -4668,15 +3816,11 @@
       <c r="B320" s="2">
         <v>2.6133308410644531</v>
       </c>
-      <c r="C320" s="2">
-        <v>2.5969889163970947</v>
-      </c>
+      <c r="C320" s="2"/>
       <c r="D320" s="2">
         <v>2.8676979541778564</v>
       </c>
-      <c r="E320" s="2">
-        <v>2.8783292770385742</v>
-      </c>
+      <c r="E320" s="2"/>
     </row>
     <row r="321">
       <c r="A321" s="1">
@@ -4685,15 +3829,11 @@
       <c r="B321" s="2">
         <v>3.4642865657806396</v>
       </c>
-      <c r="C321" s="2">
-        <v>3.4577493667602539</v>
-      </c>
+      <c r="C321" s="2"/>
       <c r="D321" s="2">
         <v>2.8698451519012451</v>
       </c>
-      <c r="E321" s="2">
-        <v>2.8436210155487061</v>
-      </c>
+      <c r="E321" s="2"/>
     </row>
     <row r="322">
       <c r="A322" s="1">
@@ -4702,15 +3842,11 @@
       <c r="B322" s="2">
         <v>3.2392730712890625</v>
       </c>
-      <c r="C322" s="2">
-        <v>3.268730640411377</v>
-      </c>
+      <c r="C322" s="2"/>
       <c r="D322" s="2">
         <v>2.8810973167419434</v>
       </c>
-      <c r="E322" s="2">
-        <v>2.8520121574401855</v>
-      </c>
+      <c r="E322" s="2"/>
     </row>
     <row r="323">
       <c r="A323" s="1">
@@ -4719,15 +3855,11 @@
       <c r="B323" s="2">
         <v>2.7675745487213135</v>
       </c>
-      <c r="C323" s="2">
-        <v>2.7209475040435791</v>
-      </c>
+      <c r="C323" s="2"/>
       <c r="D323" s="2">
         <v>2.8653018474578857</v>
       </c>
-      <c r="E323" s="2">
-        <v>2.8428835868835449</v>
-      </c>
+      <c r="E323" s="2"/>
     </row>
     <row r="324">
       <c r="A324" s="1">
@@ -4736,15 +3868,11 @@
       <c r="B324" s="2">
         <v>2.708172082901001</v>
       </c>
-      <c r="C324" s="2">
-        <v>2.7732024192810059</v>
-      </c>
+      <c r="C324" s="2"/>
       <c r="D324" s="2">
         <v>2.9021182060241699</v>
       </c>
-      <c r="E324" s="2">
-        <v>2.8884146213531494</v>
-      </c>
+      <c r="E324" s="2"/>
     </row>
     <row r="325">
       <c r="A325" s="1">
@@ -4753,15 +3881,11 @@
       <c r="B325" s="2">
         <v>2.8641316890716553</v>
       </c>
-      <c r="C325" s="2">
-        <v>2.6299369335174561</v>
-      </c>
+      <c r="C325" s="2"/>
       <c r="D325" s="2">
         <v>2.9019820690155029</v>
       </c>
-      <c r="E325" s="2">
-        <v>2.8935303688049316</v>
-      </c>
+      <c r="E325" s="2"/>
     </row>
     <row r="326">
       <c r="A326" s="1">
@@ -4770,15 +3894,11 @@
       <c r="B326" s="2">
         <v>2.8932168483734131</v>
       </c>
-      <c r="C326" s="2">
-        <v>2.9422540664672852</v>
-      </c>
+      <c r="C326" s="2"/>
       <c r="D326" s="2">
         <v>2.8163001537322998</v>
       </c>
-      <c r="E326" s="2">
-        <v>2.8049905300140381</v>
-      </c>
+      <c r="E326" s="2"/>
     </row>
     <row r="327">
       <c r="A327" s="1">
@@ -4787,15 +3907,11 @@
       <c r="B327" s="2">
         <v>2.7137627601623535</v>
       </c>
-      <c r="C327" s="2">
-        <v>2.7586433887481689</v>
-      </c>
+      <c r="C327" s="2"/>
       <c r="D327" s="2">
         <v>2.7646729946136475</v>
       </c>
-      <c r="E327" s="2">
-        <v>2.7516517639160156</v>
-      </c>
+      <c r="E327" s="2"/>
     </row>
     <row r="328">
       <c r="A328" s="1">
@@ -4804,15 +3920,11 @@
       <c r="B328" s="2">
         <v>2.8553144931793213</v>
       </c>
-      <c r="C328" s="2">
-        <v>2.8472793102264404</v>
-      </c>
+      <c r="C328" s="2"/>
       <c r="D328" s="2">
         <v>2.7419497966766357</v>
       </c>
-      <c r="E328" s="2">
-        <v>2.7294533252716064</v>
-      </c>
+      <c r="E328" s="2"/>
     </row>
     <row r="329">
       <c r="A329" s="1">
@@ -4821,15 +3933,11 @@
       <c r="B329" s="2">
         <v>2.6121056079864502</v>
       </c>
-      <c r="C329" s="2">
-        <v>2.6430299282073975</v>
-      </c>
+      <c r="C329" s="2"/>
       <c r="D329" s="2">
         <v>2.8135664463043213</v>
       </c>
-      <c r="E329" s="2">
-        <v>2.7899932861328125</v>
-      </c>
+      <c r="E329" s="2"/>
     </row>
     <row r="330">
       <c r="A330" s="1">
@@ -4838,15 +3946,11 @@
       <c r="B330" s="2">
         <v>2.6931507587432861</v>
       </c>
-      <c r="C330" s="2">
-        <v>2.6608915328979492</v>
-      </c>
+      <c r="C330" s="2"/>
       <c r="D330" s="2">
         <v>2.8811171054840088</v>
       </c>
-      <c r="E330" s="2">
-        <v>2.8690717220306396</v>
-      </c>
+      <c r="E330" s="2"/>
     </row>
     <row r="331">
       <c r="A331" s="1">
@@ -4855,15 +3959,11 @@
       <c r="B331" s="2">
         <v>2.7746286392211914</v>
       </c>
-      <c r="C331" s="2">
-        <v>2.7886812686920166</v>
-      </c>
+      <c r="C331" s="2"/>
       <c r="D331" s="2">
         <v>2.9362571239471436</v>
       </c>
-      <c r="E331" s="2">
-        <v>2.8998568058013916</v>
-      </c>
+      <c r="E331" s="2"/>
     </row>
     <row r="332">
       <c r="A332" s="1">
@@ -4872,15 +3972,11 @@
       <c r="B332" s="2">
         <v>2.5630660057067871</v>
       </c>
-      <c r="C332" s="2">
-        <v>2.5211620330810547</v>
-      </c>
+      <c r="C332" s="2"/>
       <c r="D332" s="2">
         <v>2.9898898601531982</v>
       </c>
-      <c r="E332" s="2">
-        <v>2.9406242370605469</v>
-      </c>
+      <c r="E332" s="2"/>
     </row>
     <row r="333">
       <c r="A333" s="1">
@@ -4889,15 +3985,11 @@
       <c r="B333" s="2">
         <v>3.3527207374572754</v>
       </c>
-      <c r="C333" s="2">
-        <v>3.3180608749389648</v>
-      </c>
+      <c r="C333" s="2"/>
       <c r="D333" s="2">
         <v>3.0033667087554932</v>
       </c>
-      <c r="E333" s="2">
-        <v>2.9419751167297363</v>
-      </c>
+      <c r="E333" s="2"/>
     </row>
     <row r="334">
       <c r="A334" s="1">
@@ -4906,15 +3998,11 @@
       <c r="B334" s="2">
         <v>3.4720878601074219</v>
       </c>
-      <c r="C334" s="2">
-        <v>3.3416426181793213</v>
-      </c>
+      <c r="C334" s="2"/>
       <c r="D334" s="2">
         <v>3.0960991382598877</v>
       </c>
-      <c r="E334" s="2">
-        <v>3.0456295013427734</v>
-      </c>
+      <c r="E334" s="2"/>
     </row>
     <row r="335">
       <c r="A335" s="1">
@@ -4923,15 +4011,11 @@
       <c r="B335" s="2">
         <v>3.3894779682159424</v>
       </c>
-      <c r="C335" s="2">
-        <v>3.21932053565979</v>
-      </c>
+      <c r="C335" s="2"/>
       <c r="D335" s="2">
         <v>3.0677731037139893</v>
       </c>
-      <c r="E335" s="2">
-        <v>3.0156311988830566</v>
-      </c>
+      <c r="E335" s="2"/>
     </row>
     <row r="336">
       <c r="A336" s="1">
@@ -4940,15 +4024,11 @@
       <c r="B336" s="2">
         <v>3.1964564323425293</v>
       </c>
-      <c r="C336" s="2">
-        <v>3.1255502700805664</v>
-      </c>
+      <c r="C336" s="2"/>
       <c r="D336" s="2">
         <v>3.1209614276885986</v>
       </c>
-      <c r="E336" s="2">
-        <v>3.072688102722168</v>
-      </c>
+      <c r="E336" s="2"/>
     </row>
     <row r="337">
       <c r="A337" s="1">
@@ -4957,15 +4037,11 @@
       <c r="B337" s="2">
         <v>2.9766063690185547</v>
       </c>
-      <c r="C337" s="2">
-        <v>2.8594372272491455</v>
-      </c>
+      <c r="C337" s="2"/>
       <c r="D337" s="2">
         <v>3.2216255664825439</v>
       </c>
-      <c r="E337" s="2">
-        <v>3.1743228435516357</v>
-      </c>
+      <c r="E337" s="2"/>
     </row>
     <row r="338">
       <c r="A338" s="1">
@@ -4974,15 +4050,11 @@
       <c r="B338" s="2">
         <v>3.4466981887817383</v>
       </c>
-      <c r="C338" s="2">
-        <v>3.575918436050415</v>
-      </c>
+      <c r="C338" s="2"/>
       <c r="D338" s="2">
         <v>3.2171969413757324</v>
       </c>
-      <c r="E338" s="2">
-        <v>3.1838164329528809</v>
-      </c>
+      <c r="E338" s="2"/>
     </row>
     <row r="339">
       <c r="A339" s="1">
@@ -4991,15 +4063,11 @@
       <c r="B339" s="2">
         <v>2.4382150173187256</v>
       </c>
-      <c r="C339" s="2">
-        <v>2.3909077644348145</v>
-      </c>
+      <c r="C339" s="2"/>
       <c r="D339" s="2">
         <v>3.1648685932159424</v>
       </c>
-      <c r="E339" s="2">
-        <v>3.1430068016052246</v>
-      </c>
+      <c r="E339" s="2"/>
     </row>
     <row r="340">
       <c r="A340" s="1">
@@ -5008,15 +4076,11 @@
       <c r="B340" s="2">
         <v>3.2533247470855713</v>
       </c>
-      <c r="C340" s="2">
-        <v>3.3021938800811768</v>
-      </c>
+      <c r="C340" s="2"/>
       <c r="D340" s="2">
         <v>3.0457100868225098</v>
       </c>
-      <c r="E340" s="2">
-        <v>3.0294396877288818</v>
-      </c>
+      <c r="E340" s="2"/>
     </row>
     <row r="341">
       <c r="A341" s="1">
@@ -5025,15 +4089,11 @@
       <c r="B341" s="2">
         <v>3.4690430164337158</v>
       </c>
-      <c r="C341" s="2">
-        <v>3.4358742237091064</v>
-      </c>
+      <c r="C341" s="2"/>
       <c r="D341" s="2">
         <v>3.0564477443695068</v>
       </c>
-      <c r="E341" s="2">
-        <v>3.0382809638977051</v>
-      </c>
+      <c r="E341" s="2"/>
     </row>
     <row r="342">
       <c r="A342" s="1">
@@ -5042,15 +4102,11 @@
       <c r="B342" s="2">
         <v>3.3128621578216553</v>
       </c>
-      <c r="C342" s="2">
-        <v>3.4035036563873291</v>
-      </c>
+      <c r="C342" s="2"/>
       <c r="D342" s="2">
         <v>3.0107812881469727</v>
       </c>
-      <c r="E342" s="2">
-        <v>3.005333423614502</v>
-      </c>
+      <c r="E342" s="2"/>
     </row>
     <row r="343">
       <c r="A343" s="1">
@@ -5059,15 +4115,11 @@
       <c r="B343" s="2">
         <v>3.0011341571807861</v>
       </c>
-      <c r="C343" s="2">
-        <v>2.9743552207946777</v>
-      </c>
+      <c r="C343" s="2"/>
       <c r="D343" s="2">
         <v>2.9489359855651855</v>
       </c>
-      <c r="E343" s="2">
-        <v>2.9339637756347656</v>
-      </c>
+      <c r="E343" s="2"/>
     </row>
     <row r="344">
       <c r="A344" s="1">
@@ -5076,15 +4128,11 @@
       <c r="B344" s="2">
         <v>2.3170506954193115</v>
       </c>
-      <c r="C344" s="2">
-        <v>2.1972169876098633</v>
-      </c>
+      <c r="C344" s="2"/>
       <c r="D344" s="2">
         <v>2.9932661056518555</v>
       </c>
-      <c r="E344" s="2">
-        <v>2.9787449836730957</v>
-      </c>
+      <c r="E344" s="2"/>
     </row>
     <row r="345">
       <c r="A345" s="1">
@@ -5093,15 +4141,11 @@
       <c r="B345" s="2">
         <v>3.2930951118469238</v>
       </c>
-      <c r="C345" s="2">
-        <v>3.2051219940185547</v>
-      </c>
+      <c r="C345" s="2"/>
       <c r="D345" s="2">
         <v>2.9684574604034424</v>
       </c>
-      <c r="E345" s="2">
-        <v>2.9520604610443115</v>
-      </c>
+      <c r="E345" s="2"/>
     </row>
     <row r="346">
       <c r="A346" s="1">
@@ -5110,15 +4154,11 @@
       <c r="B346" s="2">
         <v>2.5656082630157471</v>
       </c>
-      <c r="C346" s="2">
-        <v>2.5629076957702637</v>
-      </c>
+      <c r="C346" s="2"/>
       <c r="D346" s="2">
         <v>2.9091699123382568</v>
       </c>
-      <c r="E346" s="2">
-        <v>2.8921768665313721</v>
-      </c>
+      <c r="E346" s="2"/>
     </row>
     <row r="347">
       <c r="A347" s="1">
@@ -5127,15 +4167,11 @@
       <c r="B347" s="2">
         <v>2.8900904655456543</v>
       </c>
-      <c r="C347" s="2">
-        <v>2.9335930347442627</v>
-      </c>
+      <c r="C347" s="2"/>
       <c r="D347" s="2">
         <v>2.7975034713745117</v>
       </c>
-      <c r="E347" s="2">
-        <v>2.7654850482940674</v>
-      </c>
+      <c r="E347" s="2"/>
     </row>
     <row r="348">
       <c r="A348" s="1">
@@ -5144,15 +4180,11 @@
       <c r="B348" s="2">
         <v>2.8371856212615967</v>
       </c>
-      <c r="C348" s="2">
-        <v>2.793938159942627</v>
-      </c>
+      <c r="C348" s="2"/>
       <c r="D348" s="2">
         <v>2.7610433101654053</v>
       </c>
-      <c r="E348" s="2">
-        <v>2.7239854335784912</v>
-      </c>
+      <c r="E348" s="2"/>
     </row>
     <row r="349">
       <c r="A349" s="1">
@@ -5161,15 +4193,11 @@
       <c r="B349" s="2">
         <v>3.0300476551055908</v>
       </c>
-      <c r="C349" s="2">
-        <v>3.0620341300964355</v>
-      </c>
+      <c r="C349" s="2"/>
       <c r="D349" s="2">
         <v>2.8130855560302734</v>
       </c>
-      <c r="E349" s="2">
-        <v>2.7667727470397949</v>
-      </c>
+      <c r="E349" s="2"/>
     </row>
     <row r="350">
       <c r="A350" s="1">
@@ -5178,15 +4206,11 @@
       <c r="B350" s="2">
         <v>2.9354543685913086</v>
       </c>
-      <c r="C350" s="2">
-        <v>2.8969204425811768</v>
-      </c>
+      <c r="C350" s="2"/>
       <c r="D350" s="2">
         <v>2.7753708362579346</v>
       </c>
-      <c r="E350" s="2">
-        <v>2.7313573360443115</v>
-      </c>
+      <c r="E350" s="2"/>
     </row>
     <row r="351">
       <c r="A351" s="1">
@@ -5195,15 +4219,11 @@
       <c r="B351" s="2">
         <v>2.3078649044036865</v>
       </c>
-      <c r="C351" s="2">
-        <v>2.2632787227630615</v>
-      </c>
+      <c r="C351" s="2"/>
       <c r="D351" s="2">
         <v>2.7796561717987061</v>
       </c>
-      <c r="E351" s="2">
-        <v>2.7332072257995605</v>
-      </c>
+      <c r="E351" s="2"/>
     </row>
     <row r="352">
       <c r="A352" s="1">
@@ -5212,15 +4232,11 @@
       <c r="B352" s="2">
         <v>2.6729929447174072</v>
       </c>
-      <c r="C352" s="2">
-        <v>2.6008579730987549</v>
-      </c>
+      <c r="C352" s="2"/>
       <c r="D352" s="2">
         <v>2.7898030281066895</v>
       </c>
-      <c r="E352" s="2">
-        <v>2.7425720691680908</v>
-      </c>
+      <c r="E352" s="2"/>
     </row>
     <row r="353">
       <c r="A353" s="1">
@@ -5229,15 +4245,11 @@
       <c r="B353" s="2">
         <v>2.7854316234588623</v>
       </c>
-      <c r="C353" s="2">
-        <v>2.5823018550872803</v>
-      </c>
+      <c r="C353" s="2"/>
       <c r="D353" s="2">
         <v>2.8075573444366455</v>
       </c>
-      <c r="E353" s="2">
-        <v>2.7558357715606689</v>
-      </c>
+      <c r="E353" s="2"/>
     </row>
     <row r="354">
       <c r="A354" s="1">
@@ -5246,15 +4258,11 @@
       <c r="B354" s="2">
         <v>2.9536609649658203</v>
       </c>
-      <c r="C354" s="2">
-        <v>2.8863835334777832</v>
-      </c>
+      <c r="C354" s="2"/>
       <c r="D354" s="2">
         <v>2.7602970600128174</v>
       </c>
-      <c r="E354" s="2">
-        <v>2.7048985958099365</v>
-      </c>
+      <c r="E354" s="2"/>
     </row>
     <row r="355">
       <c r="A355" s="1">
@@ -5263,15 +4271,11 @@
       <c r="B355" s="2">
         <v>2.6041765213012695</v>
       </c>
-      <c r="C355" s="2">
-        <v>2.5795581340789795</v>
-      </c>
+      <c r="C355" s="2"/>
       <c r="D355" s="2">
         <v>2.7145042419433594</v>
       </c>
-      <c r="E355" s="2">
-        <v>2.6621553897857666</v>
-      </c>
+      <c r="E355" s="2"/>
     </row>
     <row r="356">
       <c r="A356" s="1">
@@ -5280,15 +4284,11 @@
       <c r="B356" s="2">
         <v>2.9814133644104004</v>
       </c>
-      <c r="C356" s="2">
-        <v>3.0178754329681396</v>
-      </c>
+      <c r="C356" s="2"/>
       <c r="D356" s="2">
         <v>2.8583881855010986</v>
       </c>
-      <c r="E356" s="2">
-        <v>2.8158974647521973</v>
-      </c>
+      <c r="E356" s="2"/>
     </row>
     <row r="357">
       <c r="A357" s="1">
@@ -5297,15 +4297,11 @@
       <c r="B357" s="2">
         <v>2.996973991394043</v>
       </c>
-      <c r="C357" s="2">
-        <v>2.9133121967315674</v>
-      </c>
+      <c r="C357" s="2"/>
       <c r="D357" s="2">
         <v>2.8879735469818115</v>
       </c>
-      <c r="E357" s="2">
-        <v>2.8541431427001953</v>
-      </c>
+      <c r="E357" s="2"/>
     </row>
     <row r="358">
       <c r="A358" s="1">
@@ -5314,15 +4310,11 @@
       <c r="B358" s="2">
         <v>2.6047053337097168</v>
       </c>
-      <c r="C358" s="2">
-        <v>2.6035990715026855</v>
-      </c>
+      <c r="C358" s="2"/>
       <c r="D358" s="2">
         <v>2.8947820663452148</v>
       </c>
-      <c r="E358" s="2">
-        <v>2.894810676574707</v>
-      </c>
+      <c r="E358" s="2"/>
     </row>
     <row r="359">
       <c r="A359" s="1">
@@ -5331,15 +4323,11 @@
       <c r="B359" s="2">
         <v>2.5233175754547119</v>
       </c>
-      <c r="C359" s="2">
-        <v>2.5122323036193848</v>
-      </c>
+      <c r="C359" s="2"/>
       <c r="D359" s="2">
         <v>2.8767657279968262</v>
       </c>
-      <c r="E359" s="2">
-        <v>2.8895518779754639</v>
-      </c>
+      <c r="E359" s="2"/>
     </row>
     <row r="360">
       <c r="A360" s="1">
@@ -5348,15 +4336,11 @@
       <c r="B360" s="2">
         <v>3.6028206348419189</v>
       </c>
-      <c r="C360" s="2">
-        <v>3.6469566822052002</v>
-      </c>
+      <c r="C360" s="2"/>
       <c r="D360" s="2">
         <v>2.9705870151519775</v>
       </c>
-      <c r="E360" s="2">
-        <v>2.9755535125732422</v>
-      </c>
+      <c r="E360" s="2"/>
     </row>
     <row r="361">
       <c r="A361" s="1">
@@ -5365,15 +4349,11 @@
       <c r="B361" s="2">
         <v>2.9392609596252441</v>
       </c>
-      <c r="C361" s="2">
-        <v>2.9450697898864746</v>
-      </c>
+      <c r="C361" s="2"/>
       <c r="D361" s="2">
         <v>3.0329892635345459</v>
       </c>
-      <c r="E361" s="2">
-        <v>3.0107643604278564</v>
-      </c>
+      <c r="E361" s="2"/>
     </row>
     <row r="362">
       <c r="A362" s="1">
@@ -5382,15 +4362,11 @@
       <c r="B362" s="2">
         <v>2.8467082977294922</v>
       </c>
-      <c r="C362" s="2">
-        <v>2.9483096599578857</v>
-      </c>
+      <c r="C362" s="2"/>
       <c r="D362" s="2">
         <v>3.1134994029998779</v>
       </c>
-      <c r="E362" s="2">
-        <v>3.1039118766784668</v>
-      </c>
+      <c r="E362" s="2"/>
     </row>
     <row r="363">
       <c r="A363" s="1">
@@ -5399,15 +4375,11 @@
       <c r="B363" s="2">
         <v>2.7915153503417969</v>
       </c>
-      <c r="C363" s="2">
-        <v>2.8390543460845947</v>
-      </c>
+      <c r="C363" s="2"/>
       <c r="D363" s="2">
         <v>3.2506794929504395</v>
       </c>
-      <c r="E363" s="2">
-        <v>3.2312788963317871</v>
-      </c>
+      <c r="E363" s="2"/>
     </row>
     <row r="364">
       <c r="A364" s="1">
@@ -5416,15 +4388,11 @@
       <c r="B364" s="2">
         <v>3.4485676288604736</v>
       </c>
-      <c r="C364" s="2">
-        <v>3.3535723686218262</v>
-      </c>
+      <c r="C364" s="2"/>
       <c r="D364" s="2">
         <v>3.3929991722106934</v>
       </c>
-      <c r="E364" s="2">
-        <v>3.3799829483032227</v>
-      </c>
+      <c r="E364" s="2"/>
     </row>
     <row r="365">
       <c r="A365" s="1">
@@ -5433,15 +4401,11 @@
       <c r="B365" s="2">
         <v>3.5430328845977783</v>
       </c>
-      <c r="C365" s="2">
-        <v>3.334773063659668</v>
-      </c>
+      <c r="C365" s="2"/>
       <c r="D365" s="2">
         <v>3.3593947887420654</v>
       </c>
-      <c r="E365" s="2">
-        <v>3.3404409885406494</v>
-      </c>
+      <c r="E365" s="2"/>
     </row>
     <row r="366">
       <c r="A366" s="1">
@@ -5450,15 +4414,11 @@
       <c r="B366" s="2">
         <v>3.7215662002563477</v>
       </c>
-      <c r="C366" s="2">
-        <v>3.7516388893127441</v>
-      </c>
+      <c r="C366" s="2"/>
       <c r="D366" s="2">
         <v>3.4102058410644531</v>
       </c>
-      <c r="E366" s="2">
-        <v>3.390101432800293</v>
-      </c>
+      <c r="E366" s="2"/>
     </row>
     <row r="367">
       <c r="A367" s="1">
@@ -5467,15 +4427,11 @@
       <c r="B367" s="2">
         <v>3.8393266201019287</v>
       </c>
-      <c r="C367" s="2">
-        <v>3.7499027252197266</v>
-      </c>
+      <c r="C367" s="2"/>
       <c r="D367" s="2">
         <v>3.4632799625396729</v>
       </c>
-      <c r="E367" s="2">
-        <v>3.4421291351318359</v>
-      </c>
+      <c r="E367" s="2"/>
     </row>
     <row r="368">
       <c r="A368" s="1">
@@ -5484,15 +4440,11 @@
       <c r="B368" s="2">
         <v>3.8041937351226807</v>
       </c>
-      <c r="C368" s="2">
-        <v>3.8505692481994629</v>
-      </c>
+      <c r="C368" s="2"/>
       <c r="D368" s="2">
         <v>3.5386779308319092</v>
       </c>
-      <c r="E368" s="2">
-        <v>3.5119853019714355</v>
-      </c>
+      <c r="E368" s="2"/>
     </row>
     <row r="369">
       <c r="A369" s="1">
@@ -5501,15 +4453,11 @@
       <c r="B369" s="2">
         <v>3.3003807067871094</v>
       </c>
-      <c r="C369" s="2">
-        <v>3.2910780906677246</v>
-      </c>
+      <c r="C369" s="2"/>
       <c r="D369" s="2">
         <v>3.5326230525970459</v>
       </c>
-      <c r="E369" s="2">
-        <v>3.5205357074737549</v>
-      </c>
+      <c r="E369" s="2"/>
     </row>
     <row r="370">
       <c r="A370" s="1">
@@ -5518,15 +4466,11 @@
       <c r="B370" s="2">
         <v>3.396561861038208</v>
       </c>
-      <c r="C370" s="2">
-        <v>3.3920149803161621</v>
-      </c>
+      <c r="C370" s="2"/>
       <c r="D370" s="2">
         <v>3.5288946628570557</v>
       </c>
-      <c r="E370" s="2">
-        <v>3.5319557189941406</v>
-      </c>
+      <c r="E370" s="2"/>
     </row>
     <row r="371">
       <c r="A371" s="1">
@@ -5535,15 +4479,11 @@
       <c r="B371" s="2">
         <v>3.3243756294250488</v>
       </c>
-      <c r="C371" s="2">
-        <v>3.4165582656860352</v>
-      </c>
+      <c r="C371" s="2"/>
       <c r="D371" s="2">
         <v>3.5113959312438965</v>
       </c>
-      <c r="E371" s="2">
-        <v>3.5066101551055908</v>
-      </c>
+      <c r="E371" s="2"/>
     </row>
     <row r="372">
       <c r="A372" s="1">
@@ -5552,15 +4492,11 @@
       <c r="B372" s="2">
         <v>3.4700953960418701</v>
       </c>
-      <c r="C372" s="2">
-        <v>3.4677608013153076</v>
-      </c>
+      <c r="C372" s="2"/>
       <c r="D372" s="2">
         <v>3.473313570022583</v>
       </c>
-      <c r="E372" s="2">
-        <v>3.488717794418335</v>
-      </c>
+      <c r="E372" s="2"/>
     </row>
     <row r="373">
       <c r="A373" s="1">
@@ -5569,15 +4505,11 @@
       <c r="B373" s="2">
         <v>3.3940751552581787</v>
       </c>
-      <c r="C373" s="2">
-        <v>3.4305253028869629</v>
-      </c>
+      <c r="C373" s="2"/>
       <c r="D373" s="2">
         <v>3.4050359725952148</v>
       </c>
-      <c r="E373" s="2">
-        <v>3.4226438999176025</v>
-      </c>
+      <c r="E373" s="2"/>
     </row>
     <row r="374">
       <c r="A374" s="1">
@@ -5586,15 +4518,11 @@
       <c r="B374" s="2">
         <v>3.5094757080078125</v>
       </c>
-      <c r="C374" s="2">
-        <v>3.4375524520874023</v>
-      </c>
+      <c r="C374" s="2"/>
       <c r="D374" s="2">
         <v>3.419992208480835</v>
       </c>
-      <c r="E374" s="2">
-        <v>3.4432876110076904</v>
-      </c>
+      <c r="E374" s="2"/>
     </row>
     <row r="375">
       <c r="A375" s="1">
@@ -5603,15 +4531,11 @@
       <c r="B375" s="2">
         <v>3.564077615737915</v>
       </c>
-      <c r="C375" s="2">
-        <v>3.5235288143157959</v>
-      </c>
+      <c r="C375" s="2"/>
       <c r="D375" s="2">
         <v>3.4214012622833252</v>
       </c>
-      <c r="E375" s="2">
-        <v>3.456613302230835</v>
-      </c>
+      <c r="E375" s="2"/>
     </row>
     <row r="376">
       <c r="A376" s="1">
@@ -5620,15 +4544,11 @@
       <c r="B376" s="2">
         <v>3.4965860843658447</v>
       </c>
-      <c r="C376" s="2">
-        <v>3.5888712406158447</v>
-      </c>
+      <c r="C376" s="2"/>
       <c r="D376" s="2">
         <v>3.5204756259918213</v>
       </c>
-      <c r="E376" s="2">
-        <v>3.5570733547210693</v>
-      </c>
+      <c r="E376" s="2"/>
     </row>
     <row r="377">
       <c r="A377" s="1">
@@ -5637,15 +4557,11 @@
       <c r="B377" s="2">
         <v>3.189694881439209</v>
       </c>
-      <c r="C377" s="2">
-        <v>3.2559041976928711</v>
-      </c>
+      <c r="C377" s="2"/>
       <c r="D377" s="2">
         <v>3.4483969211578369</v>
       </c>
-      <c r="E377" s="2">
-        <v>3.4993071556091309</v>
-      </c>
+      <c r="E377" s="2"/>
     </row>
     <row r="378">
       <c r="A378" s="1">
@@ -5654,15 +4570,11 @@
       <c r="B378" s="2">
         <v>3.4349884986877441</v>
       </c>
-      <c r="C378" s="2">
-        <v>3.4768719673156738</v>
-      </c>
+      <c r="C378" s="2"/>
       <c r="D378" s="2">
         <v>3.4510953426361084</v>
       </c>
-      <c r="E378" s="2">
-        <v>3.4914674758911133</v>
-      </c>
+      <c r="E378" s="2"/>
     </row>
     <row r="379">
       <c r="A379" s="1">
@@ -5671,15 +4583,11 @@
       <c r="B379" s="2">
         <v>3.4092419147491455</v>
       </c>
-      <c r="C379" s="2">
-        <v>3.5119457244873047</v>
-      </c>
+      <c r="C379" s="2"/>
       <c r="D379" s="2">
         <v>3.4201765060424805</v>
       </c>
-      <c r="E379" s="2">
-        <v>3.4689197540283203</v>
-      </c>
+      <c r="E379" s="2"/>
     </row>
     <row r="380">
       <c r="A380" s="1">
@@ -5688,15 +4596,11 @@
       <c r="B380" s="2">
         <v>4.2160458564758301</v>
       </c>
-      <c r="C380" s="2">
-        <v>4.3206992149353027</v>
-      </c>
+      <c r="C380" s="2"/>
       <c r="D380" s="2">
         <v>3.3299660682678223</v>
       </c>
-      <c r="E380" s="2">
-        <v>3.3825056552886963</v>
-      </c>
+      <c r="E380" s="2"/>
     </row>
     <row r="381">
       <c r="A381" s="1">
@@ -5705,15 +4609,11 @@
       <c r="B381" s="2">
         <v>2.8213868141174316</v>
       </c>
-      <c r="C381" s="2">
-        <v>2.9478662014007568</v>
-      </c>
+      <c r="C381" s="2"/>
       <c r="D381" s="2">
         <v>3.3169794082641602</v>
       </c>
-      <c r="E381" s="2">
-        <v>3.3722028732299805</v>
-      </c>
+      <c r="E381" s="2"/>
     </row>
     <row r="382">
       <c r="A382" s="1">
@@ -5722,15 +4622,11 @@
       <c r="B382" s="2">
         <v>3.4183616638183594</v>
       </c>
-      <c r="C382" s="2">
-        <v>3.359966516494751</v>
-      </c>
+      <c r="C382" s="2"/>
       <c r="D382" s="2">
         <v>3.3591029644012451</v>
       </c>
-      <c r="E382" s="2">
-        <v>3.3895571231842041</v>
-      </c>
+      <c r="E382" s="2"/>
     </row>
     <row r="383">
       <c r="A383" s="1">
@@ -5739,15 +4635,11 @@
       <c r="B383" s="2">
         <v>3.2312054634094238</v>
       </c>
-      <c r="C383" s="2">
-        <v>3.234623908996582</v>
-      </c>
+      <c r="C383" s="2"/>
       <c r="D383" s="2">
         <v>3.3747761249542236</v>
       </c>
-      <c r="E383" s="2">
-        <v>3.3976032733917236</v>
-      </c>
+      <c r="E383" s="2"/>
     </row>
     <row r="384">
       <c r="A384" s="1">
@@ -5756,15 +4648,11 @@
       <c r="B384" s="2">
         <v>2.7521841526031494</v>
       </c>
-      <c r="C384" s="2">
-        <v>2.7458021640777588</v>
-      </c>
+      <c r="C384" s="2"/>
       <c r="D384" s="2">
         <v>3.3357021808624268</v>
       </c>
-      <c r="E384" s="2">
-        <v>3.3456795215606689</v>
-      </c>
+      <c r="E384" s="2"/>
     </row>
     <row r="385">
       <c r="A385" s="1">
@@ -5773,15 +4661,11 @@
       <c r="B385" s="2">
         <v>3.3797051906585693</v>
       </c>
-      <c r="C385" s="2">
-        <v>3.496145486831665</v>
-      </c>
+      <c r="C385" s="2"/>
       <c r="D385" s="2">
         <v>3.2344791889190674</v>
       </c>
-      <c r="E385" s="2">
-        <v>3.2386133670806885</v>
-      </c>
+      <c r="E385" s="2"/>
     </row>
     <row r="386">
       <c r="A386" s="1">
@@ -5790,15 +4674,11 @@
       <c r="B386" s="2">
         <v>3.5688071250915527</v>
       </c>
-      <c r="C386" s="2">
-        <v>3.4120936393737793</v>
-      </c>
+      <c r="C386" s="2"/>
       <c r="D386" s="2">
         <v>3.2539050579071045</v>
       </c>
-      <c r="E386" s="2">
-        <v>3.2426905632019043</v>
-      </c>
+      <c r="E386" s="2"/>
     </row>
     <row r="387">
       <c r="A387" s="1">
@@ -5807,15 +4687,11 @@
       <c r="B387" s="2">
         <v>3.5760478973388672</v>
       </c>
-      <c r="C387" s="2">
-        <v>3.5492875576019287</v>
-      </c>
+      <c r="C387" s="2"/>
       <c r="D387" s="2">
         <v>3.152677059173584</v>
       </c>
-      <c r="E387" s="2">
-        <v>3.1566767692565918</v>
-      </c>
+      <c r="E387" s="2"/>
     </row>
     <row r="388">
       <c r="A388" s="1">
@@ -5824,15 +4700,11 @@
       <c r="B388" s="2">
         <v>3.0575752258300781</v>
       </c>
-      <c r="C388" s="2">
-        <v>3.0446305274963379</v>
-      </c>
+      <c r="C388" s="2"/>
       <c r="D388" s="2">
         <v>3.1137194633483887</v>
       </c>
-      <c r="E388" s="2">
-        <v>3.1057515144348145</v>
-      </c>
+      <c r="E388" s="2"/>
     </row>
     <row r="389">
       <c r="A389" s="1">
@@ -5841,15 +4713,11 @@
       <c r="B389" s="2">
         <v>3.3050394058227539</v>
       </c>
-      <c r="C389" s="2">
-        <v>3.3571047782897949</v>
-      </c>
+      <c r="C389" s="2"/>
       <c r="D389" s="2">
         <v>3.1617593765258789</v>
       </c>
-      <c r="E389" s="2">
-        <v>3.1545560359954834</v>
-      </c>
+      <c r="E389" s="2"/>
     </row>
     <row r="390">
       <c r="A390" s="1">
@@ -5858,15 +4726,11 @@
       <c r="B390" s="2">
         <v>2.9962191581726074</v>
       </c>
-      <c r="C390" s="2">
-        <v>2.9845612049102783</v>
-      </c>
+      <c r="C390" s="2"/>
       <c r="D390" s="2">
         <v>3.0901715755462646</v>
       </c>
-      <c r="E390" s="2">
-        <v>3.0731477737426758</v>
-      </c>
+      <c r="E390" s="2"/>
     </row>
     <row r="391">
       <c r="A391" s="1">
@@ -5875,15 +4739,11 @@
       <c r="B391" s="2">
         <v>2.5073091983795166</v>
       </c>
-      <c r="C391" s="2">
-        <v>2.5858418941497803</v>
-      </c>
+      <c r="C391" s="2"/>
       <c r="D391" s="2">
         <v>3.0425910949707031</v>
       </c>
-      <c r="E391" s="2">
-        <v>2.9924452304840088</v>
-      </c>
+      <c r="E391" s="2"/>
     </row>
     <row r="392">
       <c r="A392" s="1">
@@ -5892,15 +4752,11 @@
       <c r="B392" s="2">
         <v>2.8805880546569824</v>
       </c>
-      <c r="C392" s="2">
-        <v>2.7762959003448486</v>
-      </c>
+      <c r="C392" s="2"/>
       <c r="D392" s="2">
         <v>2.9899451732635498</v>
       </c>
-      <c r="E392" s="2">
-        <v>2.9411163330078125</v>
-      </c>
+      <c r="E392" s="2"/>
     </row>
     <row r="393">
       <c r="A393" s="1">
@@ -5909,15 +4765,11 @@
       <c r="B393" s="2">
         <v>3.1845428943634033</v>
       </c>
-      <c r="C393" s="2">
-        <v>3.1850430965423584</v>
-      </c>
+      <c r="C393" s="2"/>
       <c r="D393" s="2">
         <v>3.0211079120635986</v>
       </c>
-      <c r="E393" s="2">
-        <v>2.9696216583251953</v>
-      </c>
+      <c r="E393" s="2"/>
     </row>
     <row r="394">
       <c r="A394" s="1">
@@ -5926,15 +4778,11 @@
       <c r="B394" s="2">
         <v>2.7354156970977783</v>
       </c>
-      <c r="C394" s="2">
-        <v>2.7634718418121338</v>
-      </c>
+      <c r="C394" s="2"/>
       <c r="D394" s="2">
         <v>2.988760232925415</v>
       </c>
-      <c r="E394" s="2">
-        <v>2.9342961311340332</v>
-      </c>
+      <c r="E394" s="2"/>
     </row>
     <row r="395">
       <c r="A395" s="1">
@@ -5943,15 +4791,11 @@
       <c r="B395" s="2">
         <v>3.1405818462371826</v>
       </c>
-      <c r="C395" s="2">
-        <v>2.6857707500457764</v>
-      </c>
+      <c r="C395" s="2"/>
       <c r="D395" s="2">
         <v>2.959986686706543</v>
       </c>
-      <c r="E395" s="2">
-        <v>2.900881290435791</v>
-      </c>
+      <c r="E395" s="2"/>
     </row>
     <row r="396">
       <c r="A396" s="1">
@@ -5960,15 +4804,11 @@
       <c r="B396" s="2">
         <v>3.1022353172302246</v>
       </c>
-      <c r="C396" s="2">
-        <v>3.0873270034790039</v>
-      </c>
+      <c r="C396" s="2"/>
       <c r="D396" s="2">
         <v>3.0459551811218262</v>
       </c>
-      <c r="E396" s="2">
-        <v>2.9706552028656006</v>
-      </c>
+      <c r="E396" s="2"/>
     </row>
     <row r="397">
       <c r="A397" s="1">
@@ -5977,15 +4817,11 @@
       <c r="B397" s="2">
         <v>3.3380398750305176</v>
       </c>
-      <c r="C397" s="2">
-        <v>3.3011775016784668</v>
-      </c>
+      <c r="C397" s="2"/>
       <c r="D397" s="2">
         <v>3.10400390625</v>
       </c>
-      <c r="E397" s="2">
-        <v>3.0373194217681885</v>
-      </c>
+      <c r="E397" s="2"/>
     </row>
     <row r="398">
       <c r="A398" s="1">
@@ -5994,15 +4830,11 @@
       <c r="B398" s="2">
         <v>3.0139105319976807</v>
       </c>
-      <c r="C398" s="2">
-        <v>3.0391755104064941</v>
-      </c>
+      <c r="C398" s="2"/>
       <c r="D398" s="2">
         <v>3.0988743305206299</v>
       </c>
-      <c r="E398" s="2">
-        <v>3.0432610511779785</v>
-      </c>
+      <c r="E398" s="2"/>
     </row>
     <row r="399">
       <c r="A399" s="1">
@@ -6011,15 +4843,11 @@
       <c r="B399" s="2">
         <v>2.7372558116912842</v>
       </c>
-      <c r="C399" s="2">
-        <v>2.6838278770446777</v>
-      </c>
+      <c r="C399" s="2"/>
       <c r="D399" s="2">
         <v>3.1548702716827393</v>
       </c>
-      <c r="E399" s="2">
-        <v>3.0892667770385742</v>
-      </c>
+      <c r="E399" s="2"/>
     </row>
     <row r="400">
       <c r="A400" s="1">
@@ -6028,15 +4856,11 @@
       <c r="B400" s="2">
         <v>3.2810258865356445</v>
       </c>
-      <c r="C400" s="2">
-        <v>3.2138066291809082</v>
-      </c>
+      <c r="C400" s="2"/>
       <c r="D400" s="2">
         <v>3.1094582080841064</v>
       </c>
-      <c r="E400" s="2">
-        <v>3.0900681018829346</v>
-      </c>
+      <c r="E400" s="2"/>
     </row>
     <row r="401">
       <c r="A401" s="1">
@@ -6045,15 +4869,11 @@
       <c r="B401" s="2">
         <v>3.4030265808105469</v>
       </c>
-      <c r="C401" s="2">
-        <v>3.376274585723877</v>
-      </c>
+      <c r="C401" s="2"/>
       <c r="D401" s="2">
         <v>3.1314268112182617</v>
       </c>
-      <c r="E401" s="2">
-        <v>3.1196670532226562</v>
-      </c>
+      <c r="E401" s="2"/>
     </row>
     <row r="402">
       <c r="A402" s="1">
@@ -6062,15 +4882,11 @@
       <c r="B402" s="2">
         <v>3.1383779048919678</v>
       </c>
-      <c r="C402" s="2">
-        <v>3.2385175228118896</v>
-      </c>
+      <c r="C402" s="2"/>
       <c r="D402" s="2">
         <v>3.0907306671142578</v>
       </c>
-      <c r="E402" s="2">
-        <v>3.0787234306335449</v>
-      </c>
+      <c r="E402" s="2"/>
     </row>
     <row r="403">
       <c r="A403" s="1">
@@ -6079,15 +4895,11 @@
       <c r="B403" s="2">
         <v>3.2393794059753418</v>
       </c>
-      <c r="C403" s="2">
-        <v>3.1775233745574951</v>
-      </c>
+      <c r="C403" s="2"/>
       <c r="D403" s="2">
         <v>3.071422815322876</v>
       </c>
-      <c r="E403" s="2">
-        <v>3.0522520542144775</v>
-      </c>
+      <c r="E403" s="2"/>
     </row>
     <row r="404">
       <c r="A404" s="1">
@@ -6096,15 +4908,11 @@
       <c r="B404" s="2">
         <v>2.7318727970123291</v>
       </c>
-      <c r="C404" s="2">
-        <v>2.692983865737915</v>
-      </c>
+      <c r="C404" s="2"/>
       <c r="D404" s="2">
         <v>3.0552563667297363</v>
       </c>
-      <c r="E404" s="2">
-        <v>3.0309009552001953</v>
-      </c>
+      <c r="E404" s="2"/>
     </row>
     <row r="405">
       <c r="A405" s="1">
@@ -6113,15 +4921,11 @@
       <c r="B405" s="2">
         <v>3.2999529838562012</v>
       </c>
-      <c r="C405" s="2">
-        <v>3.3537156581878662</v>
-      </c>
+      <c r="C405" s="2"/>
       <c r="D405" s="2">
         <v>3.0121161937713623</v>
       </c>
-      <c r="E405" s="2">
-        <v>3.0057613849639893</v>
-      </c>
+      <c r="E405" s="2"/>
     </row>
     <row r="406">
       <c r="A406" s="1">
@@ -6130,15 +4934,11 @@
       <c r="B406" s="2">
         <v>2.9717750549316406</v>
       </c>
-      <c r="C406" s="2">
-        <v>2.932685375213623</v>
-      </c>
+      <c r="C406" s="2"/>
       <c r="D406" s="2">
         <v>2.943411111831665</v>
       </c>
-      <c r="E406" s="2">
-        <v>2.9412722587585449</v>
-      </c>
+      <c r="E406" s="2"/>
     </row>
     <row r="407">
       <c r="A407" s="1">
@@ -6147,15 +4947,11 @@
       <c r="B407" s="2">
         <v>2.8401391506195068</v>
       </c>
-      <c r="C407" s="2">
-        <v>2.8009328842163086</v>
-      </c>
+      <c r="C407" s="2"/>
       <c r="D407" s="2">
         <v>2.9322686195373535</v>
       </c>
-      <c r="E407" s="2">
-        <v>2.9244832992553711</v>
-      </c>
+      <c r="E407" s="2"/>
     </row>
     <row r="408">
       <c r="A408" s="1">
@@ -6164,15 +4960,11 @@
       <c r="B408" s="2">
         <v>2.5917577743530273</v>
       </c>
-      <c r="C408" s="2">
-        <v>2.4916689395904541</v>
-      </c>
+      <c r="C408" s="2"/>
       <c r="D408" s="2">
         <v>2.9009478092193604</v>
       </c>
-      <c r="E408" s="2">
-        <v>2.9000484943389893</v>
-      </c>
+      <c r="E408" s="2"/>
     </row>
     <row r="409">
       <c r="A409" s="1">
@@ -6181,15 +4973,11 @@
       <c r="B409" s="2">
         <v>2.8927643299102783</v>
       </c>
-      <c r="C409" s="2">
-        <v>2.9875497817993164</v>
-      </c>
+      <c r="C409" s="2"/>
       <c r="D409" s="2">
         <v>2.9216787815093994</v>
       </c>
-      <c r="E409" s="2">
-        <v>2.9256777763366699</v>
-      </c>
+      <c r="E409" s="2"/>
     </row>
     <row r="410">
       <c r="A410" s="1">
@@ -6198,15 +4986,11 @@
       <c r="B410" s="2">
         <v>2.7846798896789551</v>
       </c>
-      <c r="C410" s="2">
-        <v>2.7958729267120361</v>
-      </c>
+      <c r="C410" s="2"/>
       <c r="D410" s="2">
         <v>2.8747327327728271</v>
       </c>
-      <c r="E410" s="2">
-        <v>2.8706550598144531</v>
-      </c>
+      <c r="E410" s="2"/>
     </row>
     <row r="411">
       <c r="A411" s="1">
@@ -6215,15 +4999,11 @@
       <c r="B411" s="2">
         <v>3.0380964279174805</v>
       </c>
-      <c r="C411" s="2">
-        <v>3.0874159336090088</v>
-      </c>
+      <c r="C411" s="2"/>
       <c r="D411" s="2">
         <v>2.8957514762878418</v>
       </c>
-      <c r="E411" s="2">
-        <v>2.8893253803253174</v>
-      </c>
+      <c r="E411" s="2"/>
     </row>
     <row r="412">
       <c r="A412" s="1">
@@ -6232,15 +5012,11 @@
       <c r="B412" s="2">
         <v>2.9574911594390869</v>
       </c>
-      <c r="C412" s="2">
-        <v>2.9576101303100586</v>
-      </c>
+      <c r="C412" s="2"/>
       <c r="D412" s="2">
         <v>2.9098155498504639</v>
       </c>
-      <c r="E412" s="2">
-        <v>2.8958220481872559</v>
-      </c>
+      <c r="E412" s="2"/>
     </row>
     <row r="413">
       <c r="A413" s="1">
@@ -6249,15 +5025,11 @@
       <c r="B413" s="2">
         <v>2.9184513092041016</v>
       </c>
-      <c r="C413" s="2">
-        <v>2.9236478805541992</v>
-      </c>
+      <c r="C413" s="2"/>
       <c r="D413" s="2">
         <v>2.9318664073944092</v>
       </c>
-      <c r="E413" s="2">
-        <v>2.9231042861938477</v>
-      </c>
+      <c r="E413" s="2"/>
     </row>
     <row r="414">
       <c r="A414" s="1">
@@ -6266,15 +5038,11 @@
       <c r="B414" s="2">
         <v>2.8774399757385254</v>
       </c>
-      <c r="C414" s="2">
-        <v>2.8585107326507568</v>
-      </c>
+      <c r="C414" s="2"/>
       <c r="D414" s="2">
         <v>2.9796748161315918</v>
       </c>
-      <c r="E414" s="2">
-        <v>2.9724504947662354</v>
-      </c>
+      <c r="E414" s="2"/>
     </row>
     <row r="415">
       <c r="A415" s="1">
@@ -6283,15 +5051,11 @@
       <c r="B415" s="2">
         <v>3.1609432697296143</v>
       </c>
-      <c r="C415" s="2">
-        <v>3.1007201671600342</v>
-      </c>
+      <c r="C415" s="2"/>
       <c r="D415" s="2">
         <v>3.0407562255859375</v>
       </c>
-      <c r="E415" s="2">
-        <v>3.0319480895996094</v>
-      </c>
+      <c r="E415" s="2"/>
     </row>
     <row r="416">
       <c r="A416" s="1">
@@ -6300,15 +5064,11 @@
       <c r="B416" s="2">
         <v>2.9667150974273682</v>
       </c>
-      <c r="C416" s="2">
-        <v>2.8594017028808594</v>
-      </c>
+      <c r="C416" s="2"/>
       <c r="D416" s="2">
         <v>3.0985720157623291</v>
       </c>
-      <c r="E416" s="2">
-        <v>3.0886032581329346</v>
-      </c>
+      <c r="E416" s="2"/>
     </row>
     <row r="417">
       <c r="A417" s="1">
@@ -6317,15 +5077,11 @@
       <c r="B417" s="2">
         <v>2.7902162075042725</v>
       </c>
-      <c r="C417" s="2">
-        <v>2.7372093200683594</v>
-      </c>
+      <c r="C417" s="2"/>
       <c r="D417" s="2">
         <v>3.0900552272796631</v>
       </c>
-      <c r="E417" s="2">
-        <v>3.0837175846099854</v>
-      </c>
+      <c r="E417" s="2"/>
     </row>
     <row r="418">
       <c r="A418" s="1">
@@ -6334,15 +5090,11 @@
       <c r="B418" s="2">
         <v>3.3230390548706055</v>
       </c>
-      <c r="C418" s="2">
-        <v>3.4316658973693848</v>
-      </c>
+      <c r="C418" s="2"/>
       <c r="D418" s="2">
         <v>3.1378860473632812</v>
       </c>
-      <c r="E418" s="2">
-        <v>3.1390671730041504</v>
-      </c>
+      <c r="E418" s="2"/>
     </row>
     <row r="419">
       <c r="A419" s="1">
@@ -6351,15 +5103,11 @@
       <c r="B419" s="2">
         <v>3.3344135284423828</v>
       </c>
-      <c r="C419" s="2">
-        <v>3.3313517570495605</v>
-      </c>
+      <c r="C419" s="2"/>
       <c r="D419" s="2">
         <v>3.1894783973693848</v>
       </c>
-      <c r="E419" s="2">
-        <v>3.2038033008575439</v>
-      </c>
+      <c r="E419" s="2"/>
     </row>
     <row r="420">
       <c r="A420" s="1">
@@ -6368,15 +5116,11 @@
       <c r="B420" s="2">
         <v>3.5584390163421631</v>
       </c>
-      <c r="C420" s="2">
-        <v>3.5973122119903564</v>
-      </c>
+      <c r="C420" s="2"/>
       <c r="D420" s="2">
         <v>3.1751704216003418</v>
       </c>
-      <c r="E420" s="2">
-        <v>3.1992294788360596</v>
-      </c>
+      <c r="E420" s="2"/>
     </row>
     <row r="421">
       <c r="A421" s="1">
@@ -6385,15 +5129,11 @@
       <c r="B421" s="2">
         <v>2.8808391094207764</v>
       </c>
-      <c r="C421" s="2">
-        <v>2.9136388301849365</v>
-      </c>
+      <c r="C421" s="2"/>
       <c r="D421" s="2">
         <v>3.2250933647155762</v>
       </c>
-      <c r="E421" s="2">
-        <v>3.2470576763153076</v>
-      </c>
+      <c r="E421" s="2"/>
     </row>
     <row r="422">
       <c r="A422" s="1">
@@ -6402,15 +5142,11 @@
       <c r="B422" s="2">
         <v>3.3489301204681396</v>
       </c>
-      <c r="C422" s="2">
-        <v>3.4217934608459473</v>
-      </c>
+      <c r="C422" s="2"/>
       <c r="D422" s="2">
         <v>3.2920436859130859</v>
       </c>
-      <c r="E422" s="2">
-        <v>3.3182578086853027</v>
-      </c>
+      <c r="E422" s="2"/>
     </row>
     <row r="423">
       <c r="A423" s="1">
@@ -6419,15 +5155,11 @@
       <c r="B423" s="2">
         <v>3.3417708873748779</v>
       </c>
-      <c r="C423" s="2">
-        <v>3.4411358833312988</v>
-      </c>
+      <c r="C423" s="2"/>
       <c r="D423" s="2">
         <v>3.2705795764923096</v>
       </c>
-      <c r="E423" s="2">
-        <v>3.2771387100219727</v>
-      </c>
+      <c r="E423" s="2"/>
     </row>
     <row r="424">
       <c r="A424" s="1">
@@ -6436,15 +5168,11 @@
       <c r="B424" s="2">
         <v>3.0321712493896484</v>
       </c>
-      <c r="C424" s="2">
-        <v>3.0595571994781494</v>
-      </c>
+      <c r="C424" s="2"/>
       <c r="D424" s="2">
         <v>3.1837081909179688</v>
       </c>
-      <c r="E424" s="2">
-        <v>3.1794364452362061</v>
-      </c>
+      <c r="E424" s="2"/>
     </row>
     <row r="425">
       <c r="A425" s="1">
@@ -6453,15 +5181,11 @@
       <c r="B425" s="2">
         <v>3.4160213470458984</v>
       </c>
-      <c r="C425" s="2">
-        <v>3.2898547649383545</v>
-      </c>
+      <c r="C425" s="2"/>
       <c r="D425" s="2">
         <v>3.1636965274810791</v>
       </c>
-      <c r="E425" s="2">
-        <v>3.1508140563964844</v>
-      </c>
+      <c r="E425" s="2"/>
     </row>
     <row r="426">
       <c r="A426" s="1">
@@ -6470,15 +5194,11 @@
       <c r="B426" s="2">
         <v>3.3927681446075439</v>
       </c>
-      <c r="C426" s="2">
-        <v>3.3780109882354736</v>
-      </c>
+      <c r="C426" s="2"/>
       <c r="D426" s="2">
         <v>3.1743838787078857</v>
       </c>
-      <c r="E426" s="2">
-        <v>3.154400110244751</v>
-      </c>
+      <c r="E426" s="2"/>
     </row>
     <row r="427">
       <c r="A427" s="1">
@@ -6487,15 +5207,11 @@
       <c r="B427" s="2">
         <v>3.1298623085021973</v>
       </c>
-      <c r="C427" s="2">
-        <v>3.0615935325622559</v>
-      </c>
+      <c r="C427" s="2"/>
       <c r="D427" s="2">
         <v>3.1469569206237793</v>
       </c>
-      <c r="E427" s="2">
-        <v>3.1265749931335449</v>
-      </c>
+      <c r="E427" s="2"/>
     </row>
     <row r="428">
       <c r="A428" s="1">
@@ -6504,15 +5220,11 @@
       <c r="B428" s="2">
         <v>2.5525708198547363</v>
       </c>
-      <c r="C428" s="2">
-        <v>2.4520313739776611</v>
-      </c>
+      <c r="C428" s="2"/>
       <c r="D428" s="2">
         <v>3.1523776054382324</v>
       </c>
-      <c r="E428" s="2">
-        <v>3.1057472229003906</v>
-      </c>
+      <c r="E428" s="2"/>
     </row>
     <row r="429">
       <c r="A429" s="1">
@@ -6521,15 +5233,11 @@
       <c r="B429" s="2">
         <v>3.3783354759216309</v>
       </c>
-      <c r="C429" s="2">
-        <v>3.3397109508514404</v>
-      </c>
+      <c r="C429" s="2"/>
       <c r="D429" s="2">
         <v>3.1923325061798096</v>
       </c>
-      <c r="E429" s="2">
-        <v>3.1393229961395264</v>
-      </c>
+      <c r="E429" s="2"/>
     </row>
     <row r="430">
       <c r="A430" s="1">
@@ -6538,15 +5246,11 @@
       <c r="B430" s="2">
         <v>2.9770252704620361</v>
       </c>
-      <c r="C430" s="2">
-        <v>2.9459128379821777</v>
-      </c>
+      <c r="C430" s="2"/>
       <c r="D430" s="2">
         <v>3.1372289657592773</v>
       </c>
-      <c r="E430" s="2">
-        <v>3.0946087837219238</v>
-      </c>
+      <c r="E430" s="2"/>
     </row>
     <row r="431">
       <c r="A431" s="1">
@@ -6555,15 +5259,11 @@
       <c r="B431" s="2">
         <v>3.102086067199707</v>
       </c>
-      <c r="C431" s="2">
-        <v>3.1713683605194092</v>
-      </c>
+      <c r="C431" s="2"/>
       <c r="D431" s="2">
         <v>3.1095607280731201</v>
       </c>
-      <c r="E431" s="2">
-        <v>3.0453031063079834</v>
-      </c>
+      <c r="E431" s="2"/>
     </row>
     <row r="432">
       <c r="A432" s="1">
@@ -6572,15 +5272,11 @@
       <c r="B432" s="2">
         <v>3.3905570507049561</v>
       </c>
-      <c r="C432" s="2">
-        <v>3.2536852359771729</v>
-      </c>
+      <c r="C432" s="2"/>
       <c r="D432" s="2">
         <v>3.101276159286499</v>
       </c>
-      <c r="E432" s="2">
-        <v>3.0502133369445801</v>
-      </c>
+      <c r="E432" s="2"/>
     </row>
     <row r="433">
       <c r="A433" s="1">
@@ -6589,15 +5285,11 @@
       <c r="B433" s="2">
         <v>3.391765832901001</v>
       </c>
-      <c r="C433" s="2">
-        <v>3.3617393970489502</v>
-      </c>
+      <c r="C433" s="2"/>
       <c r="D433" s="2">
         <v>3.146780252456665</v>
       </c>
-      <c r="E433" s="2">
-        <v>3.0986473560333252</v>
-      </c>
+      <c r="E433" s="2"/>
     </row>
     <row r="434">
       <c r="A434" s="1">
@@ -6606,15 +5298,11 @@
       <c r="B434" s="2">
         <v>2.9200890064239502</v>
       </c>
-      <c r="C434" s="2">
-        <v>2.8874256610870361</v>
-      </c>
+      <c r="C434" s="2"/>
       <c r="D434" s="2">
         <v>3.1014249324798584</v>
       </c>
-      <c r="E434" s="2">
-        <v>3.0575225353240967</v>
-      </c>
+      <c r="E434" s="2"/>
     </row>
     <row r="435">
       <c r="A435" s="1">
@@ -6623,15 +5311,11 @@
       <c r="B435" s="2">
         <v>3.1437547206878662</v>
       </c>
-      <c r="C435" s="2">
-        <v>2.9342606067657471</v>
-      </c>
+      <c r="C435" s="2"/>
       <c r="D435" s="2">
         <v>3.1049909591674805</v>
       </c>
-      <c r="E435" s="2">
-        <v>3.0566942691802979</v>
-      </c>
+      <c r="E435" s="2"/>
     </row>
     <row r="436">
       <c r="A436" s="1">
@@ -6640,15 +5324,11 @@
       <c r="B436" s="2">
         <v>3.0553004741668701</v>
       </c>
-      <c r="C436" s="2">
-        <v>3.105785608291626</v>
-      </c>
+      <c r="C436" s="2"/>
       <c r="D436" s="2">
         <v>3.0878763198852539</v>
       </c>
-      <c r="E436" s="2">
-        <v>3.0363969802856445</v>
-      </c>
+      <c r="E436" s="2"/>
     </row>
     <row r="437">
       <c r="A437" s="1">
@@ -6657,15 +5337,11 @@
       <c r="B437" s="2">
         <v>2.9621086120605469</v>
       </c>
-      <c r="C437" s="2">
-        <v>2.8879373073577881</v>
-      </c>
+      <c r="C437" s="2"/>
       <c r="D437" s="2">
         <v>3.0275809764862061</v>
       </c>
-      <c r="E437" s="2">
-        <v>2.9763236045837402</v>
-      </c>
+      <c r="E437" s="2"/>
     </row>
     <row r="438">
       <c r="A438" s="1">
@@ -6674,15 +5350,11 @@
       <c r="B438" s="2">
         <v>2.9701380729675293</v>
       </c>
-      <c r="C438" s="2">
-        <v>2.9695887565612793</v>
-      </c>
+      <c r="C438" s="2"/>
       <c r="D438" s="2">
         <v>2.940532922744751</v>
       </c>
-      <c r="E438" s="2">
-        <v>2.8745687007904053</v>
-      </c>
+      <c r="E438" s="2"/>
     </row>
     <row r="439">
       <c r="A439" s="1">
@@ -6691,15 +5363,11 @@
       <c r="B439" s="2">
         <v>3.0091185569763184</v>
       </c>
-      <c r="C439" s="2">
-        <v>2.9384584426879883</v>
-      </c>
+      <c r="C439" s="2"/>
       <c r="D439" s="2">
         <v>2.9111831188201904</v>
       </c>
-      <c r="E439" s="2">
-        <v>2.853034496307373</v>
-      </c>
+      <c r="E439" s="2"/>
     </row>
     <row r="440">
       <c r="A440" s="1">
@@ -6708,15 +5376,11 @@
       <c r="B440" s="2">
         <v>2.9480540752410889</v>
       </c>
-      <c r="C440" s="2">
-        <v>2.9886913299560547</v>
-      </c>
+      <c r="C440" s="2"/>
       <c r="D440" s="2">
         <v>2.8712742328643799</v>
       </c>
-      <c r="E440" s="2">
-        <v>2.8347241878509521</v>
-      </c>
+      <c r="E440" s="2"/>
     </row>
     <row r="441">
       <c r="A441" s="1">
@@ -6725,15 +5389,11 @@
       <c r="B441" s="2">
         <v>2.8479001522064209</v>
       </c>
-      <c r="C441" s="2">
-        <v>2.7130262851715088</v>
-      </c>
+      <c r="C441" s="2"/>
       <c r="D441" s="2">
         <v>2.8171241283416748</v>
       </c>
-      <c r="E441" s="2">
-        <v>2.769498348236084</v>
-      </c>
+      <c r="E441" s="2"/>
     </row>
     <row r="442">
       <c r="A442" s="1">
@@ -6742,15 +5402,11 @@
       <c r="B442" s="2">
         <v>2.6083316802978516</v>
       </c>
-      <c r="C442" s="2">
-        <v>2.4459447860717773</v>
-      </c>
+      <c r="C442" s="2"/>
       <c r="D442" s="2">
         <v>2.7841508388519287</v>
       </c>
-      <c r="E442" s="2">
-        <v>2.7478821277618408</v>
-      </c>
+      <c r="E442" s="2"/>
     </row>
     <row r="443">
       <c r="A443" s="1">
@@ -6759,15 +5415,11 @@
       <c r="B443" s="2">
         <v>2.6559422016143799</v>
       </c>
-      <c r="C443" s="2">
-        <v>2.693617582321167</v>
-      </c>
+      <c r="C443" s="2"/>
       <c r="D443" s="2">
         <v>2.7631773948669434</v>
       </c>
-      <c r="E443" s="2">
-        <v>2.7307429313659668</v>
-      </c>
+      <c r="E443" s="2"/>
     </row>
     <row r="444">
       <c r="A444" s="1">
@@ -6776,15 +5428,11 @@
       <c r="B444" s="2">
         <v>2.7845733165740967</v>
       </c>
-      <c r="C444" s="2">
-        <v>2.7694683074951172</v>
-      </c>
+      <c r="C444" s="2"/>
       <c r="D444" s="2">
         <v>2.736886739730835</v>
       </c>
-      <c r="E444" s="2">
-        <v>2.7111306190490723</v>
-      </c>
+      <c r="E444" s="2"/>
     </row>
     <row r="445">
       <c r="A445" s="1">
@@ -6793,15 +5441,11 @@
       <c r="B445" s="2">
         <v>2.5679512023925781</v>
       </c>
-      <c r="C445" s="2">
-        <v>2.5187513828277588</v>
-      </c>
+      <c r="C445" s="2"/>
       <c r="D445" s="2">
         <v>2.6898953914642334</v>
       </c>
-      <c r="E445" s="2">
-        <v>2.6612987518310547</v>
-      </c>
+      <c r="E445" s="2"/>
     </row>
     <row r="446">
       <c r="A446" s="1">
@@ -6810,15 +5454,11 @@
       <c r="B446" s="2">
         <v>2.6653487682342529</v>
       </c>
-      <c r="C446" s="2">
-        <v>2.6933925151824951</v>
-      </c>
+      <c r="C446" s="2"/>
       <c r="D446" s="2">
         <v>2.6980898380279541</v>
       </c>
-      <c r="E446" s="2">
-        <v>2.6678330898284912</v>
-      </c>
+      <c r="E446" s="2"/>
     </row>
     <row r="447">
       <c r="A447" s="1">
@@ -6827,15 +5467,11 @@
       <c r="B447" s="2">
         <v>2.7813756465911865</v>
       </c>
-      <c r="C447" s="2">
-        <v>2.815335750579834</v>
-      </c>
+      <c r="C447" s="2"/>
       <c r="D447" s="2">
         <v>2.6988604068756104</v>
       </c>
-      <c r="E447" s="2">
-        <v>2.6760625839233398</v>
-      </c>
+      <c r="E447" s="2"/>
     </row>
     <row r="448">
       <c r="A448" s="1">
@@ -6844,15 +5480,11 @@
       <c r="B448" s="2">
         <v>2.7725033760070801</v>
       </c>
-      <c r="C448" s="2">
-        <v>2.7619476318359375</v>
-      </c>
+      <c r="C448" s="2"/>
       <c r="D448" s="2">
         <v>2.7359039783477783</v>
       </c>
-      <c r="E448" s="2">
-        <v>2.6932730674743652</v>
-      </c>
+      <c r="E448" s="2"/>
     </row>
     <row r="449">
       <c r="A449" s="1">
@@ -6861,15 +5493,11 @@
       <c r="B449" s="2">
         <v>2.5251312255859375</v>
       </c>
-      <c r="C449" s="2">
-        <v>2.5402045249938965</v>
-      </c>
+      <c r="C449" s="2"/>
       <c r="D449" s="2">
         <v>2.7346234321594238</v>
       </c>
-      <c r="E449" s="2">
-        <v>2.6889619827270508</v>
-      </c>
+      <c r="E449" s="2"/>
     </row>
     <row r="450">
       <c r="A450" s="1">
@@ -6878,15 +5506,11 @@
       <c r="B450" s="2">
         <v>2.9216506481170654</v>
       </c>
-      <c r="C450" s="2">
-        <v>2.7718348503112793</v>
-      </c>
+      <c r="C450" s="2"/>
       <c r="D450" s="2">
         <v>2.7363929748535156</v>
       </c>
-      <c r="E450" s="2">
-        <v>2.673234224319458</v>
-      </c>
+      <c r="E450" s="2"/>
     </row>
     <row r="451">
       <c r="A451" s="1">
@@ -6895,15 +5519,11 @@
       <c r="B451" s="2">
         <v>2.6152679920196533</v>
       </c>
-      <c r="C451" s="2">
-        <v>2.5200097560882568</v>
-      </c>
+      <c r="C451" s="2"/>
       <c r="D451" s="2">
         <v>2.7989218235015869</v>
       </c>
-      <c r="E451" s="2">
-        <v>2.7262670993804932</v>
-      </c>
+      <c r="E451" s="2"/>
     </row>
     <row r="452">
       <c r="A452" s="1">
@@ -6912,15 +5532,11 @@
       <c r="B452" s="2">
         <v>2.9893345832824707</v>
       </c>
-      <c r="C452" s="2">
-        <v>2.8485121726989746</v>
-      </c>
+      <c r="C452" s="2"/>
       <c r="D452" s="2">
         <v>2.7745163440704346</v>
       </c>
-      <c r="E452" s="2">
-        <v>2.6786911487579346</v>
-      </c>
+      <c r="E452" s="2"/>
     </row>
     <row r="453">
       <c r="A453" s="1">
@@ -6929,15 +5545,11 @@
       <c r="B453" s="2">
         <v>2.7730464935302734</v>
       </c>
-      <c r="C453" s="2">
-        <v>2.7306694984436035</v>
-      </c>
+      <c r="C453" s="2"/>
       <c r="D453" s="2">
         <v>2.7575724124908447</v>
       </c>
-      <c r="E453" s="2">
-        <v>2.6512291431427002</v>
-      </c>
+      <c r="E453" s="2"/>
     </row>
     <row r="454">
       <c r="A454" s="1">
@@ -6946,15 +5558,11 @@
       <c r="B454" s="2">
         <v>2.5838770866394043</v>
       </c>
-      <c r="C454" s="2">
-        <v>2.3772006034851074</v>
-      </c>
+      <c r="C454" s="2"/>
       <c r="D454" s="2">
         <v>2.8140444755554199</v>
       </c>
-      <c r="E454" s="2">
-        <v>2.7044785022735596</v>
-      </c>
+      <c r="E454" s="2"/>
     </row>
     <row r="455">
       <c r="A455" s="1">
@@ -6963,15 +5571,11 @@
       <c r="B455" s="2">
         <v>3.22810959815979</v>
       </c>
-      <c r="C455" s="2">
-        <v>3.1706900596618652</v>
-      </c>
+      <c r="C455" s="2"/>
       <c r="D455" s="2">
         <v>2.796811580657959</v>
       </c>
-      <c r="E455" s="2">
-        <v>2.7063090801239014</v>
-      </c>
+      <c r="E455" s="2"/>
     </row>
     <row r="456">
       <c r="A456" s="1">
@@ -6980,15 +5584,11 @@
       <c r="B456" s="2">
         <v>2.5617256164550781</v>
       </c>
-      <c r="C456" s="2">
-        <v>2.3871519565582275</v>
-      </c>
+      <c r="C456" s="2"/>
       <c r="D456" s="2">
         <v>2.8140428066253662</v>
       </c>
-      <c r="E456" s="2">
-        <v>2.7172482013702393</v>
-      </c>
+      <c r="E456" s="2"/>
     </row>
     <row r="457">
       <c r="A457" s="1">
@@ -6997,15 +5597,11 @@
       <c r="B457" s="2">
         <v>2.6200084686279297</v>
       </c>
-      <c r="C457" s="2">
-        <v>2.5147888660430908</v>
-      </c>
+      <c r="C457" s="2"/>
       <c r="D457" s="2">
         <v>2.7849936485290527</v>
       </c>
-      <c r="E457" s="2">
-        <v>2.7018520832061768</v>
-      </c>
+      <c r="E457" s="2"/>
     </row>
     <row r="458">
       <c r="A458" s="1">
@@ -7014,15 +5610,11 @@
       <c r="B458" s="2">
         <v>3.033379077911377</v>
       </c>
-      <c r="C458" s="2">
-        <v>3.0194478034973145</v>
-      </c>
+      <c r="C458" s="2"/>
       <c r="D458" s="2">
         <v>2.7469065189361572</v>
       </c>
-      <c r="E458" s="2">
-        <v>2.6687510013580322</v>
-      </c>
+      <c r="E458" s="2"/>
     </row>
     <row r="459">
       <c r="A459" s="1">
@@ -7031,15 +5623,11 @@
       <c r="B459" s="2">
         <v>2.7665557861328125</v>
       </c>
-      <c r="C459" s="2">
-        <v>2.7883114814758301</v>
-      </c>
+      <c r="C459" s="2"/>
       <c r="D459" s="2">
         <v>2.7278730869293213</v>
       </c>
-      <c r="E459" s="2">
-        <v>2.6800379753112793</v>
-      </c>
+      <c r="E459" s="2"/>
     </row>
     <row r="460">
       <c r="A460" s="1">
@@ -7048,15 +5636,11 @@
       <c r="B460" s="2">
         <v>2.7703475952148438</v>
       </c>
-      <c r="C460" s="2">
-        <v>2.618462085723877</v>
-      </c>
+      <c r="C460" s="2"/>
       <c r="D460" s="2">
         <v>2.6778824329376221</v>
       </c>
-      <c r="E460" s="2">
-        <v>2.6313340663909912</v>
-      </c>
+      <c r="E460" s="2"/>
     </row>
     <row r="461">
       <c r="A461" s="1">
@@ -7065,15 +5649,11 @@
       <c r="B461" s="2">
         <v>2.7278928756713867</v>
       </c>
-      <c r="C461" s="2">
-        <v>2.7099463939666748</v>
-      </c>
+      <c r="C461" s="2"/>
       <c r="D461" s="2">
         <v>2.6666951179504395</v>
       </c>
-      <c r="E461" s="2">
-        <v>2.6354753971099854</v>
-      </c>
+      <c r="E461" s="2"/>
     </row>
     <row r="462">
       <c r="A462" s="1">
@@ -7082,15 +5662,11 @@
       <c r="B462" s="2">
         <v>2.4302632808685303</v>
       </c>
-      <c r="C462" s="2">
-        <v>2.4327588081359863</v>
-      </c>
+      <c r="C462" s="2"/>
       <c r="D462" s="2">
         <v>2.6616573333740234</v>
       </c>
-      <c r="E462" s="2">
-        <v>2.6428542137145996</v>
-      </c>
+      <c r="E462" s="2"/>
     </row>
     <row r="463">
       <c r="A463" s="1">
@@ -7100,13 +5676,13 @@
         <v>2.4125761985778809</v>
       </c>
       <c r="C463" s="2">
-        <v>2.4787840843200684</v>
+        <v>2.4170904159545898</v>
       </c>
       <c r="D463" s="2">
         <v>2.6214265823364258</v>
       </c>
       <c r="E463" s="2">
-        <v>2.6092097759246826</v>
+        <v>2.5506374835968018</v>
       </c>
     </row>
     <row r="464">
@@ -7117,13 +5693,13 @@
         <v>2.7781939506530762</v>
       </c>
       <c r="C464" s="2">
-        <v>2.7323541641235352</v>
+        <v>2.6610655784606934</v>
       </c>
       <c r="D464" s="2">
         <v>2.6013615131378174</v>
       </c>
       <c r="E464" s="2">
-        <v>2.5968899726867676</v>
+        <v>2.5506374835968018</v>
       </c>
     </row>
     <row r="465">
@@ -7134,13 +5710,13 @@
         <v>2.4610390663146973</v>
       </c>
       <c r="C465" s="2">
-        <v>2.4244248867034912</v>
+        <v>2.4370486736297607</v>
       </c>
       <c r="D465" s="2">
         <v>2.6265122890472412</v>
       </c>
       <c r="E465" s="2">
-        <v>2.631542444229126</v>
+        <v>2.5506374835968018</v>
       </c>
     </row>
     <row r="466">
@@ -7151,13 +5727,13 @@
         <v>2.5746691226959229</v>
       </c>
       <c r="C466" s="2">
-        <v>2.5811989307403564</v>
+        <v>2.5597360134124756</v>
       </c>
       <c r="D466" s="2">
         <v>2.6273176670074463</v>
       </c>
       <c r="E466" s="2">
-        <v>2.6384172439575195</v>
+        <v>2.5506374835968018</v>
       </c>
     </row>
     <row r="467">
@@ -7168,13 +5744,13 @@
         <v>2.6713011264801025</v>
       </c>
       <c r="C467" s="2">
-        <v>2.7166473865509033</v>
+        <v>2.6782462596893311</v>
       </c>
       <c r="D467" s="2">
         <v>2.6889805793762207</v>
       </c>
       <c r="E467" s="2">
-        <v>2.6848781108856201</v>
+        <v>2.594632625579834</v>
       </c>
     </row>
     <row r="468">
@@ -7184,15 +5760,11 @@
       <c r="B468" s="2">
         <v>2.5859699249267578</v>
       </c>
-      <c r="C468" s="2">
-        <v>2.6774334907531738</v>
-      </c>
+      <c r="C468" s="2"/>
       <c r="D468" s="2">
         <v>2.7668824195861816</v>
       </c>
-      <c r="E468" s="2">
-        <v>2.7594542503356934</v>
-      </c>
+      <c r="E468" s="2"/>
     </row>
     <row r="469">
       <c r="A469" s="1">
@@ -7201,15 +5773,11 @@
       <c r="B469" s="2">
         <v>2.9967043399810791</v>
       </c>
-      <c r="C469" s="2">
-        <v>2.9303328990936279</v>
-      </c>
+      <c r="C469" s="2"/>
       <c r="D469" s="2">
         <v>2.7486641407012939</v>
       </c>
-      <c r="E469" s="2">
-        <v>2.7492597103118896</v>
-      </c>
+      <c r="E469" s="2"/>
     </row>
     <row r="470">
       <c r="A470" s="1">
@@ -7218,15 +5786,11 @@
       <c r="B470" s="2">
         <v>2.7351410388946533</v>
       </c>
-      <c r="C470" s="2">
-        <v>2.7718207836151123</v>
-      </c>
+      <c r="C470" s="2"/>
       <c r="D470" s="2">
         <v>2.7564685344696045</v>
       </c>
-      <c r="E470" s="2">
-        <v>2.7529697418212891</v>
-      </c>
+      <c r="E470" s="2"/>
     </row>
     <row r="471">
       <c r="A471" s="1">
@@ -7236,13 +5800,13 @@
         <v>2.9852306842803955</v>
       </c>
       <c r="C471" s="2">
-        <v>2.8509058952331543</v>
+        <v>2.8146092891693115</v>
       </c>
       <c r="D471" s="2">
         <v>2.8123488426208496</v>
       </c>
       <c r="E471" s="2">
-        <v>2.8003580570220947</v>
+        <v>2.7741949558258057</v>
       </c>
     </row>
     <row r="472">
@@ -7253,13 +5817,13 @@
         <v>3.1136932373046875</v>
       </c>
       <c r="C472" s="2">
-        <v>3.1499707698822021</v>
+        <v>3.0659594535827637</v>
       </c>
       <c r="D472" s="2">
         <v>2.7665665149688721</v>
       </c>
       <c r="E472" s="2">
-        <v>2.7456760406494141</v>
+        <v>2.6920850276947021</v>
       </c>
     </row>
     <row r="473">
@@ -7270,13 +5834,13 @@
         <v>2.6142282485961914</v>
       </c>
       <c r="C473" s="2">
-        <v>2.6406030654907227</v>
+        <v>2.6025218963623047</v>
       </c>
       <c r="D473" s="2">
         <v>2.7636537551879883</v>
       </c>
       <c r="E473" s="2">
-        <v>2.7299292087554932</v>
+        <v>2.6681163311004639</v>
       </c>
     </row>
     <row r="474">
@@ -7287,13 +5851,13 @@
         <v>2.5312793254852295</v>
       </c>
       <c r="C474" s="2">
-        <v>2.4578149318695068</v>
+        <v>2.4570136070251465</v>
       </c>
       <c r="D474" s="2">
         <v>2.7696874141693115</v>
       </c>
       <c r="E474" s="2">
-        <v>2.7314407825469971</v>
+        <v>2.6959137916564941</v>
       </c>
     </row>
     <row r="475">
@@ -7304,13 +5868,13 @@
         <v>3.0775909423828125</v>
       </c>
       <c r="C475" s="2">
-        <v>3.0076932907104492</v>
+        <v>3.0268192291259766</v>
       </c>
       <c r="D475" s="2">
         <v>2.7364692687988281</v>
       </c>
       <c r="E475" s="2">
-        <v>2.6888420581817627</v>
+        <v>2.6604418754577637</v>
       </c>
     </row>
     <row r="476">
@@ -7321,13 +5885,13 @@
         <v>2.2592616081237793</v>
       </c>
       <c r="C476" s="2">
-        <v>2.2245092391967773</v>
+        <v>2.1855864524841309</v>
       </c>
       <c r="D476" s="2">
         <v>2.731764554977417</v>
       </c>
       <c r="E476" s="2">
-        <v>2.6929621696472168</v>
+        <v>2.6612918376922607</v>
       </c>
     </row>
     <row r="477">
@@ -7338,13 +5902,13 @@
         <v>2.5597541332244873</v>
       </c>
       <c r="C477" s="2">
-        <v>2.5357129573822021</v>
+        <v>2.5243046283721924</v>
       </c>
       <c r="D477" s="2">
         <v>2.6701865196228027</v>
       </c>
       <c r="E477" s="2">
-        <v>2.6258397102355957</v>
+        <v>2.6051826477050781</v>
       </c>
     </row>
     <row r="478">
@@ -7355,13 +5919,13 @@
         <v>3.0510075092315674</v>
       </c>
       <c r="C478" s="2">
-        <v>2.9439358711242676</v>
+        <v>2.8904960155487061</v>
       </c>
       <c r="D478" s="2">
         <v>2.6619458198547363</v>
       </c>
       <c r="E478" s="2">
-        <v>2.6107809543609619</v>
+        <v>2.5964212417602539</v>
       </c>
     </row>
     <row r="479">
@@ -7372,13 +5936,13 @@
         <v>2.4361770153045654</v>
       </c>
       <c r="C479" s="2">
-        <v>2.388432502746582</v>
+        <v>2.3766672611236572</v>
       </c>
       <c r="D479" s="2">
         <v>2.6666512489318848</v>
       </c>
       <c r="E479" s="2">
-        <v>2.6231706142425537</v>
+        <v>2.6082730293273926</v>
       </c>
     </row>
     <row r="480">
@@ -7389,13 +5953,13 @@
         <v>2.9428889751434326</v>
       </c>
       <c r="C480" s="2">
-        <v>2.8879878520965576</v>
+        <v>2.8222572803497314</v>
       </c>
       <c r="D480" s="2">
         <v>2.6039409637451172</v>
       </c>
       <c r="E480" s="2">
-        <v>2.565394401550293</v>
+        <v>2.5503451824188232</v>
       </c>
     </row>
     <row r="481">
@@ -7406,13 +5970,13 @@
         <v>2.5594911575317383</v>
       </c>
       <c r="C481" s="2">
-        <v>2.5458674430847168</v>
+        <v>2.5609784126281738</v>
       </c>
       <c r="D481" s="2">
         <v>2.6355845928192139</v>
       </c>
       <c r="E481" s="2">
-        <v>2.5931217670440674</v>
+        <v>2.5757932662963867</v>
       </c>
     </row>
     <row r="482">
@@ -7423,13 +5987,13 @@
         <v>2.5400607585906982</v>
       </c>
       <c r="C482" s="2">
-        <v>2.505075216293335</v>
+        <v>2.5236692428588867</v>
       </c>
       <c r="D482" s="2">
         <v>2.6351888179779053</v>
       </c>
       <c r="E482" s="2">
-        <v>2.5845322608947754</v>
+        <v>2.5702817440032959</v>
       </c>
     </row>
     <row r="483">
@@ -7440,13 +6004,13 @@
         <v>2.5736291408538818</v>
       </c>
       <c r="C483" s="2">
-        <v>2.5693206787109375</v>
+        <v>2.5636777877807617</v>
       </c>
       <c r="D483" s="2">
         <v>2.6240286827087402</v>
       </c>
       <c r="E483" s="2">
-        <v>2.5711679458618164</v>
+        <v>2.5500538349151611</v>
       </c>
     </row>
     <row r="484">
@@ -7457,13 +6021,13 @@
         <v>2.5131983757019043</v>
       </c>
       <c r="C484" s="2">
-        <v>2.4877068996429443</v>
+        <v>2.5054695606231689</v>
       </c>
       <c r="D484" s="2">
         <v>2.633913516998291</v>
       </c>
       <c r="E484" s="2">
-        <v>2.5914018154144287</v>
+        <v>2.5648295879364014</v>
       </c>
     </row>
     <row r="485">
@@ -7474,13 +6038,13 @@
         <v>2.5440547466278076</v>
       </c>
       <c r="C485" s="2">
-        <v>2.4740560054779053</v>
+        <v>2.4146201610565186</v>
       </c>
       <c r="D485" s="2">
         <v>2.6443402767181396</v>
       </c>
       <c r="E485" s="2">
-        <v>2.5977895259857178</v>
+        <v>2.5774931907653809</v>
       </c>
     </row>
     <row r="486">
@@ -7491,13 +6055,13 @@
         <v>2.5561923980712891</v>
       </c>
       <c r="C486" s="2">
-        <v>2.4584085941314697</v>
+        <v>2.4746997356414795</v>
       </c>
       <c r="D486" s="2">
         <v>2.6657605171203613</v>
       </c>
       <c r="E486" s="2">
-        <v>2.6233038902282715</v>
+        <v>2.6019918918609619</v>
       </c>
     </row>
     <row r="487">
@@ -7508,13 +6072,13 @@
         <v>2.9505648612976074</v>
       </c>
       <c r="C487" s="2">
-        <v>2.8236570358276367</v>
+        <v>2.7084455490112305</v>
       </c>
       <c r="D487" s="2">
         <v>2.6703059673309326</v>
       </c>
       <c r="E487" s="2">
-        <v>2.6367754936218262</v>
+        <v>2.6042027473449707</v>
       </c>
     </row>
     <row r="488">
@@ -7525,13 +6089,13 @@
         <v>2.5251419544219971</v>
       </c>
       <c r="C488" s="2">
-        <v>2.5705368518829346</v>
+        <v>2.5096478462219238</v>
       </c>
       <c r="D488" s="2">
         <v>2.6668796539306641</v>
       </c>
       <c r="E488" s="2">
-        <v>2.6215143203735352</v>
+        <v>2.592982292175293</v>
       </c>
     </row>
     <row r="489">
@@ -7542,13 +6106,13 @@
         <v>3.0367288589477539</v>
       </c>
       <c r="C489" s="2">
-        <v>2.9454779624938965</v>
+        <v>2.9362308979034424</v>
       </c>
       <c r="D489" s="2">
         <v>2.6861402988433838</v>
       </c>
       <c r="E489" s="2">
-        <v>2.6456570625305176</v>
+        <v>2.608748197555542</v>
       </c>
     </row>
     <row r="490">
@@ -7559,13 +6123,13 @@
         <v>2.7522745132446289</v>
       </c>
       <c r="C490" s="2">
-        <v>2.7754948139190674</v>
+        <v>2.7814671993255615</v>
       </c>
       <c r="D490" s="2">
         <v>2.6630902290344238</v>
       </c>
       <c r="E490" s="2">
-        <v>2.6344230175018311</v>
+        <v>2.6044518947601318</v>
       </c>
     </row>
     <row r="491">
@@ -7576,13 +6140,13 @@
         <v>2.5809698104858398</v>
       </c>
       <c r="C491" s="2">
-        <v>2.6263196468353271</v>
+        <v>2.5435667037963867</v>
       </c>
       <c r="D491" s="2">
         <v>2.6858401298522949</v>
       </c>
       <c r="E491" s="2">
-        <v>2.6690926551818848</v>
+        <v>2.6357412338256836</v>
       </c>
     </row>
     <row r="492">
@@ -7593,13 +6157,13 @@
         <v>2.5427908897399902</v>
       </c>
       <c r="C492" s="2">
-        <v>2.4319705963134766</v>
+        <v>2.4626922607421875</v>
       </c>
       <c r="D492" s="2">
         <v>2.5910727977752686</v>
       </c>
       <c r="E492" s="2">
-        <v>2.5916721820831299</v>
+        <v>2.5707671642303467</v>
       </c>
     </row>
     <row r="493">
@@ -7610,13 +6174,13 @@
         <v>2.6865453720092773</v>
       </c>
       <c r="C493" s="2">
-        <v>2.7049920558929443</v>
+        <v>2.6473634243011475</v>
       </c>
       <c r="D493" s="2">
         <v>2.5656423568725586</v>
       </c>
       <c r="E493" s="2">
-        <v>2.5655207633972168</v>
+        <v>2.5479812622070312</v>
       </c>
     </row>
     <row r="494">
@@ -7627,13 +6191,13 @@
         <v>2.3366026878356934</v>
       </c>
       <c r="C494" s="2">
-        <v>2.3729491233825684</v>
+        <v>2.3759529590606689</v>
       </c>
       <c r="D494" s="2">
         <v>2.5340976715087891</v>
       </c>
       <c r="E494" s="2">
-        <v>2.5305726528167725</v>
+        <v>2.5002536773681641</v>
       </c>
     </row>
     <row r="495">
@@ -7644,13 +6208,13 @@
         <v>2.7609415054321289</v>
       </c>
       <c r="C495" s="2">
-        <v>2.770435094833374</v>
+        <v>2.7563033103942871</v>
       </c>
       <c r="D495" s="2">
         <v>2.5165019035339355</v>
       </c>
       <c r="E495" s="2">
-        <v>2.4935100078582764</v>
+        <v>2.459338903427124</v>
       </c>
     </row>
     <row r="496">
@@ -7661,13 +6225,13 @@
         <v>2.0976600646972656</v>
       </c>
       <c r="C496" s="2">
-        <v>2.1268730163574219</v>
+        <v>2.123680591583252</v>
       </c>
       <c r="D496" s="2">
         <v>2.5515782833099365</v>
       </c>
       <c r="E496" s="2">
-        <v>2.516726016998291</v>
+        <v>2.4956378936767578</v>
       </c>
     </row>
     <row r="497">
@@ -7678,13 +6242,13 @@
         <v>2.2962672710418701</v>
       </c>
       <c r="C497" s="2">
-        <v>2.3351750373840332</v>
+        <v>2.3045737743377686</v>
       </c>
       <c r="D497" s="2">
         <v>2.5546910762786865</v>
       </c>
       <c r="E497" s="2">
-        <v>2.5399808883666992</v>
+        <v>2.5079865455627441</v>
       </c>
     </row>
     <row r="498">
@@ -7695,13 +6259,13 @@
         <v>2.7528274059295654</v>
       </c>
       <c r="C498" s="2">
-        <v>2.6309454441070557</v>
+        <v>2.5066823959350586</v>
       </c>
       <c r="D498" s="2">
         <v>2.5697212219238281</v>
       </c>
       <c r="E498" s="2">
-        <v>2.5329728126525879</v>
+        <v>2.5091829299926758</v>
       </c>
     </row>
     <row r="499">
@@ -7712,13 +6276,13 @@
         <v>2.5939116477966309</v>
       </c>
       <c r="C499" s="2">
-        <v>2.4419293403625488</v>
+        <v>2.4132349491119385</v>
       </c>
       <c r="D499" s="2">
         <v>2.5828979015350342</v>
       </c>
       <c r="E499" s="2">
-        <v>2.534874439239502</v>
+        <v>2.5060770511627197</v>
       </c>
     </row>
     <row r="500">
@@ -7729,13 +6293,13 @@
         <v>2.896658182144165</v>
       </c>
       <c r="C500" s="2">
-        <v>2.8352639675140381</v>
+        <v>2.8702576160430908</v>
       </c>
       <c r="D500" s="2">
         <v>2.5934164524078369</v>
       </c>
       <c r="E500" s="2">
-        <v>2.51761794090271</v>
+        <v>2.4932911396026611</v>
       </c>
     </row>
     <row r="501">
@@ -7746,13 +6310,13 @@
         <v>2.5708050727844238</v>
       </c>
       <c r="C501" s="2">
-        <v>2.6412639617919922</v>
+        <v>2.5738303661346436</v>
       </c>
       <c r="D501" s="2">
         <v>2.6256239414215088</v>
       </c>
       <c r="E501" s="2">
-        <v>2.5440843105316162</v>
+        <v>2.5176560878753662</v>
       </c>
     </row>
     <row r="502">
@@ -7763,13 +6327,13 @@
         <v>2.8218173980712891</v>
       </c>
       <c r="C502" s="2">
-        <v>2.6419196128845215</v>
+        <v>2.6581301689147949</v>
       </c>
       <c r="D502" s="2">
         <v>2.6227767467498779</v>
       </c>
       <c r="E502" s="2">
-        <v>2.5190708637237549</v>
+        <v>2.4930458068847656</v>
       </c>
     </row>
     <row r="503">
@@ -7780,13 +6344,13 @@
         <v>2.4551935195922852</v>
       </c>
       <c r="C503" s="2">
-        <v>2.390064001083374</v>
+        <v>2.3480005264282227</v>
       </c>
       <c r="D503" s="2">
         <v>2.608351469039917</v>
       </c>
       <c r="E503" s="2">
-        <v>2.519556999206543</v>
+        <v>2.5004270076751709</v>
       </c>
     </row>
     <row r="504">
@@ -7797,13 +6361,13 @@
         <v>2.8556067943572998</v>
       </c>
       <c r="C504" s="2">
-        <v>2.6151270866394043</v>
+        <v>2.6412291526794434</v>
       </c>
       <c r="D504" s="2">
         <v>2.5827634334564209</v>
       </c>
       <c r="E504" s="2">
-        <v>2.5112056732177734</v>
+        <v>2.4920051097869873</v>
       </c>
     </row>
     <row r="505">
@@ -7814,13 +6378,13 @@
         <v>2.3875288963317871</v>
       </c>
       <c r="C505" s="2">
-        <v>2.3650712966918945</v>
+        <v>2.3429663181304932</v>
       </c>
       <c r="D505" s="2">
         <v>2.5589601993560791</v>
       </c>
       <c r="E505" s="2">
-        <v>2.4925663471221924</v>
+        <v>2.4692368507385254</v>
       </c>
     </row>
     <row r="506">
@@ -7831,13 +6395,13 @@
         <v>2.2706425189971924</v>
       </c>
       <c r="C506" s="2">
-        <v>2.1100523471832275</v>
+        <v>2.0830807685852051</v>
       </c>
       <c r="D506" s="2">
         <v>2.6139340400695801</v>
       </c>
       <c r="E506" s="2">
-        <v>2.54221510887146</v>
+        <v>2.5240826606750488</v>
       </c>
     </row>
     <row r="507">
@@ -7848,13 +6412,13 @@
         <v>2.6229984760284424</v>
       </c>
       <c r="C507" s="2">
-        <v>2.6353223323822021</v>
+        <v>2.573112964630127</v>
       </c>
       <c r="D507" s="2">
         <v>2.5573687553405762</v>
       </c>
       <c r="E507" s="2">
-        <v>2.5161616802215576</v>
+        <v>2.4880635738372803</v>
       </c>
     </row>
     <row r="508">
@@ -7865,13 +6429,13 @@
         <v>2.3636209964752197</v>
       </c>
       <c r="C508" s="2">
-        <v>2.366767406463623</v>
+        <v>2.3374385833740234</v>
       </c>
       <c r="D508" s="2">
         <v>2.5642008781433105</v>
       </c>
       <c r="E508" s="2">
-        <v>2.5261211395263672</v>
+        <v>2.4903812408447266</v>
       </c>
     </row>
     <row r="509">
@@ -7882,13 +6446,13 @@
         <v>2.6824285984039307</v>
       </c>
       <c r="C509" s="2">
-        <v>2.667508602142334</v>
+        <v>2.665341854095459</v>
       </c>
       <c r="D509" s="2">
         <v>2.5378682613372803</v>
       </c>
       <c r="E509" s="2">
-        <v>2.5399060249328613</v>
+        <v>2.4932963848114014</v>
       </c>
     </row>
     <row r="510">
@@ -7899,13 +6463,13 @@
         <v>3.0655684471130371</v>
       </c>
       <c r="C510" s="2">
-        <v>3.0881030559539795</v>
+        <v>3.0674431324005127</v>
       </c>
       <c r="D510" s="2">
         <v>2.5521366596221924</v>
       </c>
       <c r="E510" s="2">
-        <v>2.5571663379669189</v>
+        <v>2.5135848522186279</v>
       </c>
     </row>
     <row r="511">
@@ -7916,13 +6480,13 @@
         <v>2.3127312660217285</v>
       </c>
       <c r="C511" s="2">
-        <v>2.4074392318725586</v>
+        <v>2.3339591026306152</v>
       </c>
       <c r="D511" s="2">
         <v>2.6005368232727051</v>
       </c>
       <c r="E511" s="2">
-        <v>2.6139507293701172</v>
+        <v>2.573211669921875</v>
       </c>
     </row>
     <row r="512">
@@ -7933,13 +6497,13 @@
         <v>2.5166811943054199</v>
       </c>
       <c r="C512" s="2">
-        <v>2.4796979427337646</v>
+        <v>2.3688595294952393</v>
       </c>
       <c r="D512" s="2">
         <v>2.5813901424407959</v>
       </c>
       <c r="E512" s="2">
-        <v>2.5939805507659912</v>
+        <v>2.5565004348754883</v>
       </c>
     </row>
     <row r="513">
@@ -7950,13 +6514,13 @@
         <v>2.6186144351959229</v>
       </c>
       <c r="C513" s="2">
-        <v>2.7391915321350098</v>
+        <v>2.6674656867980957</v>
       </c>
       <c r="D513" s="2">
         <v>2.6622903347015381</v>
       </c>
       <c r="E513" s="2">
-        <v>2.6775155067443848</v>
+        <v>2.6483223438262939</v>
       </c>
     </row>
     <row r="514">
@@ -7967,13 +6531,13 @@
         <v>2.5159430503845215</v>
       </c>
       <c r="C514" s="2">
-        <v>2.5204150676727295</v>
+        <v>2.5255627632141113</v>
       </c>
       <c r="D514" s="2">
         <v>2.6796371936798096</v>
       </c>
       <c r="E514" s="2">
-        <v>2.6830446720123291</v>
+        <v>2.6469876766204834</v>
       </c>
     </row>
     <row r="515">
@@ -7984,13 +6548,13 @@
         <v>2.7062458992004395</v>
       </c>
       <c r="C515" s="2">
-        <v>2.6211116313934326</v>
+        <v>2.6197221279144287</v>
       </c>
       <c r="D515" s="2">
         <v>2.6662776470184326</v>
       </c>
       <c r="E515" s="2">
-        <v>2.6715512275695801</v>
+        <v>2.633171558380127</v>
       </c>
     </row>
     <row r="516">
@@ -8001,13 +6565,13 @@
         <v>2.4506778717041016</v>
       </c>
       <c r="C516" s="2">
-        <v>2.4555914402008057</v>
+        <v>2.4227101802825928</v>
       </c>
       <c r="D516" s="2">
         <v>2.7365729808807373</v>
       </c>
       <c r="E516" s="2">
-        <v>2.7240867614746094</v>
+        <v>2.6778078079223633</v>
       </c>
     </row>
     <row r="517">
@@ -8018,13 +6582,13 @@
         <v>3.0917212963104248</v>
       </c>
       <c r="C517" s="2">
-        <v>3.1185812950134277</v>
+        <v>3.1638357639312744</v>
       </c>
       <c r="D517" s="2">
         <v>2.7284095287322998</v>
       </c>
       <c r="E517" s="2">
-        <v>2.7172250747680664</v>
+        <v>2.6820940971374512</v>
       </c>
     </row>
     <row r="518">
@@ -8035,13 +6599,13 @@
         <v>2.8385505676269531</v>
       </c>
       <c r="C518" s="2">
-        <v>2.7172708511352539</v>
+        <v>2.6533305644989014</v>
       </c>
       <c r="D518" s="2">
         <v>2.742429256439209</v>
       </c>
       <c r="E518" s="2">
-        <v>2.7228140830993652</v>
+        <v>2.6831462383270264</v>
       </c>
     </row>
     <row r="519">
@@ -8052,13 +6616,13 @@
         <v>2.94533371925354</v>
       </c>
       <c r="C519" s="2">
-        <v>2.9846630096435547</v>
+        <v>2.9430980682373047</v>
       </c>
       <c r="D519" s="2">
         <v>2.8440389633178711</v>
       </c>
       <c r="E519" s="2">
-        <v>2.8389420509338379</v>
+        <v>2.7773764133453369</v>
       </c>
     </row>
     <row r="520">
@@ -8069,13 +6633,13 @@
         <v>2.9453883171081543</v>
       </c>
       <c r="C520" s="2">
-        <v>2.880258321762085</v>
+        <v>2.7356858253479004</v>
       </c>
       <c r="D520" s="2">
         <v>2.9764657020568848</v>
       </c>
       <c r="E520" s="2">
-        <v>2.9451076984405518</v>
+        <v>2.8848185539245605</v>
       </c>
     </row>
     <row r="521">
@@ -8086,13 +6650,13 @@
         <v>2.4432106018066406</v>
       </c>
       <c r="C521" s="2">
-        <v>2.4179422855377197</v>
+        <v>2.4074363708496094</v>
       </c>
       <c r="D521" s="2">
         <v>3.1342942714691162</v>
       </c>
       <c r="E521" s="2">
-        <v>3.09263014793396</v>
+        <v>3.0323138236999512</v>
       </c>
     </row>
     <row r="522">
@@ -8103,13 +6667,13 @@
         <v>2.7447912693023682</v>
       </c>
       <c r="C522" s="2">
-        <v>2.7894923686981201</v>
+        <v>2.6769335269927979</v>
       </c>
       <c r="D522" s="2">
         <v>3.1873319149017334</v>
       </c>
       <c r="E522" s="2">
-        <v>3.1294760704040527</v>
+        <v>3.0577208995819092</v>
       </c>
     </row>
     <row r="523">
@@ -8120,13 +6684,13 @@
         <v>3.4304304122924805</v>
       </c>
       <c r="C523" s="2">
-        <v>3.5655663013458252</v>
+        <v>3.3736348152160645</v>
       </c>
       <c r="D523" s="2">
         <v>3.2289783954620361</v>
       </c>
       <c r="E523" s="2">
-        <v>3.1875402927398682</v>
+        <v>3.1019084453582764</v>
       </c>
     </row>
     <row r="524">
@@ -8137,13 +6701,13 @@
         <v>3.8980875015258789</v>
       </c>
       <c r="C524" s="2">
-        <v>3.5766034126281738</v>
+        <v>3.5867025852203369</v>
       </c>
       <c r="D524" s="2">
         <v>3.2866997718811035</v>
       </c>
       <c r="E524" s="2">
-        <v>3.2286701202392578</v>
+        <v>3.136143684387207</v>
       </c>
     </row>
     <row r="525">
@@ -8154,13 +6718,13 @@
         <v>3.8711347579956055</v>
       </c>
       <c r="C525" s="2">
-        <v>3.7832942008972168</v>
+        <v>3.7501678466796875</v>
       </c>
       <c r="D525" s="2">
         <v>3.3973889350891113</v>
       </c>
       <c r="E525" s="2">
-        <v>3.3440985679626465</v>
+        <v>3.2573022842407227</v>
       </c>
     </row>
     <row r="526">
@@ -8171,13 +6735,13 @@
         <v>3.5690600872039795</v>
       </c>
       <c r="C526" s="2">
-        <v>3.4501936435699463</v>
+        <v>3.3924977779388428</v>
       </c>
       <c r="D526" s="2">
         <v>3.514833927154541</v>
       </c>
       <c r="E526" s="2">
-        <v>3.4657483100891113</v>
+        <v>3.3755507469177246</v>
       </c>
     </row>
     <row r="527">
@@ -8188,13 +6752,13 @@
         <v>3.213369607925415</v>
       </c>
       <c r="C527" s="2">
-        <v>3.2398495674133301</v>
+        <v>3.0510189533233643</v>
       </c>
       <c r="D527" s="2">
         <v>3.6371064186096191</v>
       </c>
       <c r="E527" s="2">
-        <v>3.5746128559112549</v>
+        <v>3.4944825172424316</v>
       </c>
     </row>
     <row r="528">
@@ -8205,13 +6769,13 @@
         <v>3.4648256301879883</v>
       </c>
       <c r="C528" s="2">
-        <v>3.3548316955566406</v>
+        <v>3.2512149810791016</v>
       </c>
       <c r="D528" s="2">
         <v>3.6798088550567627</v>
       </c>
       <c r="E528" s="2">
-        <v>3.6012840270996094</v>
+        <v>3.5344779491424561</v>
       </c>
     </row>
     <row r="529">
@@ -8222,13 +6786,13 @@
         <v>3.9415903091430664</v>
       </c>
       <c r="C529" s="2">
-        <v>3.9191141128540039</v>
+        <v>3.8261137008666992</v>
       </c>
       <c r="D529" s="2">
         <v>3.6931970119476318</v>
       </c>
       <c r="E529" s="2">
-        <v>3.6361896991729736</v>
+        <v>3.5629482269287109</v>
       </c>
     </row>
     <row r="530">
@@ -8239,13 +6803,13 @@
         <v>3.5002150535583496</v>
       </c>
       <c r="C530" s="2">
-        <v>3.5127894878387451</v>
+        <v>3.4716715812683105</v>
       </c>
       <c r="D530" s="2">
         <v>3.7167260646820068</v>
       </c>
       <c r="E530" s="2">
-        <v>3.658735990524292</v>
+        <v>3.5906715393066406</v>
       </c>
     </row>
     <row r="531">
@@ -8256,13 +6820,13 @@
         <v>3.8452441692352295</v>
       </c>
       <c r="C531" s="2">
-        <v>3.7692737579345703</v>
+        <v>3.7473204135894775</v>
       </c>
       <c r="D531" s="2">
         <v>3.8630597591400146</v>
       </c>
       <c r="E531" s="2">
-        <v>3.7939457893371582</v>
+        <v>3.735851526260376</v>
       </c>
     </row>
     <row r="532">
@@ -8273,13 +6837,13 @@
         <v>3.814753532409668</v>
       </c>
       <c r="C532" s="2">
-        <v>3.8056068420410156</v>
+        <v>3.7335934638977051</v>
       </c>
       <c r="D532" s="2">
         <v>3.9556484222412109</v>
       </c>
       <c r="E532" s="2">
-        <v>3.8821914196014404</v>
+        <v>3.8486275672912598</v>
       </c>
     </row>
     <row r="533">
@@ -8290,13 +6854,13 @@
         <v>4.0185794830322266</v>
       </c>
       <c r="C533" s="2">
-        <v>3.8907546997070312</v>
+        <v>3.8429343700408936</v>
       </c>
       <c r="D533" s="2">
         <v>3.9714298248291016</v>
       </c>
       <c r="E533" s="2">
-        <v>3.9115989208221436</v>
+        <v>3.8897805213928223</v>
       </c>
     </row>
     <row r="534">
@@ -8307,13 +6871,13 @@
         <v>4.0828957557678223</v>
       </c>
       <c r="C534" s="2">
-        <v>3.9862096309661865</v>
+        <v>3.9996776580810547</v>
       </c>
       <c r="D534" s="2">
         <v>4.0083322525024414</v>
       </c>
       <c r="E534" s="2">
-        <v>3.949772834777832</v>
+        <v>3.9413669109344482</v>
       </c>
     </row>
     <row r="535">
@@ -8324,13 +6888,13 @@
         <v>4.8860640525817871</v>
       </c>
       <c r="C535" s="2">
-        <v>4.6670827865600586</v>
+        <v>4.6991195678710938</v>
       </c>
       <c r="D535" s="2">
         <v>4.1091818809509277</v>
       </c>
       <c r="E535" s="2">
-        <v>4.034386157989502</v>
+        <v>4.0298209190368652</v>
       </c>
     </row>
     <row r="536">
@@ -8341,13 +6905,13 @@
         <v>4.0466670989990234</v>
       </c>
       <c r="C536" s="2">
-        <v>4.034060001373291</v>
+        <v>4.0660028457641602</v>
       </c>
       <c r="D536" s="2">
         <v>4.1340928077697754</v>
       </c>
       <c r="E536" s="2">
-        <v>4.0658416748046875</v>
+        <v>4.0685558319091797</v>
       </c>
     </row>
     <row r="537">
@@ -8358,13 +6922,13 @@
         <v>3.6068596839904785</v>
       </c>
       <c r="C537" s="2">
-        <v>3.6194994449615479</v>
+        <v>3.6215918064117432</v>
       </c>
       <c r="D537" s="2">
         <v>4.1659126281738281</v>
       </c>
       <c r="E537" s="2">
-        <v>4.0778932571411133</v>
+        <v>4.0857419967651367</v>
       </c>
     </row>
     <row r="538">
@@ -8375,13 +6939,13 @@
         <v>4.2737116813659668</v>
       </c>
       <c r="C538" s="2">
-        <v>4.2626781463623047</v>
+        <v>4.2903914451599121</v>
       </c>
       <c r="D538" s="2">
         <v>4.1496243476867676</v>
       </c>
       <c r="E538" s="2">
-        <v>4.0673575401306152</v>
+        <v>4.067662239074707</v>
       </c>
     </row>
     <row r="539">
@@ -8392,13 +6956,13 @@
         <v>4.4078612327575684</v>
       </c>
       <c r="C539" s="2">
-        <v>4.2743086814880371</v>
+        <v>4.2677555084228516</v>
       </c>
       <c r="D539" s="2">
         <v>4.1836681365966797</v>
       </c>
       <c r="E539" s="2">
-        <v>4.0857076644897461</v>
+        <v>4.0801725387573242</v>
       </c>
     </row>
     <row r="540">
@@ -8409,13 +6973,13 @@
         <v>4.0694417953491211</v>
       </c>
       <c r="C540" s="2">
-        <v>4.0523743629455566</v>
+        <v>4.0959353446960449</v>
       </c>
       <c r="D540" s="2">
         <v>4.1096882820129395</v>
       </c>
       <c r="E540" s="2">
-        <v>4.0451011657714844</v>
+        <v>4.0312118530273438</v>
       </c>
     </row>
     <row r="541">
@@ -8426,13 +6990,13 @@
         <v>4.1011319160461426</v>
       </c>
       <c r="C541" s="2">
-        <v>3.9140703678131104</v>
+        <v>3.8882694244384766</v>
       </c>
       <c r="D541" s="2">
         <v>4.0478038787841797</v>
       </c>
       <c r="E541" s="2">
-        <v>3.9790477752685547</v>
+        <v>3.9703593254089355</v>
       </c>
     </row>
     <row r="542">
@@ -8443,13 +7007,13 @@
         <v>3.8719861507415771</v>
       </c>
       <c r="C542" s="2">
-        <v>3.7959344387054443</v>
+        <v>3.6802148818969727</v>
       </c>
       <c r="D542" s="2">
         <v>4.1201076507568359</v>
       </c>
       <c r="E542" s="2">
-        <v>4.0539541244506836</v>
+        <v>4.0484580993652344</v>
       </c>
     </row>
     <row r="543">
@@ -8460,13 +7024,13 @@
         <v>4.3892917633056641</v>
       </c>
       <c r="C543" s="2">
-        <v>4.151362419128418</v>
+        <v>4.1122713088989258</v>
       </c>
       <c r="D543" s="2">
         <v>4.0656123161315918</v>
       </c>
       <c r="E543" s="2">
-        <v>3.9892416000366211</v>
+        <v>3.9810593128204346</v>
       </c>
     </row>
     <row r="544">
@@ -8477,13 +7041,13 @@
         <v>4.2202444076538086</v>
       </c>
       <c r="C544" s="2">
-        <v>4.3016219139099121</v>
+        <v>4.2584724426269531</v>
       </c>
       <c r="D544" s="2">
         <v>4.0455965995788574</v>
       </c>
       <c r="E544" s="2">
-        <v>3.9815061092376709</v>
+        <v>3.9617195129394531</v>
       </c>
     </row>
     <row r="545">
@@ -8494,13 +7058,13 @@
         <v>3.4897079467773438</v>
       </c>
       <c r="C545" s="2">
-        <v>3.4395802021026611</v>
+        <v>3.51833176612854</v>
       </c>
       <c r="D545" s="2">
         <v>4.0015368461608887</v>
       </c>
       <c r="E545" s="2">
-        <v>3.9371788501739502</v>
+        <v>3.9148509502410889</v>
       </c>
     </row>
     <row r="546">
@@ -8511,13 +7075,13 @@
         <v>4.257591724395752</v>
       </c>
       <c r="C546" s="2">
-        <v>4.2936587333679199</v>
+        <v>4.3244814872741699</v>
       </c>
       <c r="D546" s="2">
         <v>3.9736373424530029</v>
       </c>
       <c r="E546" s="2">
-        <v>3.9358797073364258</v>
+        <v>3.9095985889434814</v>
       </c>
     </row>
     <row r="547">
@@ -8528,13 +7092,13 @@
         <v>3.7832555770874023</v>
       </c>
       <c r="C547" s="2">
-        <v>3.6802628040313721</v>
+        <v>3.6838023662567139</v>
       </c>
       <c r="D547" s="2">
         <v>3.9578354358673096</v>
       </c>
       <c r="E547" s="2">
-        <v>3.9245960712432861</v>
+        <v>3.9115104675292969</v>
       </c>
     </row>
     <row r="548">
@@ -8545,13 +7109,13 @@
         <v>4.2277169227600098</v>
       </c>
       <c r="C548" s="2">
-        <v>4.2046899795532227</v>
+        <v>4.0936956405639648</v>
       </c>
       <c r="D548" s="2">
         <v>3.9201803207397461</v>
       </c>
       <c r="E548" s="2">
-        <v>3.9058601856231689</v>
+        <v>3.8745567798614502</v>
       </c>
     </row>
     <row r="549">
@@ -8562,13 +7126,13 @@
         <v>3.6729066371917725</v>
       </c>
       <c r="C549" s="2">
-        <v>3.6534287929534912</v>
+        <v>3.6741199493408203</v>
       </c>
       <c r="D549" s="2">
         <v>3.8609051704406738</v>
       </c>
       <c r="E549" s="2">
-        <v>3.8393847942352295</v>
+        <v>3.8027994632720947</v>
       </c>
     </row>
     <row r="550">
@@ -8579,13 +7143,13 @@
         <v>3.8500359058380127</v>
       </c>
       <c r="C550" s="2">
-        <v>3.9023780822753906</v>
+        <v>3.8409972190856934</v>
       </c>
       <c r="D550" s="2">
         <v>3.9055280685424805</v>
       </c>
       <c r="E550" s="2">
-        <v>3.8936059474945068</v>
+        <v>3.8523359298706055</v>
       </c>
     </row>
     <row r="551">
@@ -8596,13 +7160,13 @@
         <v>3.7297689914703369</v>
       </c>
       <c r="C551" s="2">
-        <v>3.6943824291229248</v>
+        <v>3.6974220275878906</v>
       </c>
       <c r="D551" s="2">
         <v>3.8611819744110107</v>
       </c>
       <c r="E551" s="2">
-        <v>3.8508379459381104</v>
+        <v>3.8077156543731689</v>
       </c>
     </row>
     <row r="552">
@@ -8613,13 +7177,13 @@
         <v>4.0503945350646973</v>
       </c>
       <c r="C552" s="2">
-        <v>3.9827394485473633</v>
+        <v>3.7796885967254639</v>
       </c>
       <c r="D552" s="2">
         <v>3.827488899230957</v>
       </c>
       <c r="E552" s="2">
-        <v>3.8165163993835449</v>
+        <v>3.7725594043731689</v>
       </c>
     </row>
     <row r="553">
@@ -8630,13 +7194,13 @@
         <v>3.6867685317993164</v>
       </c>
       <c r="C553" s="2">
-        <v>3.7033417224884033</v>
+        <v>3.6126565933227539</v>
       </c>
       <c r="D553" s="2">
         <v>3.7690713405609131</v>
       </c>
       <c r="E553" s="2">
-        <v>3.7357168197631836</v>
+        <v>3.7070646286010742</v>
       </c>
     </row>
     <row r="554">
@@ -8647,13 +7211,13 @@
         <v>3.8913142681121826</v>
       </c>
       <c r="C554" s="2">
-        <v>3.9275720119476318</v>
+        <v>3.9641599655151367</v>
       </c>
       <c r="D554" s="2">
-        <v>3.8859550952911377</v>
+        <v>3.8388018608093262</v>
       </c>
       <c r="E554" s="2">
-        <v>3.823641300201416</v>
+        <v>3.7529945373535156</v>
       </c>
     </row>
     <row r="555">
@@ -8664,13 +7228,13 @@
         <v>3.8584771156311035</v>
       </c>
       <c r="C555" s="2">
-        <v>3.9087467193603516</v>
+        <v>3.9228990077972412</v>
       </c>
       <c r="D555" s="2">
-        <v>3.9817161560058594</v>
+        <v>3.9248607158660889</v>
       </c>
       <c r="E555" s="2">
-        <v>3.906804084777832</v>
+        <v>3.8351039886474609</v>
       </c>
     </row>
     <row r="556">
@@ -8681,13 +7245,13 @@
         <v>3.4800169467926025</v>
       </c>
       <c r="C556" s="2">
-        <v>3.3713686466217041</v>
+        <v>3.3673961162567139</v>
       </c>
       <c r="D556" s="2">
-        <v>4.1360774040222168</v>
+        <v>4.0792217254638672</v>
       </c>
       <c r="E556" s="2">
-        <v>4.0284419059753418</v>
+        <v>3.9564995765686035</v>
       </c>
     </row>
     <row r="557">
@@ -8698,13 +7262,13 @@
         <v>3.7019596099853516</v>
       </c>
       <c r="C557" s="2">
-        <v>3.4774928092956543</v>
+        <v>3.5042417049407959</v>
       </c>
       <c r="D557" s="2">
-        <v>4.2073683738708496</v>
+        <v>4.1505126953125</v>
       </c>
       <c r="E557" s="2">
-        <v>4.0909180641174316</v>
+        <v>4.0406837463378906</v>
       </c>
     </row>
     <row r="558">
@@ -8712,16 +7276,16 @@
         <v>45413</v>
       </c>
       <c r="B558" s="2">
-        <v>4.7248592376708984</v>
+        <v>4.3004803657531738</v>
       </c>
       <c r="C558" s="2">
-        <v>4.4447507858276367</v>
+        <v>4.0874905586242676</v>
       </c>
       <c r="D558" s="2">
-        <v>4.3302793502807617</v>
+        <v>4.2734236717224121</v>
       </c>
       <c r="E558" s="2">
-        <v>4.2057290077209473</v>
+        <v>4.1610374450683594</v>
       </c>
     </row>
     <row r="559">
@@ -8729,16 +7293,16 @@
         <v>45444</v>
       </c>
       <c r="B559" s="2">
-        <v>4.7118868827819824</v>
+        <v>4.6245660781860352</v>
       </c>
       <c r="C559" s="2">
-        <v>4.6508426666259766</v>
+        <v>4.5799808502197266</v>
       </c>
       <c r="D559" s="2">
-        <v>4.4643926620483398</v>
+        <v>4.4018120765686035</v>
       </c>
       <c r="E559" s="2">
-        <v>4.3624730110168457</v>
+        <v>4.2949919700622559</v>
       </c>
     </row>
     <row r="560">
@@ -8749,13 +7313,13 @@
         <v>5.1190185546875</v>
       </c>
       <c r="C560" s="2">
-        <v>4.7891225814819336</v>
+        <v>4.7899818420410156</v>
       </c>
       <c r="D560" s="2">
-        <v>4.6924991607666016</v>
+        <v>4.6019291877746582</v>
       </c>
       <c r="E560" s="2">
-        <v>4.5566301345825195</v>
+        <v>4.4383773803710938</v>
       </c>
     </row>
     <row r="561">
@@ -8766,13 +7330,13 @@
         <v>4.6920127868652344</v>
       </c>
       <c r="C561" s="2">
-        <v>4.5450239181518555</v>
+        <v>4.5373454093933105</v>
       </c>
       <c r="D561" s="2">
-        <v>4.9908885955810547</v>
+        <v>4.8797531127929688</v>
       </c>
       <c r="E561" s="2">
-        <v>4.8634376525878906</v>
+        <v>4.7312016487121582</v>
       </c>
     </row>
     <row r="562">
@@ -8783,13 +7347,13 @@
         <v>4.7929677963256836</v>
       </c>
       <c r="C562" s="2">
-        <v>4.7366428375244141</v>
+        <v>4.6958394050598145</v>
       </c>
       <c r="D562" s="2">
-        <v>5.218010425567627</v>
+        <v>5.0986638069152832</v>
       </c>
       <c r="E562" s="2">
-        <v>5.1021428108215332</v>
+        <v>4.9400806427001953</v>
       </c>
     </row>
     <row r="563">
@@ -8797,16 +7361,16 @@
         <v>45566</v>
       </c>
       <c r="B563" s="2">
-        <v>5.098334789276123</v>
+        <v>5.0468111038208008</v>
       </c>
       <c r="C563" s="2">
-        <v>5.3382649421691895</v>
+        <v>5.1697516441345215</v>
       </c>
       <c r="D563" s="2">
-        <v>5.3737473487854004</v>
+        <v>5.3115234375</v>
       </c>
       <c r="E563" s="2">
-        <v>5.2875967025756836</v>
+        <v>5.1593103408813477</v>
       </c>
     </row>
     <row r="564">
@@ -8814,16 +7378,16 @@
         <v>45597</v>
       </c>
       <c r="B564" s="2">
-        <v>5.9114370346069336</v>
+        <v>5.6595301628112793</v>
       </c>
       <c r="C564" s="2">
-        <v>5.6561598777770996</v>
+        <v>5.2133684158325195</v>
       </c>
       <c r="D564" s="2">
-        <v>5.5502724647521973</v>
+        <v>5.4977846145629883</v>
       </c>
       <c r="E564" s="2">
-        <v>5.463860034942627</v>
+        <v>5.3269171714782715</v>
       </c>
     </row>
     <row r="565">
@@ -8831,16 +7395,16 @@
         <v>45627</v>
       </c>
       <c r="B565" s="2">
-        <v>6.1655206680297852</v>
+        <v>5.9804320335388184</v>
       </c>
       <c r="C565" s="2">
-        <v>6.1326384544372559</v>
+        <v>6.0028142929077148</v>
       </c>
       <c r="D565" s="2">
-        <v>5.6535191535949707</v>
+        <v>5.6004495620727539</v>
       </c>
       <c r="E565" s="2">
-        <v>5.5724287033081055</v>
+        <v>5.424473762512207</v>
       </c>
     </row>
     <row r="566">
@@ -8848,16 +7412,16 @@
         <v>45658</v>
       </c>
       <c r="B566" s="2">
-        <v>5.7460579872131348</v>
+        <v>5.6721553802490234</v>
       </c>
       <c r="C566" s="2">
-        <v>5.6258382797241211</v>
+        <v>5.384152889251709</v>
       </c>
       <c r="D566" s="2">
-        <v>5.773707389831543</v>
+        <v>5.7438645362854004</v>
       </c>
       <c r="E566" s="2">
-        <v>5.7008543014526367</v>
+        <v>5.5509777069091797</v>
       </c>
     </row>
     <row r="567">
@@ -8865,16 +7429,16 @@
         <v>45689</v>
       </c>
       <c r="B567" s="2">
-        <v>6.126490592956543</v>
+        <v>6.2162184715270996</v>
       </c>
       <c r="C567" s="2">
-        <v>6.113837718963623</v>
+        <v>6.0605583190917969</v>
       </c>
       <c r="D567" s="2">
-        <v>5.9138131141662598</v>
+        <v>5.9107174873352051</v>
       </c>
       <c r="E567" s="2">
-        <v>5.8385987281799316</v>
+        <v>5.703244686126709</v>
       </c>
     </row>
     <row r="568">
@@ -8882,16 +7446,16 @@
         <v>45717</v>
       </c>
       <c r="B568" s="2">
-        <v>6.3006100654602051</v>
+        <v>6.3009171485900879</v>
       </c>
       <c r="C568" s="2">
-        <v>6.237213134765625</v>
+        <v>6.0884442329406738</v>
       </c>
       <c r="D568" s="2">
-        <v>6.0497264862060547</v>
+        <v>5.9663195610046387</v>
       </c>
       <c r="E568" s="2">
-        <v>5.9219880104064941</v>
+        <v>5.729891300201416</v>
       </c>
     </row>
     <row r="569">
@@ -8899,17 +7463,145 @@
         <v>45748</v>
       </c>
       <c r="B569" s="2">
-        <v>6.048241138458252</v>
+        <v>6.0429997444152832</v>
       </c>
       <c r="C569" s="2">
-        <v>5.766240119934082</v>
+        <v>5.6679892539978027</v>
       </c>
       <c r="D569" s="2">
-        <v>6.0773839950561523</v>
+        <v>5.9827446937561035</v>
       </c>
       <c r="E569" s="2">
-        <v>5.9751534461975098</v>
-      </c>
+        <v>5.7689356803894043</v>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" s="1">
+        <v>45778</v>
+      </c>
+      <c r="B570" s="2">
+        <v>5.9827508926391602</v>
+      </c>
+      <c r="C570" s="2">
+        <v>5.6758790016174316</v>
+      </c>
+      <c r="D570" s="2">
+        <v>5.9355225563049316</v>
+      </c>
+      <c r="E570" s="2">
+        <v>5.704859733581543</v>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" s="1">
+        <v>45809</v>
+      </c>
+      <c r="B571" s="2">
+        <v>6.2946443557739258</v>
+      </c>
+      <c r="C571" s="2">
+        <v>6.0662431716918945</v>
+      </c>
+      <c r="D571" s="2">
+        <v>5.9084877967834473</v>
+      </c>
+      <c r="E571" s="2">
+        <v>5.6973419189453125</v>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" s="1">
+        <v>45839</v>
+      </c>
+      <c r="B572" s="2">
+        <v>5.5472264289855957</v>
+      </c>
+      <c r="C572" s="2">
+        <v>5.409574031829834</v>
+      </c>
+      <c r="D572" s="2">
+        <v>5.816521167755127</v>
+      </c>
+      <c r="E572" s="2">
+        <v>5.6134462356567383</v>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" s="1">
+        <v>45870</v>
+      </c>
+      <c r="B573" s="2">
+        <v>5.8073563575744629</v>
+      </c>
+      <c r="C573" s="2">
+        <v>5.5647640228271484</v>
+      </c>
+      <c r="D573" s="2">
+        <v>5.7559714317321777</v>
+      </c>
+      <c r="E573" s="2">
+        <v>5.5540714263916016</v>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" s="1">
+        <v>45901</v>
+      </c>
+      <c r="B574" s="2">
+        <v>5.5554342269897461</v>
+      </c>
+      <c r="C574" s="2">
+        <v>5.4261317253112793</v>
+      </c>
+      <c r="D574" s="2">
+        <v>5.7149677276611328</v>
+      </c>
+      <c r="E574" s="2">
+        <v>5.5377974510192871</v>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" s="1">
+        <v>45931</v>
+      </c>
+      <c r="B575" s="2">
+        <v>5.4288439750671387</v>
+      </c>
+      <c r="C575" s="2">
+        <v>5.3164925575256348</v>
+      </c>
+      <c r="D575" s="2">
+        <v>5.6703372001647949</v>
+      </c>
+      <c r="E575" s="2">
+        <v>5.5147838592529297</v>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" s="1">
+        <v>45962</v>
+      </c>
+      <c r="B576" s="2">
+        <v>5.388516902923584</v>
+      </c>
+      <c r="C576" s="2">
+        <v>5.3054971694946289</v>
+      </c>
+      <c r="D576" s="2">
+        <v>5.5454754829406738</v>
+      </c>
+      <c r="E576" s="2">
+        <v>5.4044919013977051</v>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" s="1">
+        <v>45992</v>
+      </c>
+      <c r="B577" s="2"/>
+      <c r="C577" s="2"/>
+      <c r="D577" s="2"/>
+      <c r="E577" s="2"/>
     </row>
   </sheetData>
 </worksheet>
